--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206463</t>
+          <t>2026-03-02T04:10:35.824117</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206477</t>
+          <t>2026-03-02T04:10:35.824131</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206481</t>
+          <t>2026-03-02T04:10:35.824135</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206484</t>
+          <t>2026-03-02T04:10:35.824138</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206487</t>
+          <t>2026-03-02T04:10:35.824141</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206490</t>
+          <t>2026-03-02T04:10:35.824144</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206493</t>
+          <t>2026-03-02T04:10:35.824147</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206496</t>
+          <t>2026-03-02T04:10:35.824149</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206498</t>
+          <t>2026-03-02T04:10:35.824152</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206501</t>
+          <t>2026-03-02T04:10:35.824155</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206504</t>
+          <t>2026-03-02T04:10:35.824158</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206507</t>
+          <t>2026-03-02T04:10:35.824161</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206509</t>
+          <t>2026-03-02T04:10:35.824164</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206512</t>
+          <t>2026-03-02T04:10:35.824166</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206516</t>
+          <t>2026-03-02T04:10:35.824170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206519</t>
+          <t>2026-03-02T04:10:35.824173</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206521</t>
+          <t>2026-03-02T04:10:35.824176</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206524</t>
+          <t>2026-03-02T04:10:35.824179</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206528</t>
+          <t>2026-03-02T04:10:35.824182</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206532</t>
+          <t>2026-03-02T04:10:35.824185</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206535</t>
+          <t>2026-03-02T04:10:35.824187</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206539</t>
+          <t>2026-03-02T04:10:35.824204</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206541</t>
+          <t>2026-03-02T04:10:35.824208</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206544</t>
+          <t>2026-03-02T04:10:35.824211</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206547</t>
+          <t>2026-03-02T04:10:35.824213</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206550</t>
+          <t>2026-03-02T04:10:35.824216</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206553</t>
+          <t>2026-03-02T04:10:35.824228</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206555</t>
+          <t>2026-03-02T04:10:35.824233</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206558</t>
+          <t>2026-03-02T04:10:35.824239</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206561</t>
+          <t>2026-03-02T04:10:35.824243</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206564</t>
+          <t>2026-03-02T04:10:35.824246</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206575</t>
+          <t>2026-03-02T04:10:35.824248</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206578</t>
+          <t>2026-03-02T04:10:35.824251</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1312.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>1375</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206581</t>
+          <t>2026-03-02T04:10:35.824254</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1315</v>
+        <v>1378</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206583</t>
+          <t>2026-03-02T04:10:35.824257</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1310</v>
+        <v>1373</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206586</t>
+          <t>2026-03-02T04:10:35.824259</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1304.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206589</t>
+          <t>2026-03-02T04:10:35.824262</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1306.00</t>
+          <t>1312.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206592</t>
+          <t>2026-03-02T04:10:35.824265</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1315.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1300</v>
+        <v>1315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206594</t>
+          <t>2026-03-02T04:10:35.824267</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1423.00</t>
+          <t>1304.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1423</v>
+        <v>1304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206597</t>
+          <t>2026-03-02T04:10:35.824270</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1425.00</t>
+          <t>1306.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1425</v>
+        <v>1306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206600</t>
+          <t>2026-03-02T04:10:35.824273</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1418</v>
+        <v>1300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206603</t>
+          <t>2026-03-02T04:10:35.824275</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824117</t>
+          <t>2026-03-03T04:11:31.643734</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824131</t>
+          <t>2026-03-03T04:11:31.643749</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824135</t>
+          <t>2026-03-03T04:11:31.643753</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824138</t>
+          <t>2026-03-03T04:11:31.643756</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824141</t>
+          <t>2026-03-03T04:11:31.643759</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824144</t>
+          <t>2026-03-03T04:11:31.643763</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824147</t>
+          <t>2026-03-03T04:11:31.643766</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824149</t>
+          <t>2026-03-03T04:11:31.643769</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824152</t>
+          <t>2026-03-03T04:11:31.643772</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824155</t>
+          <t>2026-03-03T04:11:31.643776</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824158</t>
+          <t>2026-03-03T04:11:31.643779</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824161</t>
+          <t>2026-03-03T04:11:31.643782</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824164</t>
+          <t>2026-03-03T04:11:31.643785</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824166</t>
+          <t>2026-03-03T04:11:31.643789</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824170</t>
+          <t>2026-03-03T04:11:31.643792</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824173</t>
+          <t>2026-03-03T04:11:31.643796</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824176</t>
+          <t>2026-03-03T04:11:31.643799</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824179</t>
+          <t>2026-03-03T04:11:31.643802</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824182</t>
+          <t>2026-03-03T04:11:31.643806</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824185</t>
+          <t>2026-03-03T04:11:31.643809</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824187</t>
+          <t>2026-03-03T04:11:31.643812</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824204</t>
+          <t>2026-03-03T04:11:31.643816</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824208</t>
+          <t>2026-03-03T04:11:31.643819</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824211</t>
+          <t>2026-03-03T04:11:31.643822</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824213</t>
+          <t>2026-03-03T04:11:31.643825</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824216</t>
+          <t>2026-03-03T04:11:31.643829</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824228</t>
+          <t>2026-03-03T04:11:31.643832</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824233</t>
+          <t>2026-03-03T04:11:31.643836</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824239</t>
+          <t>2026-03-03T04:11:31.643839</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824243</t>
+          <t>2026-03-03T04:11:31.643843</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824246</t>
+          <t>2026-03-03T04:11:31.643854</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824248</t>
+          <t>2026-03-03T04:11:31.643857</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824251</t>
+          <t>2026-03-03T04:11:31.643860</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824254</t>
+          <t>2026-03-03T04:11:31.643863</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824257</t>
+          <t>2026-03-03T04:11:31.643867</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824259</t>
+          <t>2026-03-03T04:11:31.643870</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1310</v>
+        <v>1373</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824262</t>
+          <t>2026-03-03T04:11:31.643873</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1312.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>1375</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824265</t>
+          <t>2026-03-03T04:11:31.643876</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1315</v>
+        <v>1378</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824267</t>
+          <t>2026-03-03T04:11:31.643879</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1304.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824270</t>
+          <t>2026-03-03T04:11:31.643882</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1306.00</t>
+          <t>1312.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824273</t>
+          <t>2026-03-03T04:11:31.643885</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1315.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1300</v>
+        <v>1315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824275</t>
+          <t>2026-03-03T04:11:31.643889</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643734</t>
+          <t>2026-03-04T04:05:09.006766</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643749</t>
+          <t>2026-03-04T04:05:09.006784</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643753</t>
+          <t>2026-03-04T04:05:09.006790</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643756</t>
+          <t>2026-03-04T04:05:09.006796</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643759</t>
+          <t>2026-03-04T04:05:09.006803</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643763</t>
+          <t>2026-03-04T04:05:09.006809</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643766</t>
+          <t>2026-03-04T04:05:09.006813</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643769</t>
+          <t>2026-03-04T04:05:09.006816</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643772</t>
+          <t>2026-03-04T04:05:09.006819</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643776</t>
+          <t>2026-03-04T04:05:09.006822</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643779</t>
+          <t>2026-03-04T04:05:09.006825</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643782</t>
+          <t>2026-03-04T04:05:09.006827</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643785</t>
+          <t>2026-03-04T04:05:09.006830</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643789</t>
+          <t>2026-03-04T04:05:09.006833</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643792</t>
+          <t>2026-03-04T04:05:09.006837</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643796</t>
+          <t>2026-03-04T04:05:09.006840</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643799</t>
+          <t>2026-03-04T04:05:09.006843</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643802</t>
+          <t>2026-03-04T04:05:09.006845</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643806</t>
+          <t>2026-03-04T04:05:09.006849</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643809</t>
+          <t>2026-03-04T04:05:09.006853</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643812</t>
+          <t>2026-03-04T04:05:09.006856</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643816</t>
+          <t>2026-03-04T04:05:09.006859</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643819</t>
+          <t>2026-03-04T04:05:09.006862</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643822</t>
+          <t>2026-03-04T04:05:09.006865</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643825</t>
+          <t>2026-03-04T04:05:09.006867</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643829</t>
+          <t>2026-03-04T04:05:09.006870</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643832</t>
+          <t>2026-03-04T04:05:09.006874</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643836</t>
+          <t>2026-03-04T04:05:09.006876</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643839</t>
+          <t>2026-03-04T04:05:09.006880</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643843</t>
+          <t>2026-03-04T04:05:09.006883</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643854</t>
+          <t>2026-03-04T04:05:09.006893</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643857</t>
+          <t>2026-03-04T04:05:09.006896</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643860</t>
+          <t>2026-03-04T04:05:09.006899</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643863</t>
+          <t>2026-03-04T04:05:09.006902</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643867</t>
+          <t>2026-03-04T04:05:09.006905</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643870</t>
+          <t>2026-03-04T04:05:09.006908</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643873</t>
+          <t>2026-03-04T04:05:09.006910</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643876</t>
+          <t>2026-03-04T04:05:09.006913</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643879</t>
+          <t>2026-03-04T04:05:09.006916</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1310</v>
+        <v>1373</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643882</t>
+          <t>2026-03-04T04:05:09.006919</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1312.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>1375</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643885</t>
+          <t>2026-03-04T04:05:09.006921</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1315</v>
+        <v>1378</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643889</t>
+          <t>2026-03-04T04:05:09.006924</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006766</t>
+          <t>2026-03-05T04:09:03.882129</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006784</t>
+          <t>2026-03-05T04:09:03.882142</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006790</t>
+          <t>2026-03-05T04:09:03.882146</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006796</t>
+          <t>2026-03-05T04:09:03.882149</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006803</t>
+          <t>2026-03-05T04:09:03.882152</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006809</t>
+          <t>2026-03-05T04:09:03.882156</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006813</t>
+          <t>2026-03-05T04:09:03.882158</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006816</t>
+          <t>2026-03-05T04:09:03.882161</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006819</t>
+          <t>2026-03-05T04:09:03.882164</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006822</t>
+          <t>2026-03-05T04:09:03.882167</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006825</t>
+          <t>2026-03-05T04:09:03.882170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006827</t>
+          <t>2026-03-05T04:09:03.882173</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006830</t>
+          <t>2026-03-05T04:09:03.882176</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006833</t>
+          <t>2026-03-05T04:09:03.882180</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006837</t>
+          <t>2026-03-05T04:09:03.882186</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006840</t>
+          <t>2026-03-05T04:09:03.882190</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006843</t>
+          <t>2026-03-05T04:09:03.882192</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006845</t>
+          <t>2026-03-05T04:09:03.882195</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006849</t>
+          <t>2026-03-05T04:09:03.882198</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006853</t>
+          <t>2026-03-05T04:09:03.882201</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006856</t>
+          <t>2026-03-05T04:09:03.882204</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006859</t>
+          <t>2026-03-05T04:09:03.882206</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006862</t>
+          <t>2026-03-05T04:09:03.882209</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006865</t>
+          <t>2026-03-05T04:09:03.882212</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006867</t>
+          <t>2026-03-05T04:09:03.882215</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006870</t>
+          <t>2026-03-05T04:09:03.882218</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006874</t>
+          <t>2026-03-05T04:09:03.882221</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006876</t>
+          <t>2026-03-05T04:09:03.882223</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006880</t>
+          <t>2026-03-05T04:09:03.882227</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006883</t>
+          <t>2026-03-05T04:09:03.882230</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006893</t>
+          <t>2026-03-05T04:09:03.882232</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006896</t>
+          <t>2026-03-05T04:09:03.882243</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006899</t>
+          <t>2026-03-05T04:09:03.882246</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006902</t>
+          <t>2026-03-05T04:09:03.882249</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006905</t>
+          <t>2026-03-05T04:09:03.882252</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006908</t>
+          <t>2026-03-05T04:09:03.882255</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006910</t>
+          <t>2026-03-05T04:09:03.882258</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006913</t>
+          <t>2026-03-05T04:09:03.882260</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006916</t>
+          <t>2026-03-05T04:09:03.882263</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006919</t>
+          <t>2026-03-05T04:09:03.882266</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006921</t>
+          <t>2026-03-05T04:09:03.882268</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006924</t>
+          <t>2026-03-05T04:09:03.882271</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882129</t>
+          <t>2026-03-06T04:06:05.863917</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882142</t>
+          <t>2026-03-06T04:06:05.863931</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882146</t>
+          <t>2026-03-06T04:06:05.863935</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882149</t>
+          <t>2026-03-06T04:06:05.863938</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882152</t>
+          <t>2026-03-06T04:06:05.863941</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882156</t>
+          <t>2026-03-06T04:06:05.863944</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882158</t>
+          <t>2026-03-06T04:06:05.863947</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882161</t>
+          <t>2026-03-06T04:06:05.863950</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882164</t>
+          <t>2026-03-06T04:06:05.863953</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882167</t>
+          <t>2026-03-06T04:06:05.863956</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882170</t>
+          <t>2026-03-06T04:06:05.863959</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882173</t>
+          <t>2026-03-06T04:06:05.863962</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882176</t>
+          <t>2026-03-06T04:06:05.863964</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882180</t>
+          <t>2026-03-06T04:06:05.863967</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882186</t>
+          <t>2026-03-06T04:06:05.863971</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882190</t>
+          <t>2026-03-06T04:06:05.863974</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882192</t>
+          <t>2026-03-06T04:06:05.863976</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882195</t>
+          <t>2026-03-06T04:06:05.863979</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882198</t>
+          <t>2026-03-06T04:06:05.863982</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882201</t>
+          <t>2026-03-06T04:06:05.863985</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882204</t>
+          <t>2026-03-06T04:06:05.863988</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882206</t>
+          <t>2026-03-06T04:06:05.863992</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882209</t>
+          <t>2026-03-06T04:06:05.863996</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882212</t>
+          <t>2026-03-06T04:06:05.864000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882215</t>
+          <t>2026-03-06T04:06:05.864003</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882218</t>
+          <t>2026-03-06T04:06:05.864005</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882221</t>
+          <t>2026-03-06T04:06:05.864008</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882223</t>
+          <t>2026-03-06T04:06:05.864011</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882227</t>
+          <t>2026-03-06T04:06:05.864014</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882230</t>
+          <t>2026-03-06T04:06:05.864017</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882232</t>
+          <t>2026-03-06T04:06:05.864020</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882243</t>
+          <t>2026-03-06T04:06:05.864023</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882246</t>
+          <t>2026-03-06T04:06:05.864025</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882249</t>
+          <t>2026-03-06T04:06:05.864028</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882252</t>
+          <t>2026-03-06T04:06:05.864031</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882255</t>
+          <t>2026-03-06T04:06:05.864034</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882258</t>
+          <t>2026-03-06T04:06:05.864037</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882260</t>
+          <t>2026-03-06T04:06:05.864040</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882263</t>
+          <t>2026-03-06T04:06:05.864042</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882266</t>
+          <t>2026-03-06T04:06:05.864054</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882268</t>
+          <t>2026-03-06T04:06:05.864057</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882271</t>
+          <t>2026-03-06T04:06:05.864060</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863917</t>
+          <t>2026-03-07T03:57:02.160704</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863931</t>
+          <t>2026-03-07T03:57:02.160716</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863935</t>
+          <t>2026-03-07T03:57:02.160720</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863938</t>
+          <t>2026-03-07T03:57:02.160723</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863941</t>
+          <t>2026-03-07T03:57:02.160726</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863944</t>
+          <t>2026-03-07T03:57:02.160744</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863947</t>
+          <t>2026-03-07T03:57:02.160751</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863950</t>
+          <t>2026-03-07T03:57:02.160759</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863953</t>
+          <t>2026-03-07T03:57:02.160765</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863956</t>
+          <t>2026-03-07T03:57:02.160770</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863959</t>
+          <t>2026-03-07T03:57:02.160775</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863962</t>
+          <t>2026-03-07T03:57:02.160781</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863964</t>
+          <t>2026-03-07T03:57:02.160788</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863967</t>
+          <t>2026-03-07T03:57:02.160795</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863971</t>
+          <t>2026-03-07T03:57:02.160801</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863974</t>
+          <t>2026-03-07T03:57:02.160808</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863976</t>
+          <t>2026-03-07T03:57:02.160811</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863979</t>
+          <t>2026-03-07T03:57:02.160814</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863982</t>
+          <t>2026-03-07T03:57:02.160817</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863985</t>
+          <t>2026-03-07T03:57:02.160820</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863988</t>
+          <t>2026-03-07T03:57:02.160823</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863992</t>
+          <t>2026-03-07T03:57:02.160825</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863996</t>
+          <t>2026-03-07T03:57:02.160828</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864000</t>
+          <t>2026-03-07T03:57:02.160831</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864003</t>
+          <t>2026-03-07T03:57:02.160833</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864005</t>
+          <t>2026-03-07T03:57:02.160836</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864008</t>
+          <t>2026-03-07T03:57:02.160839</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864011</t>
+          <t>2026-03-07T03:57:02.160842</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864014</t>
+          <t>2026-03-07T03:57:02.160845</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864017</t>
+          <t>2026-03-07T03:57:02.160847</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864020</t>
+          <t>2026-03-07T03:57:02.160850</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864023</t>
+          <t>2026-03-07T03:57:02.160854</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864025</t>
+          <t>2026-03-07T03:57:02.160857</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864028</t>
+          <t>2026-03-07T03:57:02.160859</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864031</t>
+          <t>2026-03-07T03:57:02.160862</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864034</t>
+          <t>2026-03-07T03:57:02.160865</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864037</t>
+          <t>2026-03-07T03:57:02.160868</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864040</t>
+          <t>2026-03-07T03:57:02.160870</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,202 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864042</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>六福</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-03-06T04:06:05.864054</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>周大福</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1299.00</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1299</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2026-03-06T04:06:05.864057</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>周生生</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-03-06T04:06:05.864060</t>
+          <t>2026-03-07T03:57:02.160873</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160704</t>
+          <t>2026-03-08T04:07:52.125602</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160716</t>
+          <t>2026-03-08T04:07:52.125617</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160720</t>
+          <t>2026-03-08T04:07:52.125621</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160723</t>
+          <t>2026-03-08T04:07:52.125625</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160726</t>
+          <t>2026-03-08T04:07:52.125628</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160744</t>
+          <t>2026-03-08T04:07:52.125631</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160751</t>
+          <t>2026-03-08T04:07:52.125634</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160759</t>
+          <t>2026-03-08T04:07:52.125636</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160765</t>
+          <t>2026-03-08T04:07:52.125639</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160770</t>
+          <t>2026-03-08T04:07:52.125642</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160775</t>
+          <t>2026-03-08T04:07:52.125645</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160781</t>
+          <t>2026-03-08T04:07:52.125647</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160788</t>
+          <t>2026-03-08T04:07:52.125650</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160795</t>
+          <t>2026-03-08T04:07:52.125653</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160801</t>
+          <t>2026-03-08T04:07:52.125656</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160808</t>
+          <t>2026-03-08T04:07:52.125658</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160811</t>
+          <t>2026-03-08T04:07:52.125661</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160814</t>
+          <t>2026-03-08T04:07:52.125664</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160817</t>
+          <t>2026-03-08T04:07:52.125668</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160820</t>
+          <t>2026-03-08T04:07:52.125671</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160823</t>
+          <t>2026-03-08T04:07:52.125675</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160825</t>
+          <t>2026-03-08T04:07:52.125679</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160828</t>
+          <t>2026-03-08T04:07:52.125702</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160831</t>
+          <t>2026-03-08T04:07:52.125706</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160833</t>
+          <t>2026-03-08T04:07:52.125708</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160836</t>
+          <t>2026-03-08T04:07:52.125711</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160839</t>
+          <t>2026-03-08T04:07:52.125714</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160842</t>
+          <t>2026-03-08T04:07:52.125717</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160845</t>
+          <t>2026-03-08T04:07:52.125720</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160847</t>
+          <t>2026-03-08T04:07:52.125722</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160850</t>
+          <t>2026-03-08T04:07:52.125725</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160854</t>
+          <t>2026-03-08T04:07:52.125728</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160857</t>
+          <t>2026-03-08T04:07:52.125731</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160859</t>
+          <t>2026-03-08T04:07:52.125734</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160862</t>
+          <t>2026-03-08T04:07:52.125737</t>
         </is>
       </c>
     </row>
@@ -2819,202 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160865</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>周生生</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-03-07T03:57:02.160868</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>六福</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-03-07T03:57:02.160870</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>周大福</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1299.00</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1299</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-03-07T03:57:02.160873</t>
+          <t>2026-03-08T04:07:52.125740</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125602</t>
+          <t>2026-03-09T04:13:11.803683</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125617</t>
+          <t>2026-03-09T04:13:11.803697</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125621</t>
+          <t>2026-03-09T04:13:11.803701</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125625</t>
+          <t>2026-03-09T04:13:11.803704</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125628</t>
+          <t>2026-03-09T04:13:11.803707</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125631</t>
+          <t>2026-03-09T04:13:11.803710</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125634</t>
+          <t>2026-03-09T04:13:11.803713</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125636</t>
+          <t>2026-03-09T04:13:11.803716</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125639</t>
+          <t>2026-03-09T04:13:11.803718</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125642</t>
+          <t>2026-03-09T04:13:11.803722</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125645</t>
+          <t>2026-03-09T04:13:11.803724</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125647</t>
+          <t>2026-03-09T04:13:11.803727</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125650</t>
+          <t>2026-03-09T04:13:11.803730</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125653</t>
+          <t>2026-03-09T04:13:11.803737</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125656</t>
+          <t>2026-03-09T04:13:11.803740</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125658</t>
+          <t>2026-03-09T04:13:11.803744</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125661</t>
+          <t>2026-03-09T04:13:11.803746</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125664</t>
+          <t>2026-03-09T04:13:11.803749</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125668</t>
+          <t>2026-03-09T04:13:11.803753</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125671</t>
+          <t>2026-03-09T04:13:11.803757</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125675</t>
+          <t>2026-03-09T04:13:11.803760</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125679</t>
+          <t>2026-03-09T04:13:11.803763</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125702</t>
+          <t>2026-03-09T04:13:11.803765</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125706</t>
+          <t>2026-03-09T04:13:11.803768</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125708</t>
+          <t>2026-03-09T04:13:11.803771</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125711</t>
+          <t>2026-03-09T04:13:11.803774</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125714</t>
+          <t>2026-03-09T04:13:11.803777</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125717</t>
+          <t>2026-03-09T04:13:11.803780</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125720</t>
+          <t>2026-03-09T04:13:11.803782</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125722</t>
+          <t>2026-03-09T04:13:11.803785</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125725</t>
+          <t>2026-03-09T04:13:11.803788</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125728</t>
+          <t>2026-03-09T04:13:11.803791</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125731</t>
+          <t>2026-03-09T04:13:11.803793</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125734</t>
+          <t>2026-03-09T04:13:11.803810</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125737</t>
+          <t>2026-03-09T04:13:11.803814</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125740</t>
+          <t>2026-03-09T04:13:11.803817</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803683</t>
+          <t>2026-03-10T04:05:21.738186</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803697</t>
+          <t>2026-03-10T04:05:21.738200</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803701</t>
+          <t>2026-03-10T04:05:21.738204</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803704</t>
+          <t>2026-03-10T04:05:21.738207</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803707</t>
+          <t>2026-03-10T04:05:21.738210</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803710</t>
+          <t>2026-03-10T04:05:21.738213</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803713</t>
+          <t>2026-03-10T04:05:21.738216</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803716</t>
+          <t>2026-03-10T04:05:21.738218</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803718</t>
+          <t>2026-03-10T04:05:21.738222</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803722</t>
+          <t>2026-03-10T04:05:21.738224</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803724</t>
+          <t>2026-03-10T04:05:21.738227</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803727</t>
+          <t>2026-03-10T04:05:21.738230</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803730</t>
+          <t>2026-03-10T04:05:21.738233</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803737</t>
+          <t>2026-03-10T04:05:21.738235</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803740</t>
+          <t>2026-03-10T04:05:21.738238</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803744</t>
+          <t>2026-03-10T04:05:21.738241</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803746</t>
+          <t>2026-03-10T04:05:21.738243</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803749</t>
+          <t>2026-03-10T04:05:21.738246</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803753</t>
+          <t>2026-03-10T04:05:21.738250</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803757</t>
+          <t>2026-03-10T04:05:21.738253</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803760</t>
+          <t>2026-03-10T04:05:21.738259</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803763</t>
+          <t>2026-03-10T04:05:21.738266</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803765</t>
+          <t>2026-03-10T04:05:21.738273</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803768</t>
+          <t>2026-03-10T04:05:21.738280</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803771</t>
+          <t>2026-03-10T04:05:21.738285</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803774</t>
+          <t>2026-03-10T04:05:21.738291</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803777</t>
+          <t>2026-03-10T04:05:21.738296</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803780</t>
+          <t>2026-03-10T04:05:21.738302</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803782</t>
+          <t>2026-03-10T04:05:21.738309</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803785</t>
+          <t>2026-03-10T04:05:21.738315</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803788</t>
+          <t>2026-03-10T04:05:21.738318</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803791</t>
+          <t>2026-03-10T04:05:21.738321</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803793</t>
+          <t>2026-03-10T04:05:21.738324</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803810</t>
+          <t>2026-03-10T04:05:21.738326</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803814</t>
+          <t>2026-03-10T04:05:21.738330</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803817</t>
+          <t>2026-03-10T04:05:21.738333</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738186</t>
+          <t>2026-03-11T04:06:22.487669</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738200</t>
+          <t>2026-03-11T04:06:22.487682</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738204</t>
+          <t>2026-03-11T04:06:22.487686</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738207</t>
+          <t>2026-03-11T04:06:22.487689</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738210</t>
+          <t>2026-03-11T04:06:22.487692</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738213</t>
+          <t>2026-03-11T04:06:22.487695</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738216</t>
+          <t>2026-03-11T04:06:22.487698</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738218</t>
+          <t>2026-03-11T04:06:22.487701</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738222</t>
+          <t>2026-03-11T04:06:22.487704</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738224</t>
+          <t>2026-03-11T04:06:22.487707</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738227</t>
+          <t>2026-03-11T04:06:22.487709</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738230</t>
+          <t>2026-03-11T04:06:22.487712</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738233</t>
+          <t>2026-03-11T04:06:22.487715</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738235</t>
+          <t>2026-03-11T04:06:22.487718</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738238</t>
+          <t>2026-03-11T04:06:22.487720</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738241</t>
+          <t>2026-03-11T04:06:22.487723</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738243</t>
+          <t>2026-03-11T04:06:22.487726</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738246</t>
+          <t>2026-03-11T04:06:22.487729</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738250</t>
+          <t>2026-03-11T04:06:22.487733</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738253</t>
+          <t>2026-03-11T04:06:22.487736</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738259</t>
+          <t>2026-03-11T04:06:22.487739</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738266</t>
+          <t>2026-03-11T04:06:22.487741</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738273</t>
+          <t>2026-03-11T04:06:22.487744</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738280</t>
+          <t>2026-03-11T04:06:22.487747</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738285</t>
+          <t>2026-03-11T04:06:22.487750</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738291</t>
+          <t>2026-03-11T04:06:22.487752</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738296</t>
+          <t>2026-03-11T04:06:22.487755</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738302</t>
+          <t>2026-03-11T04:06:22.487758</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738309</t>
+          <t>2026-03-11T04:06:22.487761</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738315</t>
+          <t>2026-03-11T04:06:22.487764</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738318</t>
+          <t>2026-03-11T04:06:22.487766</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738321</t>
+          <t>2026-03-11T04:06:22.487769</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738324</t>
+          <t>2026-03-11T04:06:22.487772</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738326</t>
+          <t>2026-03-11T04:06:22.487775</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738330</t>
+          <t>2026-03-11T04:06:22.487778</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738333</t>
+          <t>2026-03-11T04:06:22.487781</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487669</t>
+          <t>2026-03-12T04:10:08.099875</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487682</t>
+          <t>2026-03-12T04:10:08.099885</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487686</t>
+          <t>2026-03-12T04:10:08.099889</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487689</t>
+          <t>2026-03-12T04:10:08.099892</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487692</t>
+          <t>2026-03-12T04:10:08.099895</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487695</t>
+          <t>2026-03-12T04:10:08.099898</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487698</t>
+          <t>2026-03-12T04:10:08.099901</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487701</t>
+          <t>2026-03-12T04:10:08.099904</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487704</t>
+          <t>2026-03-12T04:10:08.099907</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487707</t>
+          <t>2026-03-12T04:10:08.099910</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487709</t>
+          <t>2026-03-12T04:10:08.099912</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487712</t>
+          <t>2026-03-12T04:10:08.099915</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487715</t>
+          <t>2026-03-12T04:10:08.099918</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487718</t>
+          <t>2026-03-12T04:10:08.099921</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487720</t>
+          <t>2026-03-12T04:10:08.099923</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487723</t>
+          <t>2026-03-12T04:10:08.099926</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487726</t>
+          <t>2026-03-12T04:10:08.099929</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487729</t>
+          <t>2026-03-12T04:10:08.099932</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487733</t>
+          <t>2026-03-12T04:10:08.099935</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487736</t>
+          <t>2026-03-12T04:10:08.099938</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487739</t>
+          <t>2026-03-12T04:10:08.099941</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487741</t>
+          <t>2026-03-12T04:10:08.099944</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487744</t>
+          <t>2026-03-12T04:10:08.099947</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487747</t>
+          <t>2026-03-12T04:10:08.099949</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487750</t>
+          <t>2026-03-12T04:10:08.099952</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487752</t>
+          <t>2026-03-12T04:10:08.099955</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487755</t>
+          <t>2026-03-12T04:10:08.099958</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487758</t>
+          <t>2026-03-12T04:10:08.099960</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487761</t>
+          <t>2026-03-12T04:10:08.099963</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487764</t>
+          <t>2026-03-12T04:10:08.099966</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487766</t>
+          <t>2026-03-12T04:10:08.099969</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487769</t>
+          <t>2026-03-12T04:10:08.099971</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487772</t>
+          <t>2026-03-12T04:10:08.099974</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487775</t>
+          <t>2026-03-12T04:10:08.099977</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487778</t>
+          <t>2026-03-12T04:10:08.099980</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487781</t>
+          <t>2026-03-12T04:10:08.099983</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099875</t>
+          <t>2026-03-13T04:08:49.903178</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099885</t>
+          <t>2026-03-13T04:08:49.903197</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099889</t>
+          <t>2026-03-13T04:08:49.903201</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099892</t>
+          <t>2026-03-13T04:08:49.903204</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099895</t>
+          <t>2026-03-13T04:08:49.903207</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099898</t>
+          <t>2026-03-13T04:08:49.903211</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099901</t>
+          <t>2026-03-13T04:08:49.903214</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099904</t>
+          <t>2026-03-13T04:08:49.903217</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099907</t>
+          <t>2026-03-13T04:08:49.903220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099910</t>
+          <t>2026-03-13T04:08:49.903223</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099912</t>
+          <t>2026-03-13T04:08:49.903226</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099915</t>
+          <t>2026-03-13T04:08:49.903228</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099918</t>
+          <t>2026-03-13T04:08:49.903231</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099921</t>
+          <t>2026-03-13T04:08:49.903234</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099923</t>
+          <t>2026-03-13T04:08:49.903237</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099926</t>
+          <t>2026-03-13T04:08:49.903241</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099929</t>
+          <t>2026-03-13T04:08:49.903244</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1403</v>
+        <v>1382</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099932</t>
+          <t>2026-03-13T04:08:49.903247</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099935</t>
+          <t>2026-03-13T04:08:49.903250</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099938</t>
+          <t>2026-03-13T04:08:49.903253</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099941</t>
+          <t>2026-03-13T04:08:49.903256</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099944</t>
+          <t>2026-03-13T04:08:49.903259</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099947</t>
+          <t>2026-03-13T04:08:49.903262</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099949</t>
+          <t>2026-03-13T04:08:49.903265</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099952</t>
+          <t>2026-03-13T04:08:49.903268</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1428</v>
+        <v>1452</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099955</t>
+          <t>2026-03-13T04:08:49.903271</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099958</t>
+          <t>2026-03-13T04:08:49.903274</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099960</t>
+          <t>2026-03-13T04:08:49.903277</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099963</t>
+          <t>2026-03-13T04:08:49.903280</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099966</t>
+          <t>2026-03-13T04:08:49.903283</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099969</t>
+          <t>2026-03-13T04:08:49.903285</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099971</t>
+          <t>2026-03-13T04:08:49.903289</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099974</t>
+          <t>2026-03-13T04:08:49.903292</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099977</t>
+          <t>2026-03-13T04:08:49.903295</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,72 +2754,267 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099980</t>
+          <t>2026-03-13T04:08:49.903317</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:49.903321</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>周生生</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1377.00</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:49.903324</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:49.903327</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>周大福</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>1380.00</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E40" t="n">
         <v>1380</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>涨</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-03-12T04:10:08.099983</t>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:49.903330</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903178</t>
+          <t>2026-03-14T04:07:13.062721</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903197</t>
+          <t>2026-03-14T04:07:13.062735</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903201</t>
+          <t>2026-03-14T04:07:13.062739</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903204</t>
+          <t>2026-03-14T04:07:13.062742</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903207</t>
+          <t>2026-03-14T04:07:13.062744</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903211</t>
+          <t>2026-03-14T04:07:13.062764</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903214</t>
+          <t>2026-03-14T04:07:13.062767</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903217</t>
+          <t>2026-03-14T04:07:13.062778</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903220</t>
+          <t>2026-03-14T04:07:13.062781</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903223</t>
+          <t>2026-03-14T04:07:13.062784</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903226</t>
+          <t>2026-03-14T04:07:13.062787</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903228</t>
+          <t>2026-03-14T04:07:13.062790</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903231</t>
+          <t>2026-03-14T04:07:13.062792</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903234</t>
+          <t>2026-03-14T04:07:13.062795</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903237</t>
+          <t>2026-03-14T04:07:13.062798</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903241</t>
+          <t>2026-03-14T04:07:13.062800</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903244</t>
+          <t>2026-03-14T04:07:13.062803</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903247</t>
+          <t>2026-03-14T04:07:13.062807</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903250</t>
+          <t>2026-03-14T04:07:13.062810</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903253</t>
+          <t>2026-03-14T04:07:13.062813</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903256</t>
+          <t>2026-03-14T04:07:13.062816</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903259</t>
+          <t>2026-03-14T04:07:13.062818</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903262</t>
+          <t>2026-03-14T04:07:13.062821</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903265</t>
+          <t>2026-03-14T04:07:13.062824</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903268</t>
+          <t>2026-03-14T04:07:13.062828</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903271</t>
+          <t>2026-03-14T04:07:13.062832</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903274</t>
+          <t>2026-03-14T04:07:13.062835</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903277</t>
+          <t>2026-03-14T04:07:13.062839</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903280</t>
+          <t>2026-03-14T04:07:13.062842</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903283</t>
+          <t>2026-03-14T04:07:13.062844</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903285</t>
+          <t>2026-03-14T04:07:13.062847</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903289</t>
+          <t>2026-03-14T04:07:13.062850</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903292</t>
+          <t>2026-03-14T04:07:13.062853</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903295</t>
+          <t>2026-03-14T04:07:13.062856</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903317</t>
+          <t>2026-03-14T04:07:13.062859</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903321</t>
+          <t>2026-03-14T04:07:13.062862</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903324</t>
+          <t>2026-03-14T04:07:13.062864</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903327</t>
+          <t>2026-03-14T04:07:13.062868</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903330</t>
+          <t>2026-03-14T04:07:13.062871</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062721</t>
+          <t>2026-03-15T04:29:49.276985</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062735</t>
+          <t>2026-03-15T04:29:49.277000</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062739</t>
+          <t>2026-03-15T04:29:49.277004</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062742</t>
+          <t>2026-03-15T04:29:49.277007</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062744</t>
+          <t>2026-03-15T04:29:49.277010</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062764</t>
+          <t>2026-03-15T04:29:49.277022</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062767</t>
+          <t>2026-03-15T04:29:49.277025</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062778</t>
+          <t>2026-03-15T04:29:49.277028</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062781</t>
+          <t>2026-03-15T04:29:49.277031</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062784</t>
+          <t>2026-03-15T04:29:49.277034</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062787</t>
+          <t>2026-03-15T04:29:49.277037</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062790</t>
+          <t>2026-03-15T04:29:49.277040</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062792</t>
+          <t>2026-03-15T04:29:49.277043</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062795</t>
+          <t>2026-03-15T04:29:49.277045</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062798</t>
+          <t>2026-03-15T04:29:49.277048</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062800</t>
+          <t>2026-03-15T04:29:49.277052</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062803</t>
+          <t>2026-03-15T04:29:49.277054</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062807</t>
+          <t>2026-03-15T04:29:49.277057</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062810</t>
+          <t>2026-03-15T04:29:49.277060</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062813</t>
+          <t>2026-03-15T04:29:49.277063</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062816</t>
+          <t>2026-03-15T04:29:49.277066</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062818</t>
+          <t>2026-03-15T04:29:49.277069</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062821</t>
+          <t>2026-03-15T04:29:49.277072</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062824</t>
+          <t>2026-03-15T04:29:49.277075</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062828</t>
+          <t>2026-03-15T04:29:49.277078</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062832</t>
+          <t>2026-03-15T04:29:49.277081</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062835</t>
+          <t>2026-03-15T04:29:49.277084</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062839</t>
+          <t>2026-03-15T04:29:49.277087</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062842</t>
+          <t>2026-03-15T04:29:49.277090</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062844</t>
+          <t>2026-03-15T04:29:49.277093</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062847</t>
+          <t>2026-03-15T04:29:49.277095</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062850</t>
+          <t>2026-03-15T04:29:49.277099</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062853</t>
+          <t>2026-03-15T04:29:49.277102</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062856</t>
+          <t>2026-03-15T04:29:49.277105</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062859</t>
+          <t>2026-03-15T04:29:49.277108</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062862</t>
+          <t>2026-03-15T04:29:49.277111</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062864</t>
+          <t>2026-03-15T04:29:49.277113</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062868</t>
+          <t>2026-03-15T04:29:49.277116</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062871</t>
+          <t>2026-03-15T04:29:49.277119</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1383</v>
+        <v>1360</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.276985</t>
+          <t>2026-03-16T04:36:50.724674</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277000</t>
+          <t>2026-03-16T04:36:50.724688</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277004</t>
+          <t>2026-03-16T04:36:50.724693</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277007</t>
+          <t>2026-03-16T04:36:50.724698</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277010</t>
+          <t>2026-03-16T04:36:50.724701</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277022</t>
+          <t>2026-03-16T04:36:50.724704</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277025</t>
+          <t>2026-03-16T04:36:50.724707</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277028</t>
+          <t>2026-03-16T04:36:50.724709</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277031</t>
+          <t>2026-03-16T04:36:50.724712</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277034</t>
+          <t>2026-03-16T04:36:50.724715</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277037</t>
+          <t>2026-03-16T04:36:50.724718</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277040</t>
+          <t>2026-03-16T04:36:50.724720</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277043</t>
+          <t>2026-03-16T04:36:50.724723</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277045</t>
+          <t>2026-03-16T04:36:50.724726</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277048</t>
+          <t>2026-03-16T04:36:50.724729</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277052</t>
+          <t>2026-03-16T04:36:50.724731</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277054</t>
+          <t>2026-03-16T04:36:50.724734</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277057</t>
+          <t>2026-03-16T04:36:50.724737</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277060</t>
+          <t>2026-03-16T04:36:50.724740</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277063</t>
+          <t>2026-03-16T04:36:50.724743</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277066</t>
+          <t>2026-03-16T04:36:50.724746</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277069</t>
+          <t>2026-03-16T04:36:50.724748</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277072</t>
+          <t>2026-03-16T04:36:50.724751</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277075</t>
+          <t>2026-03-16T04:36:50.724754</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277078</t>
+          <t>2026-03-16T04:36:50.724757</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277081</t>
+          <t>2026-03-16T04:36:50.724760</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277084</t>
+          <t>2026-03-16T04:36:50.724762</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277087</t>
+          <t>2026-03-16T04:36:50.724765</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277090</t>
+          <t>2026-03-16T04:36:50.724768</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277093</t>
+          <t>2026-03-16T04:36:50.724771</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277095</t>
+          <t>2026-03-16T04:36:50.724774</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277099</t>
+          <t>2026-03-16T04:36:50.724777</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277102</t>
+          <t>2026-03-16T04:36:50.724779</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277105</t>
+          <t>2026-03-16T04:36:50.724782</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277108</t>
+          <t>2026-03-16T04:36:50.724785</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277111</t>
+          <t>2026-03-16T04:36:50.724788</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277113</t>
+          <t>2026-03-16T04:36:50.724791</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277116</t>
+          <t>2026-03-16T04:36:50.724793</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3014,7 +3014,202 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277119</t>
+          <t>2026-03-16T04:36:50.724796</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-03-16T04:36:50.724799</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1380.00</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-03-16T04:36:50.724801</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>周生生</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1377.00</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-03-16T04:36:50.724804</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724674</t>
+          <t>2026-03-17T04:14:34.479171</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724688</t>
+          <t>2026-03-17T04:14:34.479184</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724693</t>
+          <t>2026-03-17T04:14:34.479188</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724698</t>
+          <t>2026-03-17T04:14:34.479192</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724701</t>
+          <t>2026-03-17T04:14:34.479195</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724704</t>
+          <t>2026-03-17T04:14:34.479198</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724707</t>
+          <t>2026-03-17T04:14:34.479201</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724709</t>
+          <t>2026-03-17T04:14:34.479204</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724712</t>
+          <t>2026-03-17T04:14:34.479207</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724715</t>
+          <t>2026-03-17T04:14:34.479210</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724718</t>
+          <t>2026-03-17T04:14:34.479213</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1399</v>
+        <v>1390</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724720</t>
+          <t>2026-03-17T04:14:34.479215</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1390</v>
+        <v>1404</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724723</t>
+          <t>2026-03-17T04:14:34.479218</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724726</t>
+          <t>2026-03-17T04:14:34.479221</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724729</t>
+          <t>2026-03-17T04:14:34.479224</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724731</t>
+          <t>2026-03-17T04:14:34.479227</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724734</t>
+          <t>2026-03-17T04:14:34.479230</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724737</t>
+          <t>2026-03-17T04:14:34.479232</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724740</t>
+          <t>2026-03-17T04:14:34.479235</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724743</t>
+          <t>2026-03-17T04:14:34.479238</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1385</v>
+        <v>1371</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724746</t>
+          <t>2026-03-17T04:14:34.479241</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724748</t>
+          <t>2026-03-17T04:14:34.479244</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724751</t>
+          <t>2026-03-17T04:14:34.479247</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724754</t>
+          <t>2026-03-17T04:14:34.479251</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724757</t>
+          <t>2026-03-17T04:14:34.479261</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724760</t>
+          <t>2026-03-17T04:14:34.479267</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724762</t>
+          <t>2026-03-17T04:14:34.479273</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1452</v>
+        <v>1400</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724765</t>
+          <t>2026-03-17T04:14:34.479279</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724768</t>
+          <t>2026-03-17T04:14:34.479286</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724771</t>
+          <t>2026-03-17T04:14:34.479292</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724774</t>
+          <t>2026-03-17T04:14:34.479298</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724777</t>
+          <t>2026-03-17T04:14:34.479303</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724779</t>
+          <t>2026-03-17T04:14:34.479309</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724782</t>
+          <t>2026-03-17T04:14:34.479316</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1380</v>
+        <v>1433</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724785</t>
+          <t>2026-03-17T04:14:34.479323</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1384</v>
+        <v>1428</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724788</t>
+          <t>2026-03-17T04:14:34.479330</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724791</t>
+          <t>2026-03-17T04:14:34.479335</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724793</t>
+          <t>2026-03-17T04:14:34.479338</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724796</t>
+          <t>2026-03-17T04:14:34.479341</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724799</t>
+          <t>2026-03-17T04:14:34.479344</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,72 +3144,267 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724801</t>
+          <t>2026-03-17T04:14:34.479347</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:34.479350</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>周生生</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>1377.00</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E44" t="n">
         <v>1377</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>跌</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-03-16T04:36:50.724804</t>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:34.479353</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:34.479356</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1380.00</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:34.479359</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479171</t>
+          <t>2026-03-18T04:22:04.296379</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479184</t>
+          <t>2026-03-18T04:22:04.296393</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479188</t>
+          <t>2026-03-18T04:22:04.296397</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479192</t>
+          <t>2026-03-18T04:22:04.296400</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479195</t>
+          <t>2026-03-18T04:22:04.296403</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479198</t>
+          <t>2026-03-18T04:22:04.296406</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479201</t>
+          <t>2026-03-18T04:22:04.296409</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479204</t>
+          <t>2026-03-18T04:22:04.296411</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1383</v>
+        <v>1360</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479207</t>
+          <t>2026-03-18T04:22:04.296414</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479210</t>
+          <t>2026-03-18T04:22:04.296423</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479213</t>
+          <t>2026-03-18T04:22:04.296430</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479215</t>
+          <t>2026-03-18T04:22:04.296437</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479218</t>
+          <t>2026-03-18T04:22:04.296443</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479221</t>
+          <t>2026-03-18T04:22:04.296449</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479224</t>
+          <t>2026-03-18T04:22:04.296454</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1390</v>
+        <v>1404</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479227</t>
+          <t>2026-03-18T04:22:04.296459</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479230</t>
+          <t>2026-03-18T04:22:04.296465</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479232</t>
+          <t>2026-03-18T04:22:04.296472</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479235</t>
+          <t>2026-03-18T04:22:04.296478</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1376</v>
+        <v>1390</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479238</t>
+          <t>2026-03-18T04:22:04.296481</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479241</t>
+          <t>2026-03-18T04:22:04.296483</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479244</t>
+          <t>2026-03-18T04:22:04.296486</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479247</t>
+          <t>2026-03-18T04:22:04.296490</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479251</t>
+          <t>2026-03-18T04:22:04.296492</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479261</t>
+          <t>2026-03-18T04:22:04.296495</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479267</t>
+          <t>2026-03-18T04:22:04.296498</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479273</t>
+          <t>2026-03-18T04:22:04.296501</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479279</t>
+          <t>2026-03-18T04:22:04.296504</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479286</t>
+          <t>2026-03-18T04:22:04.296507</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479292</t>
+          <t>2026-03-18T04:22:04.296527</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1452</v>
+        <v>1400</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479298</t>
+          <t>2026-03-18T04:22:04.296531</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479303</t>
+          <t>2026-03-18T04:22:04.296533</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479309</t>
+          <t>2026-03-18T04:22:04.296536</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479316</t>
+          <t>2026-03-18T04:22:04.296539</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479323</t>
+          <t>2026-03-18T04:22:04.296542</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479330</t>
+          <t>2026-03-18T04:22:04.296545</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479335</t>
+          <t>2026-03-18T04:22:04.296548</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1386</v>
+        <v>1428</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479338</t>
+          <t>2026-03-18T04:22:04.296551</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1380</v>
+        <v>1429</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479341</t>
+          <t>2026-03-18T04:22:04.296554</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479344</t>
+          <t>2026-03-18T04:22:04.296557</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479347</t>
+          <t>2026-03-18T04:22:04.296560</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479350</t>
+          <t>2026-03-18T04:22:04.296563</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479353</t>
+          <t>2026-03-18T04:22:04.296566</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,72 +3339,267 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479356</t>
+          <t>2026-03-18T04:22:04.296569</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:04.296571</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>周大福</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>1380.00</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E47" t="n">
         <v>1380</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>涨</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-03-17T04:14:34.479359</t>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:04.296574</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:04.296577</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>周生生</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1377.00</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:04.296580</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1358</v>
+        <v>1316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296379</t>
+          <t>2026-03-19T04:21:09.314166</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296393</t>
+          <t>2026-03-19T04:21:09.314181</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1359</v>
+        <v>1310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296397</t>
+          <t>2026-03-19T04:21:09.314185</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296400</t>
+          <t>2026-03-19T04:21:09.314188</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296403</t>
+          <t>2026-03-19T04:21:09.314192</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296406</t>
+          <t>2026-03-19T04:21:09.314195</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296409</t>
+          <t>2026-03-19T04:21:09.314198</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296411</t>
+          <t>2026-03-19T04:21:09.314201</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296414</t>
+          <t>2026-03-19T04:21:09.314204</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296423</t>
+          <t>2026-03-19T04:21:09.314207</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296430</t>
+          <t>2026-03-19T04:21:09.314210</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296437</t>
+          <t>2026-03-19T04:21:09.314213</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296443</t>
+          <t>2026-03-19T04:21:09.314216</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296449</t>
+          <t>2026-03-19T04:21:09.314221</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296454</t>
+          <t>2026-03-19T04:21:09.314227</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1404</v>
+        <v>1390</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296459</t>
+          <t>2026-03-19T04:21:09.314232</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296465</t>
+          <t>2026-03-19T04:21:09.314238</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296472</t>
+          <t>2026-03-19T04:21:09.314244</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296478</t>
+          <t>2026-03-19T04:21:09.314250</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1390</v>
+        <v>1399</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296481</t>
+          <t>2026-03-19T04:21:09.314257</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296483</t>
+          <t>2026-03-19T04:21:09.314262</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296486</t>
+          <t>2026-03-19T04:21:09.314265</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296490</t>
+          <t>2026-03-19T04:21:09.314269</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296492</t>
+          <t>2026-03-19T04:21:09.314272</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1385</v>
+        <v>1376</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296495</t>
+          <t>2026-03-19T04:21:09.314275</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1383</v>
+        <v>1371</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296498</t>
+          <t>2026-03-19T04:21:09.314278</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296501</t>
+          <t>2026-03-19T04:21:09.314281</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296504</t>
+          <t>2026-03-19T04:21:09.314285</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296507</t>
+          <t>2026-03-19T04:21:09.314288</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296527</t>
+          <t>2026-03-19T04:21:09.314291</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296531</t>
+          <t>2026-03-19T04:21:09.314294</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296533</t>
+          <t>2026-03-19T04:21:09.314297</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296536</t>
+          <t>2026-03-19T04:21:09.314300</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296539</t>
+          <t>2026-03-19T04:21:09.314303</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296542</t>
+          <t>2026-03-19T04:21:09.314306</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296545</t>
+          <t>2026-03-19T04:21:09.314309</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296548</t>
+          <t>2026-03-19T04:21:09.314312</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296551</t>
+          <t>2026-03-19T04:21:09.314316</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296554</t>
+          <t>2026-03-19T04:21:09.314319</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296557</t>
+          <t>2026-03-19T04:21:09.314322</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296560</t>
+          <t>2026-03-19T04:21:09.314325</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296563</t>
+          <t>2026-03-19T04:21:09.314329</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296566</t>
+          <t>2026-03-19T04:21:09.314332</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296569</t>
+          <t>2026-03-19T04:21:09.314335</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296571</t>
+          <t>2026-03-19T04:21:09.314338</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296574</t>
+          <t>2026-03-19T04:21:09.314341</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,72 +3534,202 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296577</t>
+          <t>2026-03-19T04:21:09.314344</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:21:09.314355</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>周生生</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>1377.00</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E50" t="n">
         <v>1377</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>跌</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-03-18T04:22:04.296580</t>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:21:09.314358</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:21:09.314361</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1316</v>
+        <v>1268</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314166</t>
+          <t>2026-03-20T04:10:46.395178</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1318</v>
+        <v>1267</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314181</t>
+          <t>2026-03-20T04:10:46.395191</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1310</v>
+        <v>1269</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314185</t>
+          <t>2026-03-20T04:10:46.395195</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1359</v>
+        <v>1310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314188</t>
+          <t>2026-03-20T04:10:46.395198</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1361</v>
+        <v>1316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314192</t>
+          <t>2026-03-20T04:10:46.395201</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314195</t>
+          <t>2026-03-20T04:10:46.395204</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314198</t>
+          <t>2026-03-20T04:10:46.395207</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314201</t>
+          <t>2026-03-20T04:10:46.395210</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314204</t>
+          <t>2026-03-20T04:10:46.395213</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314207</t>
+          <t>2026-03-20T04:10:46.395216</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314210</t>
+          <t>2026-03-20T04:10:46.395219</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314213</t>
+          <t>2026-03-20T04:10:46.395222</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314216</t>
+          <t>2026-03-20T04:10:46.395224</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314221</t>
+          <t>2026-03-20T04:10:46.395227</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314227</t>
+          <t>2026-03-20T04:10:46.395230</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1390</v>
+        <v>1380</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314232</t>
+          <t>2026-03-20T04:10:46.395233</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314238</t>
+          <t>2026-03-20T04:10:46.395236</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314244</t>
+          <t>2026-03-20T04:10:46.395239</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1404</v>
+        <v>1390</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314250</t>
+          <t>2026-03-20T04:10:46.395242</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314257</t>
+          <t>2026-03-20T04:10:46.395245</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314262</t>
+          <t>2026-03-20T04:10:46.395248</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314265</t>
+          <t>2026-03-20T04:10:46.395251</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314269</t>
+          <t>2026-03-20T04:10:46.395254</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314272</t>
+          <t>2026-03-20T04:10:46.395257</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314275</t>
+          <t>2026-03-20T04:10:46.395259</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314278</t>
+          <t>2026-03-20T04:10:46.395263</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314281</t>
+          <t>2026-03-20T04:10:46.395265</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314285</t>
+          <t>2026-03-20T04:10:46.395268</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314288</t>
+          <t>2026-03-20T04:10:46.395271</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314291</t>
+          <t>2026-03-20T04:10:46.395274</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314294</t>
+          <t>2026-03-20T04:10:46.395276</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314297</t>
+          <t>2026-03-20T04:10:46.395279</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314300</t>
+          <t>2026-03-20T04:10:46.395282</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314303</t>
+          <t>2026-03-20T04:10:46.395284</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314306</t>
+          <t>2026-03-20T04:10:46.395287</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314309</t>
+          <t>2026-03-20T04:10:46.395290</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314312</t>
+          <t>2026-03-20T04:10:46.395293</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314316</t>
+          <t>2026-03-20T04:10:46.395296</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314319</t>
+          <t>2026-03-20T04:10:46.395299</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314322</t>
+          <t>2026-03-20T04:10:46.395302</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314325</t>
+          <t>2026-03-20T04:10:46.395304</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314329</t>
+          <t>2026-03-20T04:10:46.395307</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314332</t>
+          <t>2026-03-20T04:10:46.395310</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1380</v>
+        <v>1429</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314335</t>
+          <t>2026-03-20T04:10:46.395313</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1384</v>
+        <v>1428</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314338</t>
+          <t>2026-03-20T04:10:46.395315</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314341</t>
+          <t>2026-03-20T04:10:46.395318</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314344</t>
+          <t>2026-03-20T04:10:46.395321</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314355</t>
+          <t>2026-03-20T04:10:46.395324</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314358</t>
+          <t>2026-03-20T04:10:46.395335</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314361</t>
+          <t>2026-03-20T04:10:46.395338</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395178</t>
+          <t>2026-03-21T04:02:02.219418</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395191</t>
+          <t>2026-03-21T04:02:02.219439</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395195</t>
+          <t>2026-03-21T04:02:02.219445</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395198</t>
+          <t>2026-03-21T04:02:02.219452</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395201</t>
+          <t>2026-03-21T04:02:02.219473</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395204</t>
+          <t>2026-03-21T04:02:02.219477</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395207</t>
+          <t>2026-03-21T04:02:02.219480</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395210</t>
+          <t>2026-03-21T04:02:02.219483</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395213</t>
+          <t>2026-03-21T04:02:02.219486</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395216</t>
+          <t>2026-03-21T04:02:02.219489</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395219</t>
+          <t>2026-03-21T04:02:02.219492</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395222</t>
+          <t>2026-03-21T04:02:02.219495</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395224</t>
+          <t>2026-03-21T04:02:02.219498</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395227</t>
+          <t>2026-03-21T04:02:02.219501</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395230</t>
+          <t>2026-03-21T04:02:02.219504</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395233</t>
+          <t>2026-03-21T04:02:02.219507</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395236</t>
+          <t>2026-03-21T04:02:02.219510</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395239</t>
+          <t>2026-03-21T04:02:02.219513</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395242</t>
+          <t>2026-03-21T04:02:02.219516</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395245</t>
+          <t>2026-03-21T04:02:02.219519</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395248</t>
+          <t>2026-03-21T04:02:02.219522</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395251</t>
+          <t>2026-03-21T04:02:02.219525</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395254</t>
+          <t>2026-03-21T04:02:02.219528</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395257</t>
+          <t>2026-03-21T04:02:02.219531</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395259</t>
+          <t>2026-03-21T04:02:02.219534</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395263</t>
+          <t>2026-03-21T04:02:02.219537</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395265</t>
+          <t>2026-03-21T04:02:02.219540</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395268</t>
+          <t>2026-03-21T04:02:02.219543</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395271</t>
+          <t>2026-03-21T04:02:02.219546</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395274</t>
+          <t>2026-03-21T04:02:02.219549</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395276</t>
+          <t>2026-03-21T04:02:02.219552</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395279</t>
+          <t>2026-03-21T04:02:02.219554</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395282</t>
+          <t>2026-03-21T04:02:02.219557</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395284</t>
+          <t>2026-03-21T04:02:02.219560</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395287</t>
+          <t>2026-03-21T04:02:02.219563</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395290</t>
+          <t>2026-03-21T04:02:02.219566</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395293</t>
+          <t>2026-03-21T04:02:02.219569</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395296</t>
+          <t>2026-03-21T04:02:02.219574</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395299</t>
+          <t>2026-03-21T04:02:02.219578</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395302</t>
+          <t>2026-03-21T04:02:02.219581</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395304</t>
+          <t>2026-03-21T04:02:02.219585</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395307</t>
+          <t>2026-03-21T04:02:02.219588</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395310</t>
+          <t>2026-03-21T04:02:02.219590</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395313</t>
+          <t>2026-03-21T04:02:02.219593</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395315</t>
+          <t>2026-03-21T04:02:02.219596</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395318</t>
+          <t>2026-03-21T04:02:02.219599</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395321</t>
+          <t>2026-03-21T04:02:02.219602</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395324</t>
+          <t>2026-03-21T04:02:02.219605</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395335</t>
+          <t>2026-03-21T04:02:02.219608</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395338</t>
+          <t>2026-03-21T04:02:02.219611</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219418</t>
+          <t>2026-03-22T04:16:39.784371</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219439</t>
+          <t>2026-03-22T04:16:39.784384</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219445</t>
+          <t>2026-03-22T04:16:39.784387</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219452</t>
+          <t>2026-03-22T04:16:39.784391</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219473</t>
+          <t>2026-03-22T04:16:39.784394</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219477</t>
+          <t>2026-03-22T04:16:39.784397</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219480</t>
+          <t>2026-03-22T04:16:39.784400</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219483</t>
+          <t>2026-03-22T04:16:39.784403</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219486</t>
+          <t>2026-03-22T04:16:39.784406</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219489</t>
+          <t>2026-03-22T04:16:39.784409</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219492</t>
+          <t>2026-03-22T04:16:39.784412</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219495</t>
+          <t>2026-03-22T04:16:39.784415</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219498</t>
+          <t>2026-03-22T04:16:39.784417</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219501</t>
+          <t>2026-03-22T04:16:39.784420</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219504</t>
+          <t>2026-03-22T04:16:39.784423</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219507</t>
+          <t>2026-03-22T04:16:39.784426</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219510</t>
+          <t>2026-03-22T04:16:39.784429</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219513</t>
+          <t>2026-03-22T04:16:39.784432</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219516</t>
+          <t>2026-03-22T04:16:39.784435</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219519</t>
+          <t>2026-03-22T04:16:39.784438</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219522</t>
+          <t>2026-03-22T04:16:39.784441</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219525</t>
+          <t>2026-03-22T04:16:39.784444</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219528</t>
+          <t>2026-03-22T04:16:39.784447</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219531</t>
+          <t>2026-03-22T04:16:39.784449</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219534</t>
+          <t>2026-03-22T04:16:39.784452</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219537</t>
+          <t>2026-03-22T04:16:39.784455</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219540</t>
+          <t>2026-03-22T04:16:39.784458</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219543</t>
+          <t>2026-03-22T04:16:39.784461</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219546</t>
+          <t>2026-03-22T04:16:39.784464</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219549</t>
+          <t>2026-03-22T04:16:39.784467</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219552</t>
+          <t>2026-03-22T04:16:39.784469</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219554</t>
+          <t>2026-03-22T04:16:39.784472</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219557</t>
+          <t>2026-03-22T04:16:39.784475</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219560</t>
+          <t>2026-03-22T04:16:39.784478</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219563</t>
+          <t>2026-03-22T04:16:39.784486</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219566</t>
+          <t>2026-03-22T04:16:39.784489</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219569</t>
+          <t>2026-03-22T04:16:39.784492</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219574</t>
+          <t>2026-03-22T04:16:39.784495</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219578</t>
+          <t>2026-03-22T04:16:39.784498</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219581</t>
+          <t>2026-03-22T04:16:39.784501</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219585</t>
+          <t>2026-03-22T04:16:39.784504</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219588</t>
+          <t>2026-03-22T04:16:39.784507</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219590</t>
+          <t>2026-03-22T04:16:39.784509</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219593</t>
+          <t>2026-03-22T04:16:39.784512</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219596</t>
+          <t>2026-03-22T04:16:39.784515</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219599</t>
+          <t>2026-03-22T04:16:39.784518</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219602</t>
+          <t>2026-03-22T04:16:39.784521</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219605</t>
+          <t>2026-03-22T04:16:39.784524</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219608</t>
+          <t>2026-03-22T04:16:39.784527</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219611</t>
+          <t>2026-03-22T04:16:39.784529</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1268</v>
+        <v>1206</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784371</t>
+          <t>2026-03-23T04:26:09.020068</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784384</t>
+          <t>2026-03-23T04:26:09.020088</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1269</v>
+        <v>1200</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784387</t>
+          <t>2026-03-23T04:26:09.020095</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784391</t>
+          <t>2026-03-23T04:26:09.020100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1316</v>
+        <v>1269</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784394</t>
+          <t>2026-03-23T04:26:09.020106</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1318</v>
+        <v>1267</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784397</t>
+          <t>2026-03-23T04:26:09.020113</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1361</v>
+        <v>1310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784400</t>
+          <t>2026-03-23T04:26:09.020120</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784403</t>
+          <t>2026-03-23T04:26:09.020123</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784406</t>
+          <t>2026-03-23T04:26:09.020125</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784409</t>
+          <t>2026-03-23T04:26:09.020128</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784412</t>
+          <t>2026-03-23T04:26:09.020131</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784415</t>
+          <t>2026-03-23T04:26:09.020134</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784417</t>
+          <t>2026-03-23T04:26:09.020137</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784420</t>
+          <t>2026-03-23T04:26:09.020140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784423</t>
+          <t>2026-03-23T04:26:09.020143</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784426</t>
+          <t>2026-03-23T04:26:09.020146</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1385</v>
+        <v>1360</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784429</t>
+          <t>2026-03-23T04:26:09.020148</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784432</t>
+          <t>2026-03-23T04:26:09.020151</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1390</v>
+        <v>1380</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784435</t>
+          <t>2026-03-23T04:26:09.020154</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784438</t>
+          <t>2026-03-23T04:26:09.020157</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784441</t>
+          <t>2026-03-23T04:26:09.020160</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784444</t>
+          <t>2026-03-23T04:26:09.020164</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784447</t>
+          <t>2026-03-23T04:26:09.020167</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784449</t>
+          <t>2026-03-23T04:26:09.020169</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784452</t>
+          <t>2026-03-23T04:26:09.020172</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784455</t>
+          <t>2026-03-23T04:26:09.020175</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784458</t>
+          <t>2026-03-23T04:26:09.020178</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784461</t>
+          <t>2026-03-23T04:26:09.020181</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784464</t>
+          <t>2026-03-23T04:26:09.020184</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784467</t>
+          <t>2026-03-23T04:26:09.020187</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1383</v>
+        <v>1371</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784469</t>
+          <t>2026-03-23T04:26:09.020190</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1385</v>
+        <v>1376</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784472</t>
+          <t>2026-03-23T04:26:09.020193</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784475</t>
+          <t>2026-03-23T04:26:09.020196</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1403</v>
+        <v>1382</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784478</t>
+          <t>2026-03-23T04:26:09.020198</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784486</t>
+          <t>2026-03-23T04:26:09.020201</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784489</t>
+          <t>2026-03-23T04:26:09.020204</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784492</t>
+          <t>2026-03-23T04:26:09.020207</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784495</t>
+          <t>2026-03-23T04:26:09.020210</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784498</t>
+          <t>2026-03-23T04:26:09.020213</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1452</v>
+        <v>1401</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784501</t>
+          <t>2026-03-23T04:26:09.020216</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784504</t>
+          <t>2026-03-23T04:26:09.020219</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784507</t>
+          <t>2026-03-23T04:26:09.020222</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784509</t>
+          <t>2026-03-23T04:26:09.020225</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784512</t>
+          <t>2026-03-23T04:26:09.020228</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784515</t>
+          <t>2026-03-23T04:26:09.020231</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1380</v>
+        <v>1429</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784518</t>
+          <t>2026-03-23T04:26:09.020233</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1386</v>
+        <v>1428</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784521</t>
+          <t>2026-03-23T04:26:09.020236</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784524</t>
+          <t>2026-03-23T04:26:09.020239</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784527</t>
+          <t>2026-03-23T04:26:09.020242</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784529</t>
+          <t>2026-03-23T04:26:09.020245</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020068</t>
+          <t>2026-03-24T04:15:03.140744</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>1185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020088</t>
+          <t>2026-03-24T04:15:03.140757</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1200</v>
+        <v>1178</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020095</t>
+          <t>2026-03-24T04:15:03.140761</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020100</t>
+          <t>2026-03-24T04:15:03.140764</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1269</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020106</t>
+          <t>2026-03-24T04:15:03.140767</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1267</v>
+        <v>1206</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020113</t>
+          <t>2026-03-24T04:15:03.140770</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1310</v>
+        <v>1267</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020120</t>
+          <t>2026-03-24T04:15:03.140773</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1316</v>
+        <v>1269</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020123</t>
+          <t>2026-03-24T04:15:03.140775</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1318</v>
+        <v>1268</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020125</t>
+          <t>2026-03-24T04:15:03.140778</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020128</t>
+          <t>2026-03-24T04:15:03.140781</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020131</t>
+          <t>2026-03-24T04:15:03.140784</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020134</t>
+          <t>2026-03-24T04:15:03.140786</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020137</t>
+          <t>2026-03-24T04:15:03.140789</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020140</t>
+          <t>2026-03-24T04:15:03.140792</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020143</t>
+          <t>2026-03-24T04:15:03.140795</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020146</t>
+          <t>2026-03-24T04:15:03.140797</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020148</t>
+          <t>2026-03-24T04:15:03.140800</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020151</t>
+          <t>2026-03-24T04:15:03.140803</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020154</t>
+          <t>2026-03-24T04:15:03.140806</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020157</t>
+          <t>2026-03-24T04:15:03.140809</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1385</v>
+        <v>1360</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020160</t>
+          <t>2026-03-24T04:15:03.140812</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020164</t>
+          <t>2026-03-24T04:15:03.140815</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020167</t>
+          <t>2026-03-24T04:15:03.140818</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020169</t>
+          <t>2026-03-24T04:15:03.140821</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020172</t>
+          <t>2026-03-24T04:15:03.140829</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020175</t>
+          <t>2026-03-24T04:15:03.140837</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1404</v>
+        <v>1390</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020178</t>
+          <t>2026-03-24T04:15:03.140843</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1390</v>
+        <v>1399</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020181</t>
+          <t>2026-03-24T04:15:03.140849</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020184</t>
+          <t>2026-03-24T04:15:03.140855</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020187</t>
+          <t>2026-03-24T04:15:03.140860</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020190</t>
+          <t>2026-03-24T04:15:03.140865</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020193</t>
+          <t>2026-03-24T04:15:03.140889</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020196</t>
+          <t>2026-03-24T04:15:03.140896</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020198</t>
+          <t>2026-03-24T04:15:03.140902</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020201</t>
+          <t>2026-03-24T04:15:03.140904</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1385</v>
+        <v>1371</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020204</t>
+          <t>2026-03-24T04:15:03.140907</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1403</v>
+        <v>1382</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020207</t>
+          <t>2026-03-24T04:15:03.140910</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020210</t>
+          <t>2026-03-24T04:15:03.140913</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020213</t>
+          <t>2026-03-24T04:15:03.140916</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020216</t>
+          <t>2026-03-24T04:15:03.140919</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020219</t>
+          <t>2026-03-24T04:15:03.140922</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020222</t>
+          <t>2026-03-24T04:15:03.140938</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020225</t>
+          <t>2026-03-24T04:15:03.140941</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1452</v>
+        <v>1401</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020228</t>
+          <t>2026-03-24T04:15:03.140944</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020231</t>
+          <t>2026-03-24T04:15:03.140946</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020233</t>
+          <t>2026-03-24T04:15:03.140949</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020236</t>
+          <t>2026-03-24T04:15:03.140952</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020239</t>
+          <t>2026-03-24T04:15:03.140955</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020242</t>
+          <t>2026-03-24T04:15:03.140958</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:09.020245</t>
+          <t>2026-03-24T04:15:03.140960</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1180</v>
+        <v>1237</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140744</t>
+          <t>2026-03-25T04:17:42.258368</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1185</v>
+        <v>1239</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140757</t>
+          <t>2026-03-25T04:17:42.258383</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1178</v>
+        <v>1246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140761</t>
+          <t>2026-03-25T04:17:42.258387</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140764</t>
+          <t>2026-03-25T04:17:42.258390</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140767</t>
+          <t>2026-03-25T04:17:42.258393</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140770</t>
+          <t>2026-03-25T04:17:42.258397</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1267</v>
+        <v>1200</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140773</t>
+          <t>2026-03-25T04:17:42.258400</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140775</t>
+          <t>2026-03-25T04:17:42.258402</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1268</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140778</t>
+          <t>2026-03-25T04:17:42.258405</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140781</t>
+          <t>2026-03-25T04:17:42.258408</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1310</v>
+        <v>1267</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140784</t>
+          <t>2026-03-25T04:17:42.258411</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1316</v>
+        <v>1268</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140786</t>
+          <t>2026-03-25T04:17:42.258414</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140789</t>
+          <t>2026-03-25T04:17:42.258443</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140792</t>
+          <t>2026-03-25T04:17:42.258452</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140795</t>
+          <t>2026-03-25T04:17:42.258459</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140797</t>
+          <t>2026-03-25T04:17:42.258465</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140800</t>
+          <t>2026-03-25T04:17:42.258470</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140803</t>
+          <t>2026-03-25T04:17:42.258475</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140806</t>
+          <t>2026-03-25T04:17:42.258482</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140809</t>
+          <t>2026-03-25T04:17:42.258488</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140812</t>
+          <t>2026-03-25T04:17:42.258495</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140815</t>
+          <t>2026-03-25T04:17:42.258498</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1383</v>
+        <v>1365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140818</t>
+          <t>2026-03-25T04:17:42.258501</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140821</t>
+          <t>2026-03-25T04:17:42.258504</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140829</t>
+          <t>2026-03-25T04:17:42.258506</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140837</t>
+          <t>2026-03-25T04:17:42.258509</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140843</t>
+          <t>2026-03-25T04:17:42.258512</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1399</v>
+        <v>1390</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140849</t>
+          <t>2026-03-25T04:17:42.258515</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140855</t>
+          <t>2026-03-25T04:17:42.258518</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140860</t>
+          <t>2026-03-25T04:17:42.258521</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140865</t>
+          <t>2026-03-25T04:17:42.258523</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140889</t>
+          <t>2026-03-25T04:17:42.258526</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1390</v>
+        <v>1404</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140896</t>
+          <t>2026-03-25T04:17:42.258529</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140902</t>
+          <t>2026-03-25T04:17:42.258532</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140904</t>
+          <t>2026-03-25T04:17:42.258535</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140907</t>
+          <t>2026-03-25T04:17:42.258538</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140910</t>
+          <t>2026-03-25T04:17:42.258540</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140913</t>
+          <t>2026-03-25T04:17:42.258544</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1385</v>
+        <v>1371</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140916</t>
+          <t>2026-03-25T04:17:42.258556</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140919</t>
+          <t>2026-03-25T04:17:42.258559</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140922</t>
+          <t>2026-03-25T04:17:42.258562</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140938</t>
+          <t>2026-03-25T04:17:42.258565</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140941</t>
+          <t>2026-03-25T04:17:42.258567</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140944</t>
+          <t>2026-03-25T04:17:42.258570</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140946</t>
+          <t>2026-03-25T04:17:42.258573</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1452</v>
+        <v>1401</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140949</t>
+          <t>2026-03-25T04:17:42.258576</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140952</t>
+          <t>2026-03-25T04:17:42.258579</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140955</t>
+          <t>2026-03-25T04:17:42.258582</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140958</t>
+          <t>2026-03-25T04:17:42.258584</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:03.140960</t>
+          <t>2026-03-25T04:17:42.258587</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258368</t>
+          <t>2026-03-26T04:30:36.348598</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258383</t>
+          <t>2026-03-26T04:30:36.348612</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258387</t>
+          <t>2026-03-26T04:30:36.348615</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258390</t>
+          <t>2026-03-26T04:30:36.348618</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258393</t>
+          <t>2026-03-26T04:30:36.348621</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258397</t>
+          <t>2026-03-26T04:30:36.348624</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258400</t>
+          <t>2026-03-26T04:30:36.348627</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258402</t>
+          <t>2026-03-26T04:30:36.348630</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258405</t>
+          <t>2026-03-26T04:30:36.348633</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258408</t>
+          <t>2026-03-26T04:30:36.348636</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258411</t>
+          <t>2026-03-26T04:30:36.348639</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258414</t>
+          <t>2026-03-26T04:30:36.348642</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258443</t>
+          <t>2026-03-26T04:30:36.348644</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258452</t>
+          <t>2026-03-26T04:30:36.348647</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258459</t>
+          <t>2026-03-26T04:30:36.348650</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258465</t>
+          <t>2026-03-26T04:30:36.348653</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258470</t>
+          <t>2026-03-26T04:30:36.348655</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258475</t>
+          <t>2026-03-26T04:30:36.348659</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258482</t>
+          <t>2026-03-26T04:30:36.348662</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258488</t>
+          <t>2026-03-26T04:30:36.348664</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258495</t>
+          <t>2026-03-26T04:30:36.348667</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258498</t>
+          <t>2026-03-26T04:30:36.348670</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258501</t>
+          <t>2026-03-26T04:30:36.348673</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258504</t>
+          <t>2026-03-26T04:30:36.348676</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258506</t>
+          <t>2026-03-26T04:30:36.348679</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258509</t>
+          <t>2026-03-26T04:30:36.348682</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258512</t>
+          <t>2026-03-26T04:30:36.348685</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258515</t>
+          <t>2026-03-26T04:30:36.348688</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258518</t>
+          <t>2026-03-26T04:30:36.348691</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258521</t>
+          <t>2026-03-26T04:30:36.348694</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258523</t>
+          <t>2026-03-26T04:30:36.348697</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258526</t>
+          <t>2026-03-26T04:30:36.348699</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258529</t>
+          <t>2026-03-26T04:30:36.348702</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258532</t>
+          <t>2026-03-26T04:30:36.348705</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258535</t>
+          <t>2026-03-26T04:30:36.348717</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258538</t>
+          <t>2026-03-26T04:30:36.348720</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258540</t>
+          <t>2026-03-26T04:30:36.348722</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258544</t>
+          <t>2026-03-26T04:30:36.348726</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258556</t>
+          <t>2026-03-26T04:30:36.348729</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258559</t>
+          <t>2026-03-26T04:30:36.348732</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258562</t>
+          <t>2026-03-26T04:30:36.348734</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258565</t>
+          <t>2026-03-26T04:30:36.348737</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258567</t>
+          <t>2026-03-26T04:30:36.348740</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258570</t>
+          <t>2026-03-26T04:30:36.348743</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258573</t>
+          <t>2026-03-26T04:30:36.348746</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258576</t>
+          <t>2026-03-26T04:30:36.348748</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258579</t>
+          <t>2026-03-26T04:30:36.348751</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258582</t>
+          <t>2026-03-26T04:30:36.348754</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258584</t>
+          <t>2026-03-26T04:30:36.348757</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:42.258587</t>
+          <t>2026-03-26T04:30:36.348760</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348598</t>
+          <t>2026-03-27T04:31:24.970229</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348612</t>
+          <t>2026-03-27T04:31:24.970242</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348615</t>
+          <t>2026-03-27T04:31:24.970246</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348618</t>
+          <t>2026-03-27T04:31:24.970249</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348621</t>
+          <t>2026-03-27T04:31:24.970252</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348624</t>
+          <t>2026-03-27T04:31:24.970255</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348627</t>
+          <t>2026-03-27T04:31:24.970258</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348630</t>
+          <t>2026-03-27T04:31:24.970260</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348633</t>
+          <t>2026-03-27T04:31:24.970291</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348636</t>
+          <t>2026-03-27T04:31:24.970299</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348639</t>
+          <t>2026-03-27T04:31:24.970305</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348642</t>
+          <t>2026-03-27T04:31:24.970311</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348644</t>
+          <t>2026-03-27T04:31:24.970317</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348647</t>
+          <t>2026-03-27T04:31:24.970324</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348650</t>
+          <t>2026-03-27T04:31:24.970328</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348653</t>
+          <t>2026-03-27T04:31:24.970331</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348655</t>
+          <t>2026-03-27T04:31:24.970334</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348659</t>
+          <t>2026-03-27T04:31:24.970336</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348662</t>
+          <t>2026-03-27T04:31:24.970340</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348664</t>
+          <t>2026-03-27T04:31:24.970342</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348667</t>
+          <t>2026-03-27T04:31:24.970346</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348670</t>
+          <t>2026-03-27T04:31:24.970349</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348673</t>
+          <t>2026-03-27T04:31:24.970351</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348676</t>
+          <t>2026-03-27T04:31:24.970354</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348679</t>
+          <t>2026-03-27T04:31:24.970357</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348682</t>
+          <t>2026-03-27T04:31:24.970360</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348685</t>
+          <t>2026-03-27T04:31:24.970363</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348688</t>
+          <t>2026-03-27T04:31:24.970366</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348691</t>
+          <t>2026-03-27T04:31:24.970369</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348694</t>
+          <t>2026-03-27T04:31:24.970373</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348697</t>
+          <t>2026-03-27T04:31:24.970377</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348699</t>
+          <t>2026-03-27T04:31:24.970380</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348702</t>
+          <t>2026-03-27T04:31:24.970383</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348705</t>
+          <t>2026-03-27T04:31:24.970386</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348717</t>
+          <t>2026-03-27T04:31:24.970389</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348720</t>
+          <t>2026-03-27T04:31:24.970391</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348722</t>
+          <t>2026-03-27T04:31:24.970394</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348726</t>
+          <t>2026-03-27T04:31:24.970397</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348729</t>
+          <t>2026-03-27T04:31:24.970400</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348732</t>
+          <t>2026-03-27T04:31:24.970403</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348734</t>
+          <t>2026-03-27T04:31:24.970406</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348737</t>
+          <t>2026-03-27T04:31:24.970409</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348740</t>
+          <t>2026-03-27T04:31:24.970411</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348743</t>
+          <t>2026-03-27T04:31:24.970414</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348746</t>
+          <t>2026-03-27T04:31:24.970417</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348748</t>
+          <t>2026-03-27T04:31:24.970419</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348751</t>
+          <t>2026-03-27T04:31:24.970422</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348754</t>
+          <t>2026-03-27T04:31:24.970425</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348757</t>
+          <t>2026-03-27T04:31:24.970428</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:36.348760</t>
+          <t>2026-03-27T04:31:24.970431</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970229</t>
+          <t>2026-03-28T04:16:58.566448</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970242</t>
+          <t>2026-03-28T04:16:58.566462</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970246</t>
+          <t>2026-03-28T04:16:58.566466</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970249</t>
+          <t>2026-03-28T04:16:58.566470</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970252</t>
+          <t>2026-03-28T04:16:58.566473</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970255</t>
+          <t>2026-03-28T04:16:58.566476</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970258</t>
+          <t>2026-03-28T04:16:58.566479</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970260</t>
+          <t>2026-03-28T04:16:58.566482</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1237</v>
+        <v>1246</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970291</t>
+          <t>2026-03-28T04:16:58.566485</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970299</t>
+          <t>2026-03-28T04:16:58.566488</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970305</t>
+          <t>2026-03-28T04:16:58.566491</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970311</t>
+          <t>2026-03-28T04:16:58.566494</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970317</t>
+          <t>2026-03-28T04:16:58.566497</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970324</t>
+          <t>2026-03-28T04:16:58.566499</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970328</t>
+          <t>2026-03-28T04:16:58.566502</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970331</t>
+          <t>2026-03-28T04:16:58.566505</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970334</t>
+          <t>2026-03-28T04:16:58.566508</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970336</t>
+          <t>2026-03-28T04:16:58.566511</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970340</t>
+          <t>2026-03-28T04:16:58.566514</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970342</t>
+          <t>2026-03-28T04:16:58.566517</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970346</t>
+          <t>2026-03-28T04:16:58.566520</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970349</t>
+          <t>2026-03-28T04:16:58.566523</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970351</t>
+          <t>2026-03-28T04:16:58.566526</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970354</t>
+          <t>2026-03-28T04:16:58.566529</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970357</t>
+          <t>2026-03-28T04:16:58.566532</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970360</t>
+          <t>2026-03-28T04:16:58.566535</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970363</t>
+          <t>2026-03-28T04:16:58.566538</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970366</t>
+          <t>2026-03-28T04:16:58.566541</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970369</t>
+          <t>2026-03-28T04:16:58.566544</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970373</t>
+          <t>2026-03-28T04:16:58.566546</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970377</t>
+          <t>2026-03-28T04:16:58.566549</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970380</t>
+          <t>2026-03-28T04:16:58.566552</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970383</t>
+          <t>2026-03-28T04:16:58.566555</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970386</t>
+          <t>2026-03-28T04:16:58.566558</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970389</t>
+          <t>2026-03-28T04:16:58.566561</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970391</t>
+          <t>2026-03-28T04:16:58.566564</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1399</v>
+        <v>1404</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970394</t>
+          <t>2026-03-28T04:16:58.566567</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970397</t>
+          <t>2026-03-28T04:16:58.566572</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970400</t>
+          <t>2026-03-28T04:16:58.566575</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970403</t>
+          <t>2026-03-28T04:16:58.566579</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970406</t>
+          <t>2026-03-28T04:16:58.566581</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970409</t>
+          <t>2026-03-28T04:16:58.566584</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1378</v>
+        <v>1371</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970411</t>
+          <t>2026-03-28T04:16:58.566587</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1371</v>
+        <v>1376</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970414</t>
+          <t>2026-03-28T04:16:58.566590</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970417</t>
+          <t>2026-03-28T04:16:58.566593</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970419</t>
+          <t>2026-03-28T04:16:58.566596</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970422</t>
+          <t>2026-03-28T04:16:58.566598</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970425</t>
+          <t>2026-03-28T04:16:58.566601</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970428</t>
+          <t>2026-03-28T04:16:58.566604</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:24.970431</t>
+          <t>2026-03-28T04:16:58.566607</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566448</t>
+          <t>2026-03-29T04:34:53.067761</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566462</t>
+          <t>2026-03-29T04:34:53.067773</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566466</t>
+          <t>2026-03-29T04:34:53.067777</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566470</t>
+          <t>2026-03-29T04:34:53.067780</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566473</t>
+          <t>2026-03-29T04:34:53.067783</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566476</t>
+          <t>2026-03-29T04:34:53.067788</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566479</t>
+          <t>2026-03-29T04:34:53.067803</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566482</t>
+          <t>2026-03-29T04:34:53.067811</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566485</t>
+          <t>2026-03-29T04:34:53.067816</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566488</t>
+          <t>2026-03-29T04:34:53.067822</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566491</t>
+          <t>2026-03-29T04:34:53.067828</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566494</t>
+          <t>2026-03-29T04:34:53.067833</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566497</t>
+          <t>2026-03-29T04:34:53.067840</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566499</t>
+          <t>2026-03-29T04:34:53.067846</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566502</t>
+          <t>2026-03-29T04:34:53.067853</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566505</t>
+          <t>2026-03-29T04:34:53.067859</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566508</t>
+          <t>2026-03-29T04:34:53.067864</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566511</t>
+          <t>2026-03-29T04:34:53.067869</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566514</t>
+          <t>2026-03-29T04:34:53.067875</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566517</t>
+          <t>2026-03-29T04:34:53.067881</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566520</t>
+          <t>2026-03-29T04:34:53.067888</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566523</t>
+          <t>2026-03-29T04:34:53.067895</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566526</t>
+          <t>2026-03-29T04:34:53.067924</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566529</t>
+          <t>2026-03-29T04:34:53.067930</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566532</t>
+          <t>2026-03-29T04:34:53.067933</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566535</t>
+          <t>2026-03-29T04:34:53.067937</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566538</t>
+          <t>2026-03-29T04:34:53.067940</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566541</t>
+          <t>2026-03-29T04:34:53.067943</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566544</t>
+          <t>2026-03-29T04:34:53.067945</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566546</t>
+          <t>2026-03-29T04:34:53.067948</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566549</t>
+          <t>2026-03-29T04:34:53.067951</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566552</t>
+          <t>2026-03-29T04:34:53.067954</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566555</t>
+          <t>2026-03-29T04:34:53.067957</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566558</t>
+          <t>2026-03-29T04:34:53.067960</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566561</t>
+          <t>2026-03-29T04:34:53.067963</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566564</t>
+          <t>2026-03-29T04:34:53.067966</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566567</t>
+          <t>2026-03-29T04:34:53.067969</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566572</t>
+          <t>2026-03-29T04:34:53.067972</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566575</t>
+          <t>2026-03-29T04:34:53.067975</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566579</t>
+          <t>2026-03-29T04:34:53.067978</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566581</t>
+          <t>2026-03-29T04:34:53.067981</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566584</t>
+          <t>2026-03-29T04:34:53.067984</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566587</t>
+          <t>2026-03-29T04:34:53.067987</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566590</t>
+          <t>2026-03-29T04:34:53.067990</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566593</t>
+          <t>2026-03-29T04:34:53.067993</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566596</t>
+          <t>2026-03-29T04:34:53.067996</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566598</t>
+          <t>2026-03-29T04:34:53.067999</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566601</t>
+          <t>2026-03-29T04:34:53.068002</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566604</t>
+          <t>2026-03-29T04:34:53.068004</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:58.566607</t>
+          <t>2026-03-29T04:34:53.068007</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1198</v>
+        <v>1221</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067761</t>
+          <t>2026-03-30T04:42:14.262934</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067773</t>
+          <t>2026-03-30T04:42:14.262949</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1196</v>
+        <v>1220</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067777</t>
+          <t>2026-03-30T04:42:14.262953</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067780</t>
+          <t>2026-03-30T04:42:14.262956</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067783</t>
+          <t>2026-03-30T04:42:14.262960</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067788</t>
+          <t>2026-03-30T04:42:14.262963</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067803</t>
+          <t>2026-03-30T04:42:14.262966</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067811</t>
+          <t>2026-03-30T04:42:14.262970</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067816</t>
+          <t>2026-03-30T04:42:14.262973</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067822</t>
+          <t>2026-03-30T04:42:14.262977</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1185</v>
+        <v>1237</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067828</t>
+          <t>2026-03-30T04:42:14.262980</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1178</v>
+        <v>1246</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067833</t>
+          <t>2026-03-30T04:42:14.262983</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067840</t>
+          <t>2026-03-30T04:42:14.262987</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067846</t>
+          <t>2026-03-30T04:42:14.262990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067853</t>
+          <t>2026-03-30T04:42:14.262993</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067859</t>
+          <t>2026-03-30T04:42:14.262996</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1268</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067864</t>
+          <t>2026-03-30T04:42:14.263000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1267</v>
+        <v>1200</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067869</t>
+          <t>2026-03-30T04:42:14.263003</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1318</v>
+        <v>1267</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067875</t>
+          <t>2026-03-30T04:42:14.263006</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1316</v>
+        <v>1269</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067881</t>
+          <t>2026-03-30T04:42:14.263010</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067888</t>
+          <t>2026-03-30T04:42:14.263013</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067895</t>
+          <t>2026-03-30T04:42:14.263016</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1359</v>
+        <v>1318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067924</t>
+          <t>2026-03-30T04:42:14.263020</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1361</v>
+        <v>1316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067930</t>
+          <t>2026-03-30T04:42:14.263023</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067933</t>
+          <t>2026-03-30T04:42:14.263026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067937</t>
+          <t>2026-03-30T04:42:14.263029</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067940</t>
+          <t>2026-03-30T04:42:14.263033</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067943</t>
+          <t>2026-03-30T04:42:14.263036</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067945</t>
+          <t>2026-03-30T04:42:14.263039</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067948</t>
+          <t>2026-03-30T04:42:14.263042</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067951</t>
+          <t>2026-03-30T04:42:14.263046</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067954</t>
+          <t>2026-03-30T04:42:14.263049</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1385</v>
+        <v>1360</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067957</t>
+          <t>2026-03-30T04:42:14.263052</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067960</t>
+          <t>2026-03-30T04:42:14.263056</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067963</t>
+          <t>2026-03-30T04:42:14.263059</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067966</t>
+          <t>2026-03-30T04:42:14.263062</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1404</v>
+        <v>1388</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067969</t>
+          <t>2026-03-30T04:42:14.263066</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1399</v>
+        <v>1390</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067972</t>
+          <t>2026-03-30T04:42:14.263069</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1401</v>
+        <v>1386</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067975</t>
+          <t>2026-03-30T04:42:14.263081</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067978</t>
+          <t>2026-03-30T04:42:14.263085</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067981</t>
+          <t>2026-03-30T04:42:14.263088</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067984</t>
+          <t>2026-03-30T04:42:14.263091</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067987</t>
+          <t>2026-03-30T04:42:14.263095</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067990</t>
+          <t>2026-03-30T04:42:14.263098</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067993</t>
+          <t>2026-03-30T04:42:14.263101</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1385</v>
+        <v>1376</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067996</t>
+          <t>2026-03-30T04:42:14.263105</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.067999</t>
+          <t>2026-03-30T04:42:14.263108</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1383</v>
+        <v>1371</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.068002</t>
+          <t>2026-03-30T04:42:14.263111</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.068004</t>
+          <t>2026-03-30T04:42:14.263114</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:53.068007</t>
+          <t>2026-03-30T04:42:14.263118</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262934</t>
+          <t>2026-03-31T04:33:42.939818</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262949</t>
+          <t>2026-03-31T04:33:42.939831</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262953</t>
+          <t>2026-03-31T04:33:42.939836</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262956</t>
+          <t>2026-03-31T04:33:42.939839</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262960</t>
+          <t>2026-03-31T04:33:42.939842</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262963</t>
+          <t>2026-03-31T04:33:42.939845</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262966</t>
+          <t>2026-03-31T04:33:42.939848</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262970</t>
+          <t>2026-03-31T04:33:42.939851</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262973</t>
+          <t>2026-03-31T04:33:42.939853</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262977</t>
+          <t>2026-03-31T04:33:42.939856</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262980</t>
+          <t>2026-03-31T04:33:42.939859</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262983</t>
+          <t>2026-03-31T04:33:42.939862</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262987</t>
+          <t>2026-03-31T04:33:42.939865</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262990</t>
+          <t>2026-03-31T04:33:42.939867</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262993</t>
+          <t>2026-03-31T04:33:42.939870</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.262996</t>
+          <t>2026-03-31T04:33:42.939873</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263000</t>
+          <t>2026-03-31T04:33:42.939876</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263003</t>
+          <t>2026-03-31T04:33:42.939879</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263006</t>
+          <t>2026-03-31T04:33:42.939881</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263010</t>
+          <t>2026-03-31T04:33:42.939884</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263013</t>
+          <t>2026-03-31T04:33:42.939887</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263016</t>
+          <t>2026-03-31T04:33:42.939890</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263020</t>
+          <t>2026-03-31T04:33:42.939893</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263023</t>
+          <t>2026-03-31T04:33:42.939896</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263026</t>
+          <t>2026-03-31T04:33:42.939899</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263029</t>
+          <t>2026-03-31T04:33:42.939901</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263033</t>
+          <t>2026-03-31T04:33:42.939904</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263036</t>
+          <t>2026-03-31T04:33:42.939907</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263039</t>
+          <t>2026-03-31T04:33:42.939910</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263042</t>
+          <t>2026-03-31T04:33:42.939912</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263046</t>
+          <t>2026-03-31T04:33:42.939915</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263049</t>
+          <t>2026-03-31T04:33:42.939918</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263052</t>
+          <t>2026-03-31T04:33:42.939921</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263056</t>
+          <t>2026-03-31T04:33:42.939923</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263059</t>
+          <t>2026-03-31T04:33:42.939926</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263062</t>
+          <t>2026-03-31T04:33:42.939929</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263066</t>
+          <t>2026-03-31T04:33:42.939932</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263069</t>
+          <t>2026-03-31T04:33:42.939935</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263081</t>
+          <t>2026-03-31T04:33:42.939945</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263085</t>
+          <t>2026-03-31T04:33:42.939948</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263088</t>
+          <t>2026-03-31T04:33:42.939951</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263091</t>
+          <t>2026-03-31T04:33:42.939954</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263095</t>
+          <t>2026-03-31T04:33:42.939956</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263098</t>
+          <t>2026-03-31T04:33:42.939959</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263101</t>
+          <t>2026-03-31T04:33:42.939962</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263105</t>
+          <t>2026-03-31T04:33:42.939964</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263108</t>
+          <t>2026-03-31T04:33:42.939967</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263111</t>
+          <t>2026-03-31T04:33:42.939970</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263114</t>
+          <t>2026-03-31T04:33:42.939973</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:14.263118</t>
+          <t>2026-03-31T04:33:42.939976</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939818</t>
+          <t>2026-04-01T04:44:34.741690</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939831</t>
+          <t>2026-04-01T04:44:34.741706</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939836</t>
+          <t>2026-04-01T04:44:34.741712</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939839</t>
+          <t>2026-04-01T04:44:34.741716</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939842</t>
+          <t>2026-04-01T04:44:34.741721</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939845</t>
+          <t>2026-04-01T04:44:34.741724</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939848</t>
+          <t>2026-04-01T04:44:34.741727</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939851</t>
+          <t>2026-04-01T04:44:34.741731</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939853</t>
+          <t>2026-04-01T04:44:34.741734</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939856</t>
+          <t>2026-04-01T04:44:34.741737</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939859</t>
+          <t>2026-04-01T04:44:34.741740</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939862</t>
+          <t>2026-04-01T04:44:34.741743</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939865</t>
+          <t>2026-04-01T04:44:34.741746</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939867</t>
+          <t>2026-04-01T04:44:34.741748</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939870</t>
+          <t>2026-04-01T04:44:34.741751</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1180</v>
+        <v>1237</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939873</t>
+          <t>2026-04-01T04:44:34.741754</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1178</v>
+        <v>1246</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939876</t>
+          <t>2026-04-01T04:44:34.741757</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1185</v>
+        <v>1239</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939879</t>
+          <t>2026-04-01T04:44:34.741760</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939881</t>
+          <t>2026-04-01T04:44:34.741763</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1206</v>
+        <v>1185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939884</t>
+          <t>2026-04-01T04:44:34.741766</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1200</v>
+        <v>1178</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939887</t>
+          <t>2026-04-01T04:44:34.741770</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1268</v>
+        <v>1206</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939890</t>
+          <t>2026-04-01T04:44:34.741773</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1269</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939893</t>
+          <t>2026-04-01T04:44:34.741776</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1267</v>
+        <v>1200</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939896</t>
+          <t>2026-04-01T04:44:34.741779</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939899</t>
+          <t>2026-04-01T04:44:34.741782</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1318</v>
+        <v>1267</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939901</t>
+          <t>2026-04-01T04:44:34.741785</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1316</v>
+        <v>1269</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939904</t>
+          <t>2026-04-01T04:44:34.741788</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1361</v>
+        <v>1310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939907</t>
+          <t>2026-04-01T04:44:34.741791</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939910</t>
+          <t>2026-04-01T04:44:34.741794</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939912</t>
+          <t>2026-04-01T04:44:34.741797</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939915</t>
+          <t>2026-04-01T04:44:34.741800</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939918</t>
+          <t>2026-04-01T04:44:34.741802</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939921</t>
+          <t>2026-04-01T04:44:34.741805</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939923</t>
+          <t>2026-04-01T04:44:34.741808</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939926</t>
+          <t>2026-04-01T04:44:34.741811</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939929</t>
+          <t>2026-04-01T04:44:34.741814</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1383</v>
+        <v>1360</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939932</t>
+          <t>2026-04-01T04:44:34.741817</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939935</t>
+          <t>2026-04-01T04:44:34.741820</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939945</t>
+          <t>2026-04-01T04:44:34.741824</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939948</t>
+          <t>2026-04-01T04:44:34.741827</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939951</t>
+          <t>2026-04-01T04:44:34.741830</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939954</t>
+          <t>2026-04-01T04:44:34.741834</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939956</t>
+          <t>2026-04-01T04:44:34.741837</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1404</v>
+        <v>1388</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939959</t>
+          <t>2026-04-01T04:44:34.741840</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939962</t>
+          <t>2026-04-01T04:44:34.741843</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939964</t>
+          <t>2026-04-01T04:44:34.741846</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939967</t>
+          <t>2026-04-01T04:44:34.741848</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939970</t>
+          <t>2026-04-01T04:44:34.741851</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939973</t>
+          <t>2026-04-01T04:44:34.741854</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:42.939976</t>
+          <t>2026-04-01T04:44:34.741857</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741690</t>
+          <t>2026-04-02T04:27:09.691963</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741706</t>
+          <t>2026-04-02T04:27:09.691978</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741712</t>
+          <t>2026-04-02T04:27:09.691981</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1228</v>
+        <v>1266</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741716</t>
+          <t>2026-04-02T04:27:09.691984</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741721</t>
+          <t>2026-04-02T04:27:09.691987</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1223</v>
+        <v>1268</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741724</t>
+          <t>2026-04-02T04:27:09.691990</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741727</t>
+          <t>2026-04-02T04:27:09.691993</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741731</t>
+          <t>2026-04-02T04:27:09.691996</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741734</t>
+          <t>2026-04-02T04:27:09.691999</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741737</t>
+          <t>2026-04-02T04:27:09.692001</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1196</v>
+        <v>1220</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741740</t>
+          <t>2026-04-02T04:27:09.692004</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1198</v>
+        <v>1221</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741743</t>
+          <t>2026-04-02T04:27:09.692008</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741746</t>
+          <t>2026-04-02T04:27:09.692011</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741748</t>
+          <t>2026-04-02T04:27:09.692014</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741751</t>
+          <t>2026-04-02T04:27:09.692017</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741754</t>
+          <t>2026-04-02T04:27:09.692020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741757</t>
+          <t>2026-04-02T04:27:09.692022</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741760</t>
+          <t>2026-04-02T04:27:09.692025</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1180</v>
+        <v>1246</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741763</t>
+          <t>2026-04-02T04:27:09.692028</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1185</v>
+        <v>1237</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741766</t>
+          <t>2026-04-02T04:27:09.692031</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1178</v>
+        <v>1239</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741770</t>
+          <t>2026-04-02T04:27:09.692034</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1206</v>
+        <v>1178</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741773</t>
+          <t>2026-04-02T04:27:09.692037</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>1180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741776</t>
+          <t>2026-04-02T04:27:09.692040</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741779</t>
+          <t>2026-04-02T04:27:09.692043</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1268</v>
+        <v>1206</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741782</t>
+          <t>2026-04-02T04:27:09.692046</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741785</t>
+          <t>2026-04-02T04:27:09.692049</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1269</v>
+        <v>1200</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741788</t>
+          <t>2026-04-02T04:27:09.692052</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1310</v>
+        <v>1267</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741791</t>
+          <t>2026-04-02T04:27:09.692054</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1316</v>
+        <v>1269</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741794</t>
+          <t>2026-04-02T04:27:09.692057</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1318</v>
+        <v>1268</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741797</t>
+          <t>2026-04-02T04:27:09.692060</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1361</v>
+        <v>1310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741800</t>
+          <t>2026-04-02T04:27:09.692064</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741802</t>
+          <t>2026-04-02T04:27:09.692067</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741805</t>
+          <t>2026-04-02T04:27:09.692071</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741808</t>
+          <t>2026-04-02T04:27:09.692075</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741811</t>
+          <t>2026-04-02T04:27:09.692079</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741814</t>
+          <t>2026-04-02T04:27:09.692081</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741817</t>
+          <t>2026-04-02T04:27:09.692084</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741820</t>
+          <t>2026-04-02T04:27:09.692087</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741824</t>
+          <t>2026-04-02T04:27:09.692090</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741827</t>
+          <t>2026-04-02T04:27:09.692093</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741830</t>
+          <t>2026-04-02T04:27:09.692096</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741834</t>
+          <t>2026-04-02T04:27:09.692099</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741837</t>
+          <t>2026-04-02T04:27:09.692102</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741840</t>
+          <t>2026-04-02T04:27:09.692105</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741843</t>
+          <t>2026-04-02T04:27:09.692107</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1399</v>
+        <v>1390</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741846</t>
+          <t>2026-04-02T04:27:09.692110</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1401</v>
+        <v>1386</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741848</t>
+          <t>2026-04-02T04:27:09.692113</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1404</v>
+        <v>1388</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741851</t>
+          <t>2026-04-02T04:27:09.692116</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741854</t>
+          <t>2026-04-02T04:27:09.692119</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:34.741857</t>
+          <t>2026-04-02T04:27:09.692122</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.691963</t>
+          <t>2026-04-03T04:27:20.644031</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.691978</t>
+          <t>2026-04-03T04:27:20.644048</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.691981</t>
+          <t>2026-04-03T04:27:20.644053</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.691984</t>
+          <t>2026-04-03T04:27:20.644058</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.691987</t>
+          <t>2026-04-03T04:27:20.644063</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.691990</t>
+          <t>2026-04-03T04:27:20.644068</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.691993</t>
+          <t>2026-04-03T04:27:20.644073</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.691996</t>
+          <t>2026-04-03T04:27:20.644077</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.691999</t>
+          <t>2026-04-03T04:27:20.644082</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692001</t>
+          <t>2026-04-03T04:27:20.644087</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692004</t>
+          <t>2026-04-03T04:27:20.644092</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692008</t>
+          <t>2026-04-03T04:27:20.644097</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692011</t>
+          <t>2026-04-03T04:27:20.644102</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692014</t>
+          <t>2026-04-03T04:27:20.644106</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692017</t>
+          <t>2026-04-03T04:27:20.644111</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692020</t>
+          <t>2026-04-03T04:27:20.644116</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692022</t>
+          <t>2026-04-03T04:27:20.644121</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692025</t>
+          <t>2026-04-03T04:27:20.644126</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692028</t>
+          <t>2026-04-03T04:27:20.644131</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692031</t>
+          <t>2026-04-03T04:27:20.644136</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692034</t>
+          <t>2026-04-03T04:27:20.644141</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692037</t>
+          <t>2026-04-03T04:27:20.644146</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692040</t>
+          <t>2026-04-03T04:27:20.644151</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692043</t>
+          <t>2026-04-03T04:27:20.644156</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692046</t>
+          <t>2026-04-03T04:27:20.644161</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692049</t>
+          <t>2026-04-03T04:27:20.644165</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692052</t>
+          <t>2026-04-03T04:27:20.644170</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692054</t>
+          <t>2026-04-03T04:27:20.644175</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692057</t>
+          <t>2026-04-03T04:27:20.644180</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692060</t>
+          <t>2026-04-03T04:27:20.644185</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692064</t>
+          <t>2026-04-03T04:27:20.644189</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692067</t>
+          <t>2026-04-03T04:27:20.644194</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692071</t>
+          <t>2026-04-03T04:27:20.644199</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692075</t>
+          <t>2026-04-03T04:27:20.644204</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692079</t>
+          <t>2026-04-03T04:27:20.644208</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692081</t>
+          <t>2026-04-03T04:27:20.644213</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692084</t>
+          <t>2026-04-03T04:27:20.644218</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692087</t>
+          <t>2026-04-03T04:27:20.644223</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692090</t>
+          <t>2026-04-03T04:27:20.644228</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692093</t>
+          <t>2026-04-03T04:27:20.644233</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692096</t>
+          <t>2026-04-03T04:27:20.644238</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692099</t>
+          <t>2026-04-03T04:27:20.644243</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692102</t>
+          <t>2026-04-03T04:27:20.644247</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692105</t>
+          <t>2026-04-03T04:27:20.644252</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692107</t>
+          <t>2026-04-03T04:27:20.644257</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692110</t>
+          <t>2026-04-03T04:27:20.644261</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692113</t>
+          <t>2026-04-03T04:27:20.644266</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692116</t>
+          <t>2026-04-03T04:27:20.644271</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692119</t>
+          <t>2026-04-03T04:27:20.644276</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:09.692122</t>
+          <t>2026-04-03T04:27:20.644281</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644031</t>
+          <t>2026-04-04T04:13:38.890233</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644048</t>
+          <t>2026-04-04T04:13:38.890248</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644053</t>
+          <t>2026-04-04T04:13:38.890252</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644058</t>
+          <t>2026-04-04T04:13:38.890255</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644063</t>
+          <t>2026-04-04T04:13:38.890259</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644068</t>
+          <t>2026-04-04T04:13:38.890262</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644073</t>
+          <t>2026-04-04T04:13:38.890265</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644077</t>
+          <t>2026-04-04T04:13:38.890268</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644082</t>
+          <t>2026-04-04T04:13:38.890272</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644087</t>
+          <t>2026-04-04T04:13:38.890275</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644092</t>
+          <t>2026-04-04T04:13:38.890279</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644097</t>
+          <t>2026-04-04T04:13:38.890282</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644102</t>
+          <t>2026-04-04T04:13:38.890285</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644106</t>
+          <t>2026-04-04T04:13:38.890288</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644111</t>
+          <t>2026-04-04T04:13:38.890291</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644116</t>
+          <t>2026-04-04T04:13:38.890294</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644121</t>
+          <t>2026-04-04T04:13:38.890297</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644126</t>
+          <t>2026-04-04T04:13:38.890301</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644131</t>
+          <t>2026-04-04T04:13:38.890304</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644136</t>
+          <t>2026-04-04T04:13:38.890307</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644141</t>
+          <t>2026-04-04T04:13:38.890311</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644146</t>
+          <t>2026-04-04T04:13:38.890315</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644151</t>
+          <t>2026-04-04T04:13:38.890318</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644156</t>
+          <t>2026-04-04T04:13:38.890321</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644161</t>
+          <t>2026-04-04T04:13:38.890324</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644165</t>
+          <t>2026-04-04T04:13:38.890328</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644170</t>
+          <t>2026-04-04T04:13:38.890331</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644175</t>
+          <t>2026-04-04T04:13:38.890334</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644180</t>
+          <t>2026-04-04T04:13:38.890337</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644185</t>
+          <t>2026-04-04T04:13:38.890341</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644189</t>
+          <t>2026-04-04T04:13:38.890344</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644194</t>
+          <t>2026-04-04T04:13:38.890347</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644199</t>
+          <t>2026-04-04T04:13:38.890350</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644204</t>
+          <t>2026-04-04T04:13:38.890354</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644208</t>
+          <t>2026-04-04T04:13:38.890357</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644213</t>
+          <t>2026-04-04T04:13:38.890360</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644218</t>
+          <t>2026-04-04T04:13:38.890363</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644223</t>
+          <t>2026-04-04T04:13:38.890367</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644228</t>
+          <t>2026-04-04T04:13:38.890371</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644233</t>
+          <t>2026-04-04T04:13:38.890374</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644238</t>
+          <t>2026-04-04T04:13:38.890377</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644243</t>
+          <t>2026-04-04T04:13:38.890380</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644247</t>
+          <t>2026-04-04T04:13:38.890383</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644252</t>
+          <t>2026-04-04T04:13:38.890387</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644257</t>
+          <t>2026-04-04T04:13:38.890390</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644261</t>
+          <t>2026-04-04T04:13:38.890394</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644266</t>
+          <t>2026-04-04T04:13:38.890397</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644271</t>
+          <t>2026-04-04T04:13:38.890401</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644276</t>
+          <t>2026-04-04T04:13:38.890404</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:20.644281</t>
+          <t>2026-04-04T04:13:38.890407</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890233</t>
+          <t>2026-04-05T04:34:37.132047</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890248</t>
+          <t>2026-04-05T04:34:37.132086</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890252</t>
+          <t>2026-04-05T04:34:37.132095</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890255</t>
+          <t>2026-04-05T04:34:37.132101</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890259</t>
+          <t>2026-04-05T04:34:37.132107</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890262</t>
+          <t>2026-04-05T04:34:37.132112</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890265</t>
+          <t>2026-04-05T04:34:37.132118</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890268</t>
+          <t>2026-04-05T04:34:37.132124</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890272</t>
+          <t>2026-04-05T04:34:37.132131</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890275</t>
+          <t>2026-04-05T04:34:37.132134</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890279</t>
+          <t>2026-04-05T04:34:37.132137</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890282</t>
+          <t>2026-04-05T04:34:37.132140</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890285</t>
+          <t>2026-04-05T04:34:37.132142</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890288</t>
+          <t>2026-04-05T04:34:37.132145</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890291</t>
+          <t>2026-04-05T04:34:37.132148</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890294</t>
+          <t>2026-04-05T04:34:37.132151</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890297</t>
+          <t>2026-04-05T04:34:37.132154</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890301</t>
+          <t>2026-04-05T04:34:37.132158</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890304</t>
+          <t>2026-04-05T04:34:37.132161</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890307</t>
+          <t>2026-04-05T04:34:37.132164</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890311</t>
+          <t>2026-04-05T04:34:37.132167</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890315</t>
+          <t>2026-04-05T04:34:37.132170</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890318</t>
+          <t>2026-04-05T04:34:37.132173</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890321</t>
+          <t>2026-04-05T04:34:37.132176</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1239</v>
+        <v>1246</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890324</t>
+          <t>2026-04-05T04:34:37.132178</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890328</t>
+          <t>2026-04-05T04:34:37.132181</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1246</v>
+        <v>1239</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890331</t>
+          <t>2026-04-05T04:34:37.132184</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890334</t>
+          <t>2026-04-05T04:34:37.132187</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890337</t>
+          <t>2026-04-05T04:34:37.132190</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890341</t>
+          <t>2026-04-05T04:34:37.132193</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890344</t>
+          <t>2026-04-05T04:34:37.132196</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890347</t>
+          <t>2026-04-05T04:34:37.132198</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890350</t>
+          <t>2026-04-05T04:34:37.132201</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890354</t>
+          <t>2026-04-05T04:34:37.132204</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890357</t>
+          <t>2026-04-05T04:34:37.132207</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890360</t>
+          <t>2026-04-05T04:34:37.132210</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890363</t>
+          <t>2026-04-05T04:34:37.132212</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890367</t>
+          <t>2026-04-05T04:34:37.132215</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890371</t>
+          <t>2026-04-05T04:34:37.132218</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890374</t>
+          <t>2026-04-05T04:34:37.132221</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890377</t>
+          <t>2026-04-05T04:34:37.132224</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890380</t>
+          <t>2026-04-05T04:34:37.132227</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890383</t>
+          <t>2026-04-05T04:34:37.132230</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890387</t>
+          <t>2026-04-05T04:34:37.132232</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890390</t>
+          <t>2026-04-05T04:34:37.132235</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890394</t>
+          <t>2026-04-05T04:34:37.132238</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890397</t>
+          <t>2026-04-05T04:34:37.132241</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890401</t>
+          <t>2026-04-05T04:34:37.132244</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890404</t>
+          <t>2026-04-05T04:34:37.132246</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.890407</t>
+          <t>2026-04-05T04:34:37.132249</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132047</t>
+          <t>2026-04-06T04:41:46.729232</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132086</t>
+          <t>2026-04-06T04:41:46.729245</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132095</t>
+          <t>2026-04-06T04:41:46.729249</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132101</t>
+          <t>2026-04-06T04:41:46.729253</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132107</t>
+          <t>2026-04-06T04:41:46.729255</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132112</t>
+          <t>2026-04-06T04:41:46.729258</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132118</t>
+          <t>2026-04-06T04:41:46.729261</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132124</t>
+          <t>2026-04-06T04:41:46.729264</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132131</t>
+          <t>2026-04-06T04:41:46.729267</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132134</t>
+          <t>2026-04-06T04:41:46.729270</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132137</t>
+          <t>2026-04-06T04:41:46.729273</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132140</t>
+          <t>2026-04-06T04:41:46.729275</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132142</t>
+          <t>2026-04-06T04:41:46.729278</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132145</t>
+          <t>2026-04-06T04:41:46.729281</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132148</t>
+          <t>2026-04-06T04:41:46.729284</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132151</t>
+          <t>2026-04-06T04:41:46.729286</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132154</t>
+          <t>2026-04-06T04:41:46.729289</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132158</t>
+          <t>2026-04-06T04:41:46.729292</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132161</t>
+          <t>2026-04-06T04:41:46.729295</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132164</t>
+          <t>2026-04-06T04:41:46.729298</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132167</t>
+          <t>2026-04-06T04:41:46.729302</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132170</t>
+          <t>2026-04-06T04:41:46.729305</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132173</t>
+          <t>2026-04-06T04:41:46.729307</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132176</t>
+          <t>2026-04-06T04:41:46.729310</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132178</t>
+          <t>2026-04-06T04:41:46.729313</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132181</t>
+          <t>2026-04-06T04:41:46.729316</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132184</t>
+          <t>2026-04-06T04:41:46.729319</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132187</t>
+          <t>2026-04-06T04:41:46.729322</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132190</t>
+          <t>2026-04-06T04:41:46.729325</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132193</t>
+          <t>2026-04-06T04:41:46.729327</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132196</t>
+          <t>2026-04-06T04:41:46.729330</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132198</t>
+          <t>2026-04-06T04:41:46.729333</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132201</t>
+          <t>2026-04-06T04:41:46.729336</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132204</t>
+          <t>2026-04-06T04:41:46.729339</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132207</t>
+          <t>2026-04-06T04:41:46.729341</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132210</t>
+          <t>2026-04-06T04:41:46.729344</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132212</t>
+          <t>2026-04-06T04:41:46.729347</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132215</t>
+          <t>2026-04-06T04:41:46.729350</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132218</t>
+          <t>2026-04-06T04:41:46.729352</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132221</t>
+          <t>2026-04-06T04:41:46.729356</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132224</t>
+          <t>2026-04-06T04:41:46.729358</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132227</t>
+          <t>2026-04-06T04:41:46.729361</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132230</t>
+          <t>2026-04-06T04:41:46.729364</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132232</t>
+          <t>2026-04-06T04:41:46.729367</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132235</t>
+          <t>2026-04-06T04:41:46.729370</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132238</t>
+          <t>2026-04-06T04:41:46.729372</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132241</t>
+          <t>2026-04-06T04:41:46.729375</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132244</t>
+          <t>2026-04-06T04:41:46.729378</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132246</t>
+          <t>2026-04-06T04:41:46.729381</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:37.132249</t>
+          <t>2026-04-06T04:41:46.729383</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729232</t>
+          <t>2026-04-07T04:30:30.151804</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729245</t>
+          <t>2026-04-07T04:30:30.151812</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729249</t>
+          <t>2026-04-07T04:30:30.151816</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729253</t>
+          <t>2026-04-07T04:30:30.151819</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729255</t>
+          <t>2026-04-07T04:30:30.151822</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729258</t>
+          <t>2026-04-07T04:30:30.151825</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729261</t>
+          <t>2026-04-07T04:30:30.151828</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729264</t>
+          <t>2026-04-07T04:30:30.151831</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729267</t>
+          <t>2026-04-07T04:30:30.151834</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729270</t>
+          <t>2026-04-07T04:30:30.151837</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729273</t>
+          <t>2026-04-07T04:30:30.151839</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729275</t>
+          <t>2026-04-07T04:30:30.151842</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729278</t>
+          <t>2026-04-07T04:30:30.151845</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729281</t>
+          <t>2026-04-07T04:30:30.151848</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729284</t>
+          <t>2026-04-07T04:30:30.151851</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729286</t>
+          <t>2026-04-07T04:30:30.151853</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729289</t>
+          <t>2026-04-07T04:30:30.151856</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729292</t>
+          <t>2026-04-07T04:30:30.151859</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729295</t>
+          <t>2026-04-07T04:30:30.151862</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729298</t>
+          <t>2026-04-07T04:30:30.151865</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729302</t>
+          <t>2026-04-07T04:30:30.151868</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729305</t>
+          <t>2026-04-07T04:30:30.151871</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729307</t>
+          <t>2026-04-07T04:30:30.151874</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729310</t>
+          <t>2026-04-07T04:30:30.151877</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729313</t>
+          <t>2026-04-07T04:30:30.151880</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729316</t>
+          <t>2026-04-07T04:30:30.151883</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729319</t>
+          <t>2026-04-07T04:30:30.151885</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729322</t>
+          <t>2026-04-07T04:30:30.151888</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729325</t>
+          <t>2026-04-07T04:30:30.151891</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729327</t>
+          <t>2026-04-07T04:30:30.151894</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729330</t>
+          <t>2026-04-07T04:30:30.151897</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729333</t>
+          <t>2026-04-07T04:30:30.151900</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729336</t>
+          <t>2026-04-07T04:30:30.151902</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729339</t>
+          <t>2026-04-07T04:30:30.151905</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729341</t>
+          <t>2026-04-07T04:30:30.151908</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729344</t>
+          <t>2026-04-07T04:30:30.151911</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729347</t>
+          <t>2026-04-07T04:30:30.151914</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729350</t>
+          <t>2026-04-07T04:30:30.151916</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729352</t>
+          <t>2026-04-07T04:30:30.151919</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729356</t>
+          <t>2026-04-07T04:30:30.151922</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729358</t>
+          <t>2026-04-07T04:30:30.151925</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729361</t>
+          <t>2026-04-07T04:30:30.151928</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729364</t>
+          <t>2026-04-07T04:30:30.151931</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729367</t>
+          <t>2026-04-07T04:30:30.151933</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729370</t>
+          <t>2026-04-07T04:30:30.151936</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729372</t>
+          <t>2026-04-07T04:30:30.151939</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729375</t>
+          <t>2026-04-07T04:30:30.151942</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729378</t>
+          <t>2026-04-07T04:30:30.151944</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729381</t>
+          <t>2026-04-07T04:30:30.151947</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:46.729383</t>
+          <t>2026-04-07T04:30:30.151950</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151804</t>
+          <t>2026-04-08T04:34:17.653351</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151812</t>
+          <t>2026-04-08T04:34:17.653365</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151816</t>
+          <t>2026-04-08T04:34:17.653369</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151819</t>
+          <t>2026-04-08T04:34:17.653372</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151822</t>
+          <t>2026-04-08T04:34:17.653375</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151825</t>
+          <t>2026-04-08T04:34:17.653378</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151828</t>
+          <t>2026-04-08T04:34:17.653381</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151831</t>
+          <t>2026-04-08T04:34:17.653383</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151834</t>
+          <t>2026-04-08T04:34:17.653386</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151837</t>
+          <t>2026-04-08T04:34:17.653389</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151839</t>
+          <t>2026-04-08T04:34:17.653392</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151842</t>
+          <t>2026-04-08T04:34:17.653394</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151845</t>
+          <t>2026-04-08T04:34:17.653397</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151848</t>
+          <t>2026-04-08T04:34:17.653400</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151851</t>
+          <t>2026-04-08T04:34:17.653403</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151853</t>
+          <t>2026-04-08T04:34:17.653406</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151856</t>
+          <t>2026-04-08T04:34:17.653409</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151859</t>
+          <t>2026-04-08T04:34:17.653412</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1223</v>
+        <v>1268</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151862</t>
+          <t>2026-04-08T04:34:17.653415</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1228</v>
+        <v>1264</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151865</t>
+          <t>2026-04-08T04:34:17.653418</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1221</v>
+        <v>1266</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151868</t>
+          <t>2026-04-08T04:34:17.653421</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151871</t>
+          <t>2026-04-08T04:34:17.653424</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151874</t>
+          <t>2026-04-08T04:34:17.653427</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151877</t>
+          <t>2026-04-08T04:34:17.653429</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151880</t>
+          <t>2026-04-08T04:34:17.653432</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151883</t>
+          <t>2026-04-08T04:34:17.653435</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151885</t>
+          <t>2026-04-08T04:34:17.653438</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1233</v>
+        <v>1196</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151888</t>
+          <t>2026-04-08T04:34:17.653441</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1237</v>
+        <v>1198</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151891</t>
+          <t>2026-04-08T04:34:17.653444</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151894</t>
+          <t>2026-04-08T04:34:17.653446</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151897</t>
+          <t>2026-04-08T04:34:17.653454</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1246</v>
+        <v>1239</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151900</t>
+          <t>2026-04-08T04:34:17.653461</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151902</t>
+          <t>2026-04-08T04:34:17.653466</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1185</v>
+        <v>1239</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151905</t>
+          <t>2026-04-08T04:34:17.653472</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1180</v>
+        <v>1237</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151908</t>
+          <t>2026-04-08T04:34:17.653478</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1178</v>
+        <v>1246</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151911</t>
+          <t>2026-04-08T04:34:17.653485</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151914</t>
+          <t>2026-04-08T04:34:17.653490</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151916</t>
+          <t>2026-04-08T04:34:17.653496</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1206</v>
+        <v>1185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151919</t>
+          <t>2026-04-08T04:34:17.653502</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151922</t>
+          <t>2026-04-08T04:34:17.653508</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151925</t>
+          <t>2026-04-08T04:34:17.653514</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151928</t>
+          <t>2026-04-08T04:34:17.653522</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151931</t>
+          <t>2026-04-08T04:34:17.653525</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151933</t>
+          <t>2026-04-08T04:34:17.653528</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151936</t>
+          <t>2026-04-08T04:34:17.653531</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1359</v>
+        <v>1318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151939</t>
+          <t>2026-04-08T04:34:17.653534</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1361</v>
+        <v>1310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151942</t>
+          <t>2026-04-08T04:34:17.653537</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1358</v>
+        <v>1316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151944</t>
+          <t>2026-04-08T04:34:17.653540</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151947</t>
+          <t>2026-04-08T04:34:17.653543</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:30.151950</t>
+          <t>2026-04-08T04:34:17.653545</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1293</v>
+        <v>1272</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653351</t>
+          <t>2026-04-09T04:31:12.831243</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1295</v>
+        <v>1270</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653365</t>
+          <t>2026-04-09T04:31:12.831261</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653369</t>
+          <t>2026-04-09T04:31:12.831265</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1257</v>
+        <v>1292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653372</t>
+          <t>2026-04-09T04:31:12.831268</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653375</t>
+          <t>2026-04-09T04:31:12.831271</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1259</v>
+        <v>1295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653378</t>
+          <t>2026-04-09T04:31:12.831274</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653381</t>
+          <t>2026-04-09T04:31:12.831277</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653383</t>
+          <t>2026-04-09T04:31:12.831280</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653386</t>
+          <t>2026-04-09T04:31:12.831283</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653389</t>
+          <t>2026-04-09T04:31:12.831286</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653392</t>
+          <t>2026-04-09T04:31:12.831289</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653394</t>
+          <t>2026-04-09T04:31:12.831292</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653397</t>
+          <t>2026-04-09T04:31:12.831295</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653400</t>
+          <t>2026-04-09T04:31:12.831298</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653403</t>
+          <t>2026-04-09T04:31:12.831301</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653406</t>
+          <t>2026-04-09T04:31:12.831304</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653409</t>
+          <t>2026-04-09T04:31:12.831307</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653412</t>
+          <t>2026-04-09T04:31:12.831310</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653415</t>
+          <t>2026-04-09T04:31:12.831313</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653418</t>
+          <t>2026-04-09T04:31:12.831316</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653421</t>
+          <t>2026-04-09T04:31:12.831319</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1221</v>
+        <v>1266</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653424</t>
+          <t>2026-04-09T04:31:12.831323</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1223</v>
+        <v>1264</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653427</t>
+          <t>2026-04-09T04:31:12.831325</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653429</t>
+          <t>2026-04-09T04:31:12.831328</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653432</t>
+          <t>2026-04-09T04:31:12.831331</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653435</t>
+          <t>2026-04-09T04:31:12.831334</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653438</t>
+          <t>2026-04-09T04:31:12.831337</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1196</v>
+        <v>1220</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653441</t>
+          <t>2026-04-09T04:31:12.831340</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1198</v>
+        <v>1221</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653444</t>
+          <t>2026-04-09T04:31:12.831343</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653446</t>
+          <t>2026-04-09T04:31:12.831346</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653454</t>
+          <t>2026-04-09T04:31:12.831348</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653461</t>
+          <t>2026-04-09T04:31:12.831351</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653466</t>
+          <t>2026-04-09T04:31:12.831354</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653472</t>
+          <t>2026-04-09T04:31:12.831357</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653478</t>
+          <t>2026-04-09T04:31:12.831360</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653485</t>
+          <t>2026-04-09T04:31:12.831363</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653490</t>
+          <t>2026-04-09T04:31:12.831366</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1178</v>
+        <v>1246</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653496</t>
+          <t>2026-04-09T04:31:12.831369</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1185</v>
+        <v>1237</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653502</t>
+          <t>2026-04-09T04:31:12.831372</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653508</t>
+          <t>2026-04-09T04:31:12.831375</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653514</t>
+          <t>2026-04-09T04:31:12.831378</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653522</t>
+          <t>2026-04-09T04:31:12.831381</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1269</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653525</t>
+          <t>2026-04-09T04:31:12.831384</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1267</v>
+        <v>1206</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653528</t>
+          <t>2026-04-09T04:31:12.831387</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653531</t>
+          <t>2026-04-09T04:31:12.831390</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653534</t>
+          <t>2026-04-09T04:31:12.831393</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653537</t>
+          <t>2026-04-09T04:31:12.831396</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653540</t>
+          <t>2026-04-09T04:31:12.831399</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1359</v>
+        <v>1318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653543</t>
+          <t>2026-04-09T04:31:12.831402</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1361</v>
+        <v>1316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:17.653545</t>
+          <t>2026-04-09T04:31:12.831405</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831243</t>
+          <t>2026-04-10T04:43:51.356643</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831261</t>
+          <t>2026-04-10T04:43:51.356659</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831265</t>
+          <t>2026-04-10T04:43:51.356664</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831268</t>
+          <t>2026-04-10T04:43:51.356667</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831271</t>
+          <t>2026-04-10T04:43:51.356670</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831274</t>
+          <t>2026-04-10T04:43:51.356673</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831277</t>
+          <t>2026-04-10T04:43:51.356676</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831280</t>
+          <t>2026-04-10T04:43:51.356679</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831283</t>
+          <t>2026-04-10T04:43:51.356690</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831286</t>
+          <t>2026-04-10T04:43:51.356693</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831289</t>
+          <t>2026-04-10T04:43:51.356696</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831292</t>
+          <t>2026-04-10T04:43:51.356699</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831295</t>
+          <t>2026-04-10T04:43:51.356702</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831298</t>
+          <t>2026-04-10T04:43:51.356704</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831301</t>
+          <t>2026-04-10T04:43:51.356707</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831304</t>
+          <t>2026-04-10T04:43:51.356710</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831307</t>
+          <t>2026-04-10T04:43:51.356713</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831310</t>
+          <t>2026-04-10T04:43:51.356716</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831313</t>
+          <t>2026-04-10T04:43:51.356722</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831316</t>
+          <t>2026-04-10T04:43:51.356724</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831319</t>
+          <t>2026-04-10T04:43:51.356728</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831323</t>
+          <t>2026-04-10T04:43:51.356731</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831325</t>
+          <t>2026-04-10T04:43:51.356733</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831328</t>
+          <t>2026-04-10T04:43:51.356736</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831331</t>
+          <t>2026-04-10T04:43:51.356739</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831334</t>
+          <t>2026-04-10T04:43:51.356742</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831337</t>
+          <t>2026-04-10T04:43:51.356745</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831340</t>
+          <t>2026-04-10T04:43:51.356748</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831343</t>
+          <t>2026-04-10T04:43:51.356753</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831346</t>
+          <t>2026-04-10T04:43:51.356755</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831348</t>
+          <t>2026-04-10T04:43:51.356758</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831351</t>
+          <t>2026-04-10T04:43:51.356761</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831354</t>
+          <t>2026-04-10T04:43:51.356764</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831357</t>
+          <t>2026-04-10T04:43:51.356767</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831360</t>
+          <t>2026-04-10T04:43:51.356770</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831363</t>
+          <t>2026-04-10T04:43:51.356772</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831366</t>
+          <t>2026-04-10T04:43:51.356775</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831369</t>
+          <t>2026-04-10T04:43:51.356778</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831372</t>
+          <t>2026-04-10T04:43:51.356782</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831375</t>
+          <t>2026-04-10T04:43:51.356785</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831378</t>
+          <t>2026-04-10T04:43:51.356788</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831381</t>
+          <t>2026-04-10T04:43:51.356791</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831384</t>
+          <t>2026-04-10T04:43:51.356794</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831387</t>
+          <t>2026-04-10T04:43:51.356797</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831390</t>
+          <t>2026-04-10T04:43:51.356800</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831393</t>
+          <t>2026-04-10T04:43:51.356803</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831396</t>
+          <t>2026-04-10T04:43:51.356806</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831399</t>
+          <t>2026-04-10T04:43:51.356808</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831402</t>
+          <t>2026-04-10T04:43:51.356811</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:12.831405</t>
+          <t>2026-04-10T04:43:51.356814</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356643</t>
+          <t>2026-04-11T04:19:28.092353</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356659</t>
+          <t>2026-04-11T04:19:28.092372</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356664</t>
+          <t>2026-04-11T04:19:28.092378</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356667</t>
+          <t>2026-04-11T04:19:28.092384</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356670</t>
+          <t>2026-04-11T04:19:28.092389</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356673</t>
+          <t>2026-04-11T04:19:28.092394</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356676</t>
+          <t>2026-04-11T04:19:28.092398</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356679</t>
+          <t>2026-04-11T04:19:28.092403</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356690</t>
+          <t>2026-04-11T04:19:28.092419</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356693</t>
+          <t>2026-04-11T04:19:28.092422</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356696</t>
+          <t>2026-04-11T04:19:28.092425</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356699</t>
+          <t>2026-04-11T04:19:28.092428</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356702</t>
+          <t>2026-04-11T04:19:28.092431</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356704</t>
+          <t>2026-04-11T04:19:28.092434</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356707</t>
+          <t>2026-04-11T04:19:28.092437</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356710</t>
+          <t>2026-04-11T04:19:28.092439</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356713</t>
+          <t>2026-04-11T04:19:28.092442</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356716</t>
+          <t>2026-04-11T04:19:28.092445</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356722</t>
+          <t>2026-04-11T04:19:28.092451</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356724</t>
+          <t>2026-04-11T04:19:28.092454</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356728</t>
+          <t>2026-04-11T04:19:28.092458</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356731</t>
+          <t>2026-04-11T04:19:28.092461</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356733</t>
+          <t>2026-04-11T04:19:28.092464</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356736</t>
+          <t>2026-04-11T04:19:28.092466</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356739</t>
+          <t>2026-04-11T04:19:28.092469</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356742</t>
+          <t>2026-04-11T04:19:28.092472</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356745</t>
+          <t>2026-04-11T04:19:28.092475</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1228</v>
+        <v>1221</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356748</t>
+          <t>2026-04-11T04:19:28.092478</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356753</t>
+          <t>2026-04-11T04:19:28.092483</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356755</t>
+          <t>2026-04-11T04:19:28.092486</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356758</t>
+          <t>2026-04-11T04:19:28.092489</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356761</t>
+          <t>2026-04-11T04:19:28.092492</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356764</t>
+          <t>2026-04-11T04:19:28.092495</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356767</t>
+          <t>2026-04-11T04:19:28.092498</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356770</t>
+          <t>2026-04-11T04:19:28.092501</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356772</t>
+          <t>2026-04-11T04:19:28.092503</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356775</t>
+          <t>2026-04-11T04:19:28.092506</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356778</t>
+          <t>2026-04-11T04:19:28.092509</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356782</t>
+          <t>2026-04-11T04:19:28.092513</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356785</t>
+          <t>2026-04-11T04:19:28.092516</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356788</t>
+          <t>2026-04-11T04:19:28.092518</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356791</t>
+          <t>2026-04-11T04:19:28.092522</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356794</t>
+          <t>2026-04-11T04:19:28.092525</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356797</t>
+          <t>2026-04-11T04:19:28.092527</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356800</t>
+          <t>2026-04-11T04:19:28.092531</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356803</t>
+          <t>2026-04-11T04:19:28.092533</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356806</t>
+          <t>2026-04-11T04:19:28.092536</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356808</t>
+          <t>2026-04-11T04:19:28.092539</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356811</t>
+          <t>2026-04-11T04:19:28.092543</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:51.356814</t>
+          <t>2026-04-11T04:19:28.092545</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092353</t>
+          <t>2026-04-12T04:43:52.692415</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092372</t>
+          <t>2026-04-12T04:43:52.692431</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092378</t>
+          <t>2026-04-12T04:43:52.692435</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092384</t>
+          <t>2026-04-12T04:43:52.692438</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092389</t>
+          <t>2026-04-12T04:43:52.692441</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092394</t>
+          <t>2026-04-12T04:43:52.692444</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092398</t>
+          <t>2026-04-12T04:43:52.692447</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092403</t>
+          <t>2026-04-12T04:43:52.692449</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092419</t>
+          <t>2026-04-12T04:43:52.692483</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092422</t>
+          <t>2026-04-12T04:43:52.692486</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092425</t>
+          <t>2026-04-12T04:43:52.692489</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092428</t>
+          <t>2026-04-12T04:43:52.692492</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092431</t>
+          <t>2026-04-12T04:43:52.692494</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092434</t>
+          <t>2026-04-12T04:43:52.692497</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092437</t>
+          <t>2026-04-12T04:43:52.692500</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092439</t>
+          <t>2026-04-12T04:43:52.692503</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092442</t>
+          <t>2026-04-12T04:43:52.692506</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092445</t>
+          <t>2026-04-12T04:43:52.692509</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092451</t>
+          <t>2026-04-12T04:43:52.692514</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092454</t>
+          <t>2026-04-12T04:43:52.692517</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092458</t>
+          <t>2026-04-12T04:43:52.692520</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092461</t>
+          <t>2026-04-12T04:43:52.692523</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092464</t>
+          <t>2026-04-12T04:43:52.692526</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092466</t>
+          <t>2026-04-12T04:43:52.692528</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092469</t>
+          <t>2026-04-12T04:43:52.692531</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092472</t>
+          <t>2026-04-12T04:43:52.692534</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092475</t>
+          <t>2026-04-12T04:43:52.692537</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092478</t>
+          <t>2026-04-12T04:43:52.692540</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092483</t>
+          <t>2026-04-12T04:43:52.692546</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092486</t>
+          <t>2026-04-12T04:43:52.692549</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092489</t>
+          <t>2026-04-12T04:43:52.692552</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092492</t>
+          <t>2026-04-12T04:43:52.692555</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092495</t>
+          <t>2026-04-12T04:43:52.692557</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092498</t>
+          <t>2026-04-12T04:43:52.692560</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092501</t>
+          <t>2026-04-12T04:43:52.692563</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092503</t>
+          <t>2026-04-12T04:43:52.692566</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092506</t>
+          <t>2026-04-12T04:43:52.692569</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092509</t>
+          <t>2026-04-12T04:43:52.692572</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092513</t>
+          <t>2026-04-12T04:43:52.692576</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092516</t>
+          <t>2026-04-12T04:43:52.692580</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092518</t>
+          <t>2026-04-12T04:43:52.692583</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092522</t>
+          <t>2026-04-12T04:43:52.692586</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092525</t>
+          <t>2026-04-12T04:43:52.692589</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092527</t>
+          <t>2026-04-12T04:43:52.692592</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092531</t>
+          <t>2026-04-12T04:43:52.692594</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092533</t>
+          <t>2026-04-12T04:43:52.692597</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092536</t>
+          <t>2026-04-12T04:43:52.692600</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092539</t>
+          <t>2026-04-12T04:43:52.692603</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092543</t>
+          <t>2026-04-12T04:43:52.692606</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:28.092545</t>
+          <t>2026-04-12T04:43:52.692609</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692415</t>
+          <t>2026-04-13T04:55:09.580263</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692431</t>
+          <t>2026-04-13T04:55:09.580278</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692435</t>
+          <t>2026-04-13T04:55:09.580282</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692438</t>
+          <t>2026-04-13T04:55:09.580285</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692441</t>
+          <t>2026-04-13T04:55:09.580288</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692444</t>
+          <t>2026-04-13T04:55:09.580291</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692447</t>
+          <t>2026-04-13T04:55:09.580294</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692449</t>
+          <t>2026-04-13T04:55:09.580297</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692483</t>
+          <t>2026-04-13T04:55:09.580307</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692486</t>
+          <t>2026-04-13T04:55:09.580310</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692489</t>
+          <t>2026-04-13T04:55:09.580313</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692492</t>
+          <t>2026-04-13T04:55:09.580316</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692494</t>
+          <t>2026-04-13T04:55:09.580319</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692497</t>
+          <t>2026-04-13T04:55:09.580321</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692500</t>
+          <t>2026-04-13T04:55:09.580324</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692503</t>
+          <t>2026-04-13T04:55:09.580327</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692506</t>
+          <t>2026-04-13T04:55:09.580329</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692509</t>
+          <t>2026-04-13T04:55:09.580332</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692514</t>
+          <t>2026-04-13T04:55:09.580338</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692517</t>
+          <t>2026-04-13T04:55:09.580340</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692520</t>
+          <t>2026-04-13T04:55:09.580343</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692523</t>
+          <t>2026-04-13T04:55:09.580346</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692526</t>
+          <t>2026-04-13T04:55:09.580349</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692528</t>
+          <t>2026-04-13T04:55:09.580352</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692531</t>
+          <t>2026-04-13T04:55:09.580355</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692534</t>
+          <t>2026-04-13T04:55:09.580358</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692537</t>
+          <t>2026-04-13T04:55:09.580361</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692540</t>
+          <t>2026-04-13T04:55:09.580364</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692546</t>
+          <t>2026-04-13T04:55:09.580368</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692549</t>
+          <t>2026-04-13T04:55:09.580371</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692552</t>
+          <t>2026-04-13T04:55:09.580374</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692555</t>
+          <t>2026-04-13T04:55:09.580377</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692557</t>
+          <t>2026-04-13T04:55:09.580379</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692560</t>
+          <t>2026-04-13T04:55:09.580382</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692563</t>
+          <t>2026-04-13T04:55:09.580385</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692566</t>
+          <t>2026-04-13T04:55:09.580387</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692569</t>
+          <t>2026-04-13T04:55:09.580390</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692572</t>
+          <t>2026-04-13T04:55:09.580393</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692576</t>
+          <t>2026-04-13T04:55:09.580396</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692580</t>
+          <t>2026-04-13T04:55:09.580399</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692583</t>
+          <t>2026-04-13T04:55:09.580402</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692586</t>
+          <t>2026-04-13T04:55:09.580405</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692589</t>
+          <t>2026-04-13T04:55:09.580408</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692592</t>
+          <t>2026-04-13T04:55:09.580411</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692594</t>
+          <t>2026-04-13T04:55:09.580413</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692597</t>
+          <t>2026-04-13T04:55:09.580416</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692600</t>
+          <t>2026-04-13T04:55:09.580419</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692603</t>
+          <t>2026-04-13T04:55:09.580422</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692606</t>
+          <t>2026-04-13T04:55:09.580425</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:52.692609</t>
+          <t>2026-04-13T04:55:09.580427</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580263</t>
+          <t>2026-04-14T04:42:40.955627</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580278</t>
+          <t>2026-04-14T04:42:40.955652</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580282</t>
+          <t>2026-04-14T04:42:40.955655</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580285</t>
+          <t>2026-04-14T04:42:40.955658</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580288</t>
+          <t>2026-04-14T04:42:40.955661</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580291</t>
+          <t>2026-04-14T04:42:40.955663</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580294</t>
+          <t>2026-04-14T04:42:40.955666</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580297</t>
+          <t>2026-04-14T04:42:40.955669</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580307</t>
+          <t>2026-04-14T04:42:40.955678</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580310</t>
+          <t>2026-04-14T04:42:40.955681</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580313</t>
+          <t>2026-04-14T04:42:40.955684</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580316</t>
+          <t>2026-04-14T04:42:40.955687</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580319</t>
+          <t>2026-04-14T04:42:40.955689</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580321</t>
+          <t>2026-04-14T04:42:40.955692</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580324</t>
+          <t>2026-04-14T04:42:40.955695</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580327</t>
+          <t>2026-04-14T04:42:40.955698</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580329</t>
+          <t>2026-04-14T04:42:40.955700</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580332</t>
+          <t>2026-04-14T04:42:40.955703</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580338</t>
+          <t>2026-04-14T04:42:40.955708</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580340</t>
+          <t>2026-04-14T04:42:40.955711</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580343</t>
+          <t>2026-04-14T04:42:40.955714</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580346</t>
+          <t>2026-04-14T04:42:40.955717</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580349</t>
+          <t>2026-04-14T04:42:40.955720</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580352</t>
+          <t>2026-04-14T04:42:40.955723</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580355</t>
+          <t>2026-04-14T04:42:40.955725</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580358</t>
+          <t>2026-04-14T04:42:40.955728</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580361</t>
+          <t>2026-04-14T04:42:40.955731</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580364</t>
+          <t>2026-04-14T04:42:40.955734</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580368</t>
+          <t>2026-04-14T04:42:40.955739</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580371</t>
+          <t>2026-04-14T04:42:40.955742</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580374</t>
+          <t>2026-04-14T04:42:40.955745</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580377</t>
+          <t>2026-04-14T04:42:40.955748</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580379</t>
+          <t>2026-04-14T04:42:40.955750</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580382</t>
+          <t>2026-04-14T04:42:40.955753</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580385</t>
+          <t>2026-04-14T04:42:40.955756</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580387</t>
+          <t>2026-04-14T04:42:40.955759</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580390</t>
+          <t>2026-04-14T04:42:40.955761</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580393</t>
+          <t>2026-04-14T04:42:40.955764</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580396</t>
+          <t>2026-04-14T04:42:40.955767</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580399</t>
+          <t>2026-04-14T04:42:40.955770</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580402</t>
+          <t>2026-04-14T04:42:40.955773</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580405</t>
+          <t>2026-04-14T04:42:40.955776</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580408</t>
+          <t>2026-04-14T04:42:40.955778</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580411</t>
+          <t>2026-04-14T04:42:40.955781</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580413</t>
+          <t>2026-04-14T04:42:40.955784</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580416</t>
+          <t>2026-04-14T04:42:40.955787</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580419</t>
+          <t>2026-04-14T04:42:40.955789</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580422</t>
+          <t>2026-04-14T04:42:40.955792</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580425</t>
+          <t>2026-04-14T04:42:40.955795</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:09.580427</t>
+          <t>2026-04-14T04:42:40.955798</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955627</t>
+          <t>2026-04-15T04:42:57.771634</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955652</t>
+          <t>2026-04-15T04:42:57.771647</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955655</t>
+          <t>2026-04-15T04:42:57.771651</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955658</t>
+          <t>2026-04-15T04:42:57.771654</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955661</t>
+          <t>2026-04-15T04:42:57.771658</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955663</t>
+          <t>2026-04-15T04:42:57.771661</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955666</t>
+          <t>2026-04-15T04:42:57.771664</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955669</t>
+          <t>2026-04-15T04:42:57.771667</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955678</t>
+          <t>2026-04-15T04:42:57.771670</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955681</t>
+          <t>2026-04-15T04:42:57.771673</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955684</t>
+          <t>2026-04-15T04:42:57.771676</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955687</t>
+          <t>2026-04-15T04:42:57.771679</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955689</t>
+          <t>2026-04-15T04:42:57.771682</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1292</v>
+        <v>1272</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955692</t>
+          <t>2026-04-15T04:42:57.771685</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1295</v>
+        <v>1270</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955695</t>
+          <t>2026-04-15T04:42:57.771688</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1255</v>
+        <v>1295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955698</t>
+          <t>2026-04-15T04:42:57.771691</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955700</t>
+          <t>2026-04-15T04:42:57.771694</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1257</v>
+        <v>1293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955703</t>
+          <t>2026-04-15T04:42:57.771697</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955708</t>
+          <t>2026-04-15T04:42:57.771700</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955711</t>
+          <t>2026-04-15T04:42:57.771703</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955714</t>
+          <t>2026-04-15T04:42:57.771706</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955717</t>
+          <t>2026-04-15T04:42:57.771709</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1264</v>
+        <v>1257</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955720</t>
+          <t>2026-04-15T04:42:57.771712</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955723</t>
+          <t>2026-04-15T04:42:57.771715</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955725</t>
+          <t>2026-04-15T04:42:57.771718</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955728</t>
+          <t>2026-04-15T04:42:57.771721</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955731</t>
+          <t>2026-04-15T04:42:57.771724</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955734</t>
+          <t>2026-04-15T04:42:57.771727</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955739</t>
+          <t>2026-04-15T04:42:57.771730</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955742</t>
+          <t>2026-04-15T04:42:57.771734</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955745</t>
+          <t>2026-04-15T04:42:57.771737</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955748</t>
+          <t>2026-04-15T04:42:57.771741</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955750</t>
+          <t>2026-04-15T04:42:57.771745</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1228</v>
+        <v>1266</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955753</t>
+          <t>2026-04-15T04:42:57.771748</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1223</v>
+        <v>1264</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955756</t>
+          <t>2026-04-15T04:42:57.771751</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1221</v>
+        <v>1268</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955759</t>
+          <t>2026-04-15T04:42:57.771753</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955761</t>
+          <t>2026-04-15T04:42:57.771756</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955764</t>
+          <t>2026-04-15T04:42:57.771759</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955767</t>
+          <t>2026-04-15T04:42:57.771762</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955770</t>
+          <t>2026-04-15T04:42:57.771766</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955773</t>
+          <t>2026-04-15T04:42:57.771769</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955776</t>
+          <t>2026-04-15T04:42:57.771772</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955778</t>
+          <t>2026-04-15T04:42:57.771775</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955781</t>
+          <t>2026-04-15T04:42:57.771778</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955784</t>
+          <t>2026-04-15T04:42:57.771781</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955787</t>
+          <t>2026-04-15T04:42:57.771784</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955789</t>
+          <t>2026-04-15T04:42:57.771787</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955792</t>
+          <t>2026-04-15T04:42:57.771790</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955795</t>
+          <t>2026-04-15T04:42:57.771793</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1185</v>
+        <v>1239</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.955798</t>
+          <t>2026-04-15T04:42:57.771796</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771634</t>
+          <t>2026-04-16T04:48:29.671516</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771647</t>
+          <t>2026-04-16T04:48:29.671532</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771651</t>
+          <t>2026-04-16T04:48:29.671536</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1272</v>
+        <v>1300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771654</t>
+          <t>2026-04-16T04:48:29.671540</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771658</t>
+          <t>2026-04-16T04:48:29.671543</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1277</v>
+        <v>1296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771661</t>
+          <t>2026-04-16T04:48:29.671545</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771664</t>
+          <t>2026-04-16T04:48:29.671548</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771667</t>
+          <t>2026-04-16T04:48:29.671551</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771670</t>
+          <t>2026-04-16T04:48:29.671554</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771673</t>
+          <t>2026-04-16T04:48:29.671557</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771676</t>
+          <t>2026-04-16T04:48:29.671560</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771679</t>
+          <t>2026-04-16T04:48:29.671563</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771682</t>
+          <t>2026-04-16T04:48:29.671566</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771685</t>
+          <t>2026-04-16T04:48:29.671568</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771688</t>
+          <t>2026-04-16T04:48:29.671571</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1295</v>
+        <v>1270</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771691</t>
+          <t>2026-04-16T04:48:29.671574</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1292</v>
+        <v>1272</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771694</t>
+          <t>2026-04-16T04:48:29.671577</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771697</t>
+          <t>2026-04-16T04:48:29.671580</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1259</v>
+        <v>1295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771700</t>
+          <t>2026-04-16T04:48:29.671583</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771703</t>
+          <t>2026-04-16T04:48:29.671586</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1257</v>
+        <v>1292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771706</t>
+          <t>2026-04-16T04:48:29.671589</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771709</t>
+          <t>2026-04-16T04:48:29.671593</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771712</t>
+          <t>2026-04-16T04:48:29.671595</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771715</t>
+          <t>2026-04-16T04:48:29.671598</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771718</t>
+          <t>2026-04-16T04:48:29.671601</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771721</t>
+          <t>2026-04-16T04:48:29.671604</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771724</t>
+          <t>2026-04-16T04:48:29.671607</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771727</t>
+          <t>2026-04-16T04:48:29.671610</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771730</t>
+          <t>2026-04-16T04:48:29.671612</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771734</t>
+          <t>2026-04-16T04:48:29.671616</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771737</t>
+          <t>2026-04-16T04:48:29.671619</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771741</t>
+          <t>2026-04-16T04:48:29.671622</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771745</t>
+          <t>2026-04-16T04:48:29.671624</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771748</t>
+          <t>2026-04-16T04:48:29.671627</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771751</t>
+          <t>2026-04-16T04:48:29.671630</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771753</t>
+          <t>2026-04-16T04:48:29.671633</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771756</t>
+          <t>2026-04-16T04:48:29.671636</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1221</v>
+        <v>1268</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771759</t>
+          <t>2026-04-16T04:48:29.671639</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1228</v>
+        <v>1264</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771762</t>
+          <t>2026-04-16T04:48:29.671642</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771766</t>
+          <t>2026-04-16T04:48:29.671645</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771769</t>
+          <t>2026-04-16T04:48:29.671647</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771772</t>
+          <t>2026-04-16T04:48:29.671650</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1198</v>
+        <v>1221</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771775</t>
+          <t>2026-04-16T04:48:29.671653</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1196</v>
+        <v>1223</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771778</t>
+          <t>2026-04-16T04:48:29.671656</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771781</t>
+          <t>2026-04-16T04:48:29.671659</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771784</t>
+          <t>2026-04-16T04:48:29.671662</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771787</t>
+          <t>2026-04-16T04:48:29.671664</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771790</t>
+          <t>2026-04-16T04:48:29.671667</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771793</t>
+          <t>2026-04-16T04:48:29.671673</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:57.771796</t>
+          <t>2026-04-16T04:48:29.671676</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671516</t>
+          <t>2026-04-17T04:46:15.765566</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671532</t>
+          <t>2026-04-17T04:46:15.765577</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671536</t>
+          <t>2026-04-17T04:46:15.765581</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671540</t>
+          <t>2026-04-17T04:46:15.765585</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671543</t>
+          <t>2026-04-17T04:46:15.765589</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671545</t>
+          <t>2026-04-17T04:46:15.765593</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671548</t>
+          <t>2026-04-17T04:46:15.765596</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671551</t>
+          <t>2026-04-17T04:46:15.765600</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671554</t>
+          <t>2026-04-17T04:46:15.765604</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671557</t>
+          <t>2026-04-17T04:46:15.765607</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671560</t>
+          <t>2026-04-17T04:46:15.765611</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671563</t>
+          <t>2026-04-17T04:46:15.765615</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671566</t>
+          <t>2026-04-17T04:46:15.765618</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671568</t>
+          <t>2026-04-17T04:46:15.765622</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671571</t>
+          <t>2026-04-17T04:46:15.765625</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671574</t>
+          <t>2026-04-17T04:46:15.765648</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671577</t>
+          <t>2026-04-17T04:46:15.765652</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671580</t>
+          <t>2026-04-17T04:46:15.765656</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671583</t>
+          <t>2026-04-17T04:46:15.765660</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671586</t>
+          <t>2026-04-17T04:46:15.765664</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671589</t>
+          <t>2026-04-17T04:46:15.765668</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671593</t>
+          <t>2026-04-17T04:46:15.765671</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671595</t>
+          <t>2026-04-17T04:46:15.765676</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671598</t>
+          <t>2026-04-17T04:46:15.765680</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671601</t>
+          <t>2026-04-17T04:46:15.765684</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671604</t>
+          <t>2026-04-17T04:46:15.765688</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671607</t>
+          <t>2026-04-17T04:46:15.765692</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671610</t>
+          <t>2026-04-17T04:46:15.765695</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671612</t>
+          <t>2026-04-17T04:46:15.765699</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671616</t>
+          <t>2026-04-17T04:46:15.765703</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671619</t>
+          <t>2026-04-17T04:46:15.765706</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671622</t>
+          <t>2026-04-17T04:46:15.765710</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671624</t>
+          <t>2026-04-17T04:46:15.765714</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671627</t>
+          <t>2026-04-17T04:46:15.765717</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671630</t>
+          <t>2026-04-17T04:46:15.765721</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671633</t>
+          <t>2026-04-17T04:46:15.765725</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671636</t>
+          <t>2026-04-17T04:46:15.765729</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671639</t>
+          <t>2026-04-17T04:46:15.765732</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671642</t>
+          <t>2026-04-17T04:46:15.765736</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671645</t>
+          <t>2026-04-17T04:46:15.765740</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671647</t>
+          <t>2026-04-17T04:46:15.765744</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671650</t>
+          <t>2026-04-17T04:46:15.765748</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671653</t>
+          <t>2026-04-17T04:46:15.765752</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671656</t>
+          <t>2026-04-17T04:46:15.765755</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671659</t>
+          <t>2026-04-17T04:46:15.765759</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671662</t>
+          <t>2026-04-17T04:46:15.765762</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671664</t>
+          <t>2026-04-17T04:46:15.765766</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671667</t>
+          <t>2026-04-17T04:46:15.765770</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671673</t>
+          <t>2026-04-17T04:46:15.765773</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:29.671676</t>
+          <t>2026-04-17T04:46:15.765777</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765566</t>
+          <t>2026-04-18T04:29:43.524255</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765577</t>
+          <t>2026-04-18T04:29:43.524272</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765581</t>
+          <t>2026-04-18T04:29:43.524276</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765585</t>
+          <t>2026-04-18T04:29:43.524279</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765589</t>
+          <t>2026-04-18T04:29:43.524282</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765593</t>
+          <t>2026-04-18T04:29:43.524285</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765596</t>
+          <t>2026-04-18T04:29:43.524288</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765600</t>
+          <t>2026-04-18T04:29:43.524291</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765604</t>
+          <t>2026-04-18T04:29:43.524294</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765607</t>
+          <t>2026-04-18T04:29:43.524297</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765611</t>
+          <t>2026-04-18T04:29:43.524300</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1277</v>
+        <v>1270</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765615</t>
+          <t>2026-04-18T04:29:43.524303</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765618</t>
+          <t>2026-04-18T04:29:43.524306</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765622</t>
+          <t>2026-04-18T04:29:43.524309</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765625</t>
+          <t>2026-04-18T04:29:43.524312</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765648</t>
+          <t>2026-04-18T04:29:43.524315</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765652</t>
+          <t>2026-04-18T04:29:43.524317</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765656</t>
+          <t>2026-04-18T04:29:43.524320</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765660</t>
+          <t>2026-04-18T04:29:43.524324</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765664</t>
+          <t>2026-04-18T04:29:43.524326</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765668</t>
+          <t>2026-04-18T04:29:43.524330</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765671</t>
+          <t>2026-04-18T04:29:43.524332</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765676</t>
+          <t>2026-04-18T04:29:43.524335</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765680</t>
+          <t>2026-04-18T04:29:43.524338</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765684</t>
+          <t>2026-04-18T04:29:43.524341</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765688</t>
+          <t>2026-04-18T04:29:43.524344</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765692</t>
+          <t>2026-04-18T04:29:43.524347</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765695</t>
+          <t>2026-04-18T04:29:43.524350</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765699</t>
+          <t>2026-04-18T04:29:43.524353</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765703</t>
+          <t>2026-04-18T04:29:43.524356</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765706</t>
+          <t>2026-04-18T04:29:43.524358</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765710</t>
+          <t>2026-04-18T04:29:43.524361</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765714</t>
+          <t>2026-04-18T04:29:43.524364</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765717</t>
+          <t>2026-04-18T04:29:43.524367</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765721</t>
+          <t>2026-04-18T04:29:43.524370</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765725</t>
+          <t>2026-04-18T04:29:43.524373</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765729</t>
+          <t>2026-04-18T04:29:43.524376</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765732</t>
+          <t>2026-04-18T04:29:43.524378</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765736</t>
+          <t>2026-04-18T04:29:43.524382</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765740</t>
+          <t>2026-04-18T04:29:43.524385</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765744</t>
+          <t>2026-04-18T04:29:43.524388</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765748</t>
+          <t>2026-04-18T04:29:43.524391</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765752</t>
+          <t>2026-04-18T04:29:43.524393</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765755</t>
+          <t>2026-04-18T04:29:43.524396</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765759</t>
+          <t>2026-04-18T04:29:43.524399</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765762</t>
+          <t>2026-04-18T04:29:43.524402</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765766</t>
+          <t>2026-04-18T04:29:43.524405</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765770</t>
+          <t>2026-04-18T04:29:43.524408</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765773</t>
+          <t>2026-04-18T04:29:43.524410</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:15.765777</t>
+          <t>2026-04-18T04:29:43.524413</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524255</t>
+          <t>2026-04-19T04:47:53.902422</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524272</t>
+          <t>2026-04-19T04:47:53.902439</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524276</t>
+          <t>2026-04-19T04:47:53.902442</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524279</t>
+          <t>2026-04-19T04:47:53.902446</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524282</t>
+          <t>2026-04-19T04:47:53.902449</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524285</t>
+          <t>2026-04-19T04:47:53.902452</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524288</t>
+          <t>2026-04-19T04:47:53.902455</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524291</t>
+          <t>2026-04-19T04:47:53.902458</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524294</t>
+          <t>2026-04-19T04:47:53.902461</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524297</t>
+          <t>2026-04-19T04:47:53.902464</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1277</v>
+        <v>1270</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524300</t>
+          <t>2026-04-19T04:47:53.902467</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524303</t>
+          <t>2026-04-19T04:47:53.902470</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524306</t>
+          <t>2026-04-19T04:47:53.902473</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524309</t>
+          <t>2026-04-19T04:47:53.902475</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524312</t>
+          <t>2026-04-19T04:47:53.902479</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524315</t>
+          <t>2026-04-19T04:47:53.902482</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524317</t>
+          <t>2026-04-19T04:47:53.902484</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524320</t>
+          <t>2026-04-19T04:47:53.902487</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524324</t>
+          <t>2026-04-19T04:47:53.902490</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524326</t>
+          <t>2026-04-19T04:47:53.902493</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524330</t>
+          <t>2026-04-19T04:47:53.902497</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524332</t>
+          <t>2026-04-19T04:47:53.902500</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524335</t>
+          <t>2026-04-19T04:47:53.902502</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524338</t>
+          <t>2026-04-19T04:47:53.902505</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524341</t>
+          <t>2026-04-19T04:47:53.902508</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524344</t>
+          <t>2026-04-19T04:47:53.902513</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524347</t>
+          <t>2026-04-19T04:47:53.902516</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524350</t>
+          <t>2026-04-19T04:47:53.902519</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524353</t>
+          <t>2026-04-19T04:47:53.902523</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524356</t>
+          <t>2026-04-19T04:47:53.902526</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524358</t>
+          <t>2026-04-19T04:47:53.902529</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524361</t>
+          <t>2026-04-19T04:47:53.902532</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524364</t>
+          <t>2026-04-19T04:47:53.902535</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524367</t>
+          <t>2026-04-19T04:47:53.902538</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524370</t>
+          <t>2026-04-19T04:47:53.902540</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524373</t>
+          <t>2026-04-19T04:47:53.902543</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524376</t>
+          <t>2026-04-19T04:47:53.902546</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524378</t>
+          <t>2026-04-19T04:47:53.902549</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524382</t>
+          <t>2026-04-19T04:47:53.902552</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524385</t>
+          <t>2026-04-19T04:47:53.902556</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524388</t>
+          <t>2026-04-19T04:47:53.902559</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524391</t>
+          <t>2026-04-19T04:47:53.902562</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524393</t>
+          <t>2026-04-19T04:47:53.902564</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524396</t>
+          <t>2026-04-19T04:47:53.902567</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524399</t>
+          <t>2026-04-19T04:47:53.902570</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524402</t>
+          <t>2026-04-19T04:47:53.902573</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524405</t>
+          <t>2026-04-19T04:47:53.902576</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524408</t>
+          <t>2026-04-19T04:47:53.902579</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524410</t>
+          <t>2026-04-19T04:47:53.902582</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:43.524413</t>
+          <t>2026-04-19T04:47:53.902585</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902422</t>
+          <t>2026-04-20T04:54:56.264408</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902439</t>
+          <t>2026-04-20T04:54:56.264428</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902442</t>
+          <t>2026-04-20T04:54:56.264432</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902446</t>
+          <t>2026-04-20T04:54:56.264435</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902449</t>
+          <t>2026-04-20T04:54:56.264438</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902452</t>
+          <t>2026-04-20T04:54:56.264441</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902455</t>
+          <t>2026-04-20T04:54:56.264444</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902458</t>
+          <t>2026-04-20T04:54:56.264446</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902461</t>
+          <t>2026-04-20T04:54:56.264449</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902464</t>
+          <t>2026-04-20T04:54:56.264452</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902467</t>
+          <t>2026-04-20T04:54:56.264455</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902470</t>
+          <t>2026-04-20T04:54:56.264458</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902473</t>
+          <t>2026-04-20T04:54:56.264461</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902475</t>
+          <t>2026-04-20T04:54:56.264464</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902479</t>
+          <t>2026-04-20T04:54:56.264467</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902482</t>
+          <t>2026-04-20T04:54:56.264470</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902484</t>
+          <t>2026-04-20T04:54:56.264472</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902487</t>
+          <t>2026-04-20T04:54:56.264475</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902490</t>
+          <t>2026-04-20T04:54:56.264479</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902493</t>
+          <t>2026-04-20T04:54:56.264481</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902497</t>
+          <t>2026-04-20T04:54:56.264485</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902500</t>
+          <t>2026-04-20T04:54:56.264488</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902502</t>
+          <t>2026-04-20T04:54:56.264491</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902505</t>
+          <t>2026-04-20T04:54:56.264493</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902508</t>
+          <t>2026-04-20T04:54:56.264496</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902513</t>
+          <t>2026-04-20T04:54:56.264499</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902516</t>
+          <t>2026-04-20T04:54:56.264502</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902519</t>
+          <t>2026-04-20T04:54:56.264505</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902523</t>
+          <t>2026-04-20T04:54:56.264508</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902526</t>
+          <t>2026-04-20T04:54:56.264511</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902529</t>
+          <t>2026-04-20T04:54:56.264514</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902532</t>
+          <t>2026-04-20T04:54:56.264517</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902535</t>
+          <t>2026-04-20T04:54:56.264519</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902538</t>
+          <t>2026-04-20T04:54:56.264523</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902540</t>
+          <t>2026-04-20T04:54:56.264525</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902543</t>
+          <t>2026-04-20T04:54:56.264528</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902546</t>
+          <t>2026-04-20T04:54:56.264531</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902549</t>
+          <t>2026-04-20T04:54:56.264534</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902552</t>
+          <t>2026-04-20T04:54:56.264537</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902556</t>
+          <t>2026-04-20T04:54:56.264540</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902559</t>
+          <t>2026-04-20T04:54:56.264543</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902562</t>
+          <t>2026-04-20T04:54:56.264546</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902564</t>
+          <t>2026-04-20T04:54:56.264549</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902567</t>
+          <t>2026-04-20T04:54:56.264552</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902570</t>
+          <t>2026-04-20T04:54:56.264555</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902573</t>
+          <t>2026-04-20T04:54:56.264557</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902576</t>
+          <t>2026-04-20T04:54:56.264561</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902579</t>
+          <t>2026-04-20T04:54:56.264563</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902582</t>
+          <t>2026-04-20T04:54:56.264566</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:53.902585</t>
+          <t>2026-04-20T04:54:56.264569</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264408</t>
+          <t>2026-04-21T04:45:45.701426</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264428</t>
+          <t>2026-04-21T04:45:45.701441</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264432</t>
+          <t>2026-04-21T04:45:45.701444</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264435</t>
+          <t>2026-04-21T04:45:45.701447</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264438</t>
+          <t>2026-04-21T04:45:45.701450</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264441</t>
+          <t>2026-04-21T04:45:45.701453</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264444</t>
+          <t>2026-04-21T04:45:45.701456</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264446</t>
+          <t>2026-04-21T04:45:45.701458</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264449</t>
+          <t>2026-04-21T04:45:45.701461</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264452</t>
+          <t>2026-04-21T04:45:45.701464</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264455</t>
+          <t>2026-04-21T04:45:45.701467</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264458</t>
+          <t>2026-04-21T04:45:45.701470</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264461</t>
+          <t>2026-04-21T04:45:45.701473</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264464</t>
+          <t>2026-04-21T04:45:45.701476</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264467</t>
+          <t>2026-04-21T04:45:45.701479</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264470</t>
+          <t>2026-04-21T04:45:45.701482</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264472</t>
+          <t>2026-04-21T04:45:45.701484</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264475</t>
+          <t>2026-04-21T04:45:45.701487</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264479</t>
+          <t>2026-04-21T04:45:45.701491</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264481</t>
+          <t>2026-04-21T04:45:45.701493</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264485</t>
+          <t>2026-04-21T04:45:45.701497</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264488</t>
+          <t>2026-04-21T04:45:45.701500</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264491</t>
+          <t>2026-04-21T04:45:45.701503</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264493</t>
+          <t>2026-04-21T04:45:45.701505</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264496</t>
+          <t>2026-04-21T04:45:45.701508</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264499</t>
+          <t>2026-04-21T04:45:45.701511</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264502</t>
+          <t>2026-04-21T04:45:45.701514</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264505</t>
+          <t>2026-04-21T04:45:45.701517</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264508</t>
+          <t>2026-04-21T04:45:45.701520</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264511</t>
+          <t>2026-04-21T04:45:45.701522</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264514</t>
+          <t>2026-04-21T04:45:45.701525</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264517</t>
+          <t>2026-04-21T04:45:45.701528</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264519</t>
+          <t>2026-04-21T04:45:45.701531</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264523</t>
+          <t>2026-04-21T04:45:45.701534</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264525</t>
+          <t>2026-04-21T04:45:45.701537</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264528</t>
+          <t>2026-04-21T04:45:45.701540</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264531</t>
+          <t>2026-04-21T04:45:45.701542</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264534</t>
+          <t>2026-04-21T04:45:45.701545</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264537</t>
+          <t>2026-04-21T04:45:45.701548</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264540</t>
+          <t>2026-04-21T04:45:45.701552</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264543</t>
+          <t>2026-04-21T04:45:45.701554</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264546</t>
+          <t>2026-04-21T04:45:45.701557</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264549</t>
+          <t>2026-04-21T04:45:45.701560</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264552</t>
+          <t>2026-04-21T04:45:45.701563</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264555</t>
+          <t>2026-04-21T04:45:45.701566</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264557</t>
+          <t>2026-04-21T04:45:45.701569</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264561</t>
+          <t>2026-04-21T04:45:45.701571</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264563</t>
+          <t>2026-04-21T04:45:45.701574</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264566</t>
+          <t>2026-04-21T04:45:45.701577</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:56.264569</t>
+          <t>2026-04-21T04:45:45.701580</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701426</t>
+          <t>2026-04-22T04:43:37.580051</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701441</t>
+          <t>2026-04-22T04:43:37.580069</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1289</v>
+        <v>1271</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701444</t>
+          <t>2026-04-22T04:43:37.580073</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701447</t>
+          <t>2026-04-22T04:43:37.580076</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701450</t>
+          <t>2026-04-22T04:43:37.580079</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701453</t>
+          <t>2026-04-22T04:43:37.580082</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701456</t>
+          <t>2026-04-22T04:43:37.580085</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701458</t>
+          <t>2026-04-22T04:43:37.580095</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701461</t>
+          <t>2026-04-22T04:43:37.580098</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701464</t>
+          <t>2026-04-22T04:43:37.580101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1294</v>
+        <v>1277</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701467</t>
+          <t>2026-04-22T04:43:37.580103</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1291</v>
+        <v>1283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701470</t>
+          <t>2026-04-22T04:43:37.580106</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701473</t>
+          <t>2026-04-22T04:43:37.580109</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701476</t>
+          <t>2026-04-22T04:43:37.580112</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701479</t>
+          <t>2026-04-22T04:43:37.580115</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1270</v>
+        <v>1296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701482</t>
+          <t>2026-04-22T04:43:37.580118</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701484</t>
+          <t>2026-04-22T04:43:37.580121</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1272</v>
+        <v>1294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701487</t>
+          <t>2026-04-22T04:43:37.580126</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701491</t>
+          <t>2026-04-22T04:43:37.580129</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701493</t>
+          <t>2026-04-22T04:43:37.580132</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701497</t>
+          <t>2026-04-22T04:43:37.580135</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701500</t>
+          <t>2026-04-22T04:43:37.580138</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701503</t>
+          <t>2026-04-22T04:43:37.580141</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701505</t>
+          <t>2026-04-22T04:43:37.580144</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701508</t>
+          <t>2026-04-22T04:43:37.580147</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701511</t>
+          <t>2026-04-22T04:43:37.580150</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701514</t>
+          <t>2026-04-22T04:43:37.580153</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701517</t>
+          <t>2026-04-22T04:43:37.580158</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1293</v>
+        <v>1272</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701520</t>
+          <t>2026-04-22T04:43:37.580161</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1295</v>
+        <v>1270</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701522</t>
+          <t>2026-04-22T04:43:37.580164</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1257</v>
+        <v>1292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701525</t>
+          <t>2026-04-22T04:43:37.580166</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1259</v>
+        <v>1295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701528</t>
+          <t>2026-04-22T04:43:37.580170</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701531</t>
+          <t>2026-04-22T04:43:37.580172</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701534</t>
+          <t>2026-04-22T04:43:37.580175</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701537</t>
+          <t>2026-04-22T04:43:37.580178</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701540</t>
+          <t>2026-04-22T04:43:37.580181</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701542</t>
+          <t>2026-04-22T04:43:37.580184</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701545</t>
+          <t>2026-04-22T04:43:37.580188</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701548</t>
+          <t>2026-04-22T04:43:37.580191</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701552</t>
+          <t>2026-04-22T04:43:37.580194</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701554</t>
+          <t>2026-04-22T04:43:37.580196</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701557</t>
+          <t>2026-04-22T04:43:37.580200</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701560</t>
+          <t>2026-04-22T04:43:37.580203</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701563</t>
+          <t>2026-04-22T04:43:37.580205</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701566</t>
+          <t>2026-04-22T04:43:37.580208</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701569</t>
+          <t>2026-04-22T04:43:37.580211</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701571</t>
+          <t>2026-04-22T04:43:37.580214</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701574</t>
+          <t>2026-04-22T04:43:37.580217</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701577</t>
+          <t>2026-04-22T04:43:37.580220</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1228</v>
+        <v>1266</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.701580</t>
+          <t>2026-04-22T04:43:37.580223</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580051</t>
+          <t>2026-04-23T04:47:39.179186</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580069</t>
+          <t>2026-04-23T04:47:39.179201</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580073</t>
+          <t>2026-04-23T04:47:39.179205</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1285</v>
+        <v>1271</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580076</t>
+          <t>2026-04-23T04:47:39.179208</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580079</t>
+          <t>2026-04-23T04:47:39.179211</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1289</v>
+        <v>1276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580082</t>
+          <t>2026-04-23T04:47:39.179214</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580085</t>
+          <t>2026-04-23T04:47:39.179217</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580095</t>
+          <t>2026-04-23T04:47:39.179227</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580098</t>
+          <t>2026-04-23T04:47:39.179230</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580101</t>
+          <t>2026-04-23T04:47:39.179233</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580103</t>
+          <t>2026-04-23T04:47:39.179235</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580106</t>
+          <t>2026-04-23T04:47:39.179238</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1294</v>
+        <v>1285</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580109</t>
+          <t>2026-04-23T04:47:39.179241</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1296</v>
+        <v>1283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580112</t>
+          <t>2026-04-23T04:47:39.179244</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580115</t>
+          <t>2026-04-23T04:47:39.179247</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580118</t>
+          <t>2026-04-23T04:47:39.179250</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580121</t>
+          <t>2026-04-23T04:47:39.179253</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580126</t>
+          <t>2026-04-23T04:47:39.179260</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1277</v>
+        <v>1296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580129</t>
+          <t>2026-04-23T04:47:39.179263</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580132</t>
+          <t>2026-04-23T04:47:39.179266</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1272</v>
+        <v>1300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580135</t>
+          <t>2026-04-23T04:47:39.179270</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580138</t>
+          <t>2026-04-23T04:47:39.179273</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580141</t>
+          <t>2026-04-23T04:47:39.179276</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580144</t>
+          <t>2026-04-23T04:47:39.179279</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580147</t>
+          <t>2026-04-23T04:47:39.179281</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580150</t>
+          <t>2026-04-23T04:47:39.179284</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580153</t>
+          <t>2026-04-23T04:47:39.179287</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580158</t>
+          <t>2026-04-23T04:47:39.179292</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580161</t>
+          <t>2026-04-23T04:47:39.179295</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580164</t>
+          <t>2026-04-23T04:47:39.179298</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580166</t>
+          <t>2026-04-23T04:47:39.179300</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580170</t>
+          <t>2026-04-23T04:47:39.179303</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580172</t>
+          <t>2026-04-23T04:47:39.179306</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580175</t>
+          <t>2026-04-23T04:47:39.179309</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1255</v>
+        <v>1292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580178</t>
+          <t>2026-04-23T04:47:39.179312</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1259</v>
+        <v>1293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580181</t>
+          <t>2026-04-23T04:47:39.179315</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580184</t>
+          <t>2026-04-23T04:47:39.179318</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580188</t>
+          <t>2026-04-23T04:47:39.179322</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580191</t>
+          <t>2026-04-23T04:47:39.179325</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580194</t>
+          <t>2026-04-23T04:47:39.179328</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580196</t>
+          <t>2026-04-23T04:47:39.179331</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580200</t>
+          <t>2026-04-23T04:47:39.179334</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580203</t>
+          <t>2026-04-23T04:47:39.179337</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580205</t>
+          <t>2026-04-23T04:47:39.179339</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580208</t>
+          <t>2026-04-23T04:47:39.179342</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580211</t>
+          <t>2026-04-23T04:47:39.179345</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580214</t>
+          <t>2026-04-23T04:47:39.179348</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580217</t>
+          <t>2026-04-23T04:47:39.179351</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580220</t>
+          <t>2026-04-23T04:47:39.179354</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:37.580223</t>
+          <t>2026-04-23T04:47:39.179357</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1276</v>
+        <v>1265</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179186</t>
+          <t>2026-04-24T04:51:35.281304</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1269</v>
+        <v>1260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179201</t>
+          <t>2026-04-24T04:51:35.281316</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1274</v>
+        <v>1263</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179205</t>
+          <t>2026-04-24T04:51:35.281319</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179208</t>
+          <t>2026-04-24T04:51:35.281323</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179211</t>
+          <t>2026-04-24T04:51:35.281326</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179214</t>
+          <t>2026-04-24T04:51:35.281329</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179217</t>
+          <t>2026-04-24T04:51:35.281331</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179227</t>
+          <t>2026-04-24T04:51:35.281341</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1289</v>
+        <v>1271</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179230</t>
+          <t>2026-04-24T04:51:35.281344</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179233</t>
+          <t>2026-04-24T04:51:35.281347</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179235</t>
+          <t>2026-04-24T04:51:35.281350</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179238</t>
+          <t>2026-04-24T04:51:35.281353</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179241</t>
+          <t>2026-04-24T04:51:35.281357</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179244</t>
+          <t>2026-04-24T04:51:35.281368</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179247</t>
+          <t>2026-04-24T04:51:35.281374</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179250</t>
+          <t>2026-04-24T04:51:35.281380</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179253</t>
+          <t>2026-04-24T04:51:35.281386</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179260</t>
+          <t>2026-04-24T04:51:35.281395</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179263</t>
+          <t>2026-04-24T04:51:35.281398</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179266</t>
+          <t>2026-04-24T04:51:35.281401</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179270</t>
+          <t>2026-04-24T04:51:35.281405</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179273</t>
+          <t>2026-04-24T04:51:35.281408</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179276</t>
+          <t>2026-04-24T04:51:35.281410</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179279</t>
+          <t>2026-04-24T04:51:35.281413</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179281</t>
+          <t>2026-04-24T04:51:35.281416</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179284</t>
+          <t>2026-04-24T04:51:35.281419</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179287</t>
+          <t>2026-04-24T04:51:35.281422</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179292</t>
+          <t>2026-04-24T04:51:35.281427</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179295</t>
+          <t>2026-04-24T04:51:35.281429</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179298</t>
+          <t>2026-04-24T04:51:35.281432</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179300</t>
+          <t>2026-04-24T04:51:35.281435</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179303</t>
+          <t>2026-04-24T04:51:35.281438</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179306</t>
+          <t>2026-04-24T04:51:35.281440</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179309</t>
+          <t>2026-04-24T04:51:35.281443</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179312</t>
+          <t>2026-04-24T04:51:35.281446</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179315</t>
+          <t>2026-04-24T04:51:35.281449</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179318</t>
+          <t>2026-04-24T04:51:35.281452</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179322</t>
+          <t>2026-04-24T04:51:35.281456</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179325</t>
+          <t>2026-04-24T04:51:35.281459</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179328</t>
+          <t>2026-04-24T04:51:35.281462</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179331</t>
+          <t>2026-04-24T04:51:35.281465</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179334</t>
+          <t>2026-04-24T04:51:35.281468</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179337</t>
+          <t>2026-04-24T04:51:35.281470</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179339</t>
+          <t>2026-04-24T04:51:35.281473</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179342</t>
+          <t>2026-04-24T04:51:35.281476</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179345</t>
+          <t>2026-04-24T04:51:35.281479</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179348</t>
+          <t>2026-04-24T04:51:35.281481</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179351</t>
+          <t>2026-04-24T04:51:35.281484</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179354</t>
+          <t>2026-04-24T04:51:35.281487</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:39.179357</t>
+          <t>2026-04-24T04:51:35.281490</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281304</t>
+          <t>2026-04-25T04:33:39.417458</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281316</t>
+          <t>2026-04-25T04:33:39.417481</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281319</t>
+          <t>2026-04-25T04:33:39.417487</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281323</t>
+          <t>2026-04-25T04:33:39.417493</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281326</t>
+          <t>2026-04-25T04:33:39.417498</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281329</t>
+          <t>2026-04-25T04:33:39.417501</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281331</t>
+          <t>2026-04-25T04:33:39.417504</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281341</t>
+          <t>2026-04-25T04:33:39.417513</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281344</t>
+          <t>2026-04-25T04:33:39.417516</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281347</t>
+          <t>2026-04-25T04:33:39.417519</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281350</t>
+          <t>2026-04-25T04:33:39.417522</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281353</t>
+          <t>2026-04-25T04:33:39.417525</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281357</t>
+          <t>2026-04-25T04:33:39.417528</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281368</t>
+          <t>2026-04-25T04:33:39.417530</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281374</t>
+          <t>2026-04-25T04:33:39.417533</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281380</t>
+          <t>2026-04-25T04:33:39.417536</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1285</v>
+        <v>1277</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281386</t>
+          <t>2026-04-25T04:33:39.417539</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281395</t>
+          <t>2026-04-25T04:33:39.417545</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281398</t>
+          <t>2026-04-25T04:33:39.417547</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281401</t>
+          <t>2026-04-25T04:33:39.417550</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281405</t>
+          <t>2026-04-25T04:33:39.417554</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281408</t>
+          <t>2026-04-25T04:33:39.417557</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281410</t>
+          <t>2026-04-25T04:33:39.417559</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281413</t>
+          <t>2026-04-25T04:33:39.417562</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281416</t>
+          <t>2026-04-25T04:33:39.417565</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281419</t>
+          <t>2026-04-25T04:33:39.417568</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281422</t>
+          <t>2026-04-25T04:33:39.417571</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281427</t>
+          <t>2026-04-25T04:33:39.417576</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281429</t>
+          <t>2026-04-25T04:33:39.417579</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281432</t>
+          <t>2026-04-25T04:33:39.417581</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281435</t>
+          <t>2026-04-25T04:33:39.417584</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281438</t>
+          <t>2026-04-25T04:33:39.417587</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281440</t>
+          <t>2026-04-25T04:33:39.417590</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281443</t>
+          <t>2026-04-25T04:33:39.417593</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281446</t>
+          <t>2026-04-25T04:33:39.417596</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281449</t>
+          <t>2026-04-25T04:33:39.417598</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281452</t>
+          <t>2026-04-25T04:33:39.417601</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281456</t>
+          <t>2026-04-25T04:33:39.417605</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281459</t>
+          <t>2026-04-25T04:33:39.417608</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281462</t>
+          <t>2026-04-25T04:33:39.417611</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281465</t>
+          <t>2026-04-25T04:33:39.417614</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281468</t>
+          <t>2026-04-25T04:33:39.417618</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281470</t>
+          <t>2026-04-25T04:33:39.417621</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281473</t>
+          <t>2026-04-25T04:33:39.417623</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281476</t>
+          <t>2026-04-25T04:33:39.417626</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281479</t>
+          <t>2026-04-25T04:33:39.417629</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281481</t>
+          <t>2026-04-25T04:33:39.417632</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281484</t>
+          <t>2026-04-25T04:33:39.417635</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281487</t>
+          <t>2026-04-25T04:33:39.417638</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:35.281490</t>
+          <t>2026-04-25T04:33:39.417641</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417458</t>
+          <t>2026-04-26T04:56:11.919054</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417481</t>
+          <t>2026-04-26T04:56:11.919076</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417487</t>
+          <t>2026-04-26T04:56:11.919080</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417493</t>
+          <t>2026-04-26T04:56:11.919084</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417498</t>
+          <t>2026-04-26T04:56:11.919087</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417501</t>
+          <t>2026-04-26T04:56:11.919090</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417504</t>
+          <t>2026-04-26T04:56:11.919093</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417513</t>
+          <t>2026-04-26T04:56:11.919096</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417516</t>
+          <t>2026-04-26T04:56:11.919099</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417519</t>
+          <t>2026-04-26T04:56:11.919102</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417522</t>
+          <t>2026-04-26T04:56:11.919104</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417525</t>
+          <t>2026-04-26T04:56:11.919107</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417528</t>
+          <t>2026-04-26T04:56:11.919110</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417530</t>
+          <t>2026-04-26T04:56:11.919113</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417533</t>
+          <t>2026-04-26T04:56:11.919116</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417536</t>
+          <t>2026-04-26T04:56:11.919119</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417539</t>
+          <t>2026-04-26T04:56:11.919122</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417545</t>
+          <t>2026-04-26T04:56:11.919125</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417547</t>
+          <t>2026-04-26T04:56:11.919128</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417550</t>
+          <t>2026-04-26T04:56:11.919131</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417554</t>
+          <t>2026-04-26T04:56:11.919135</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417557</t>
+          <t>2026-04-26T04:56:11.919138</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417559</t>
+          <t>2026-04-26T04:56:11.919141</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417562</t>
+          <t>2026-04-26T04:56:11.919144</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417565</t>
+          <t>2026-04-26T04:56:11.919147</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417568</t>
+          <t>2026-04-26T04:56:11.919150</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417571</t>
+          <t>2026-04-26T04:56:11.919152</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417576</t>
+          <t>2026-04-26T04:56:11.919155</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417579</t>
+          <t>2026-04-26T04:56:11.919158</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417581</t>
+          <t>2026-04-26T04:56:11.919161</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417584</t>
+          <t>2026-04-26T04:56:11.919164</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417587</t>
+          <t>2026-04-26T04:56:11.919167</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417590</t>
+          <t>2026-04-26T04:56:11.919170</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417593</t>
+          <t>2026-04-26T04:56:11.919173</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417596</t>
+          <t>2026-04-26T04:56:11.919176</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417598</t>
+          <t>2026-04-26T04:56:11.919179</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417601</t>
+          <t>2026-04-26T04:56:11.919181</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417605</t>
+          <t>2026-04-26T04:56:11.919185</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417608</t>
+          <t>2026-04-26T04:56:11.919188</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417611</t>
+          <t>2026-04-26T04:56:11.919191</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417614</t>
+          <t>2026-04-26T04:56:11.919193</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417618</t>
+          <t>2026-04-26T04:56:11.919198</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417621</t>
+          <t>2026-04-26T04:56:11.919202</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417623</t>
+          <t>2026-04-26T04:56:11.919207</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417626</t>
+          <t>2026-04-26T04:56:11.919210</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417629</t>
+          <t>2026-04-26T04:56:11.919212</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417632</t>
+          <t>2026-04-26T04:56:11.919215</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417635</t>
+          <t>2026-04-26T04:56:11.919218</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417638</t>
+          <t>2026-04-26T04:56:11.919221</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:39.417641</t>
+          <t>2026-04-26T04:56:11.919224</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919054</t>
+          <t>2026-04-27T05:19:52.524818</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919076</t>
+          <t>2026-04-27T05:19:52.524831</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1261.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919080</t>
+          <t>2026-04-27T05:19:52.524835</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1269</v>
+        <v>1260</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919084</t>
+          <t>2026-04-27T05:19:52.524838</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1274</v>
+        <v>1263</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919087</t>
+          <t>2026-04-27T05:19:52.524841</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1276</v>
+        <v>1265</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919090</t>
+          <t>2026-04-27T05:19:52.524844</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919093</t>
+          <t>2026-04-27T05:19:52.524846</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919096</t>
+          <t>2026-04-27T05:19:52.524856</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919099</t>
+          <t>2026-04-27T05:19:52.524859</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919102</t>
+          <t>2026-04-27T05:19:52.524862</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919104</t>
+          <t>2026-04-27T05:19:52.524865</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1289</v>
+        <v>1271</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919107</t>
+          <t>2026-04-27T05:19:52.524867</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919110</t>
+          <t>2026-04-27T05:19:52.524870</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919113</t>
+          <t>2026-04-27T05:19:52.524873</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919116</t>
+          <t>2026-04-27T05:19:52.524876</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919119</t>
+          <t>2026-04-27T05:19:52.524879</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919122</t>
+          <t>2026-04-27T05:19:52.524881</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919125</t>
+          <t>2026-04-27T05:19:52.524886</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919128</t>
+          <t>2026-04-27T05:19:52.524889</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919131</t>
+          <t>2026-04-27T05:19:52.524892</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919135</t>
+          <t>2026-04-27T05:19:52.524895</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919138</t>
+          <t>2026-04-27T05:19:52.524898</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919141</t>
+          <t>2026-04-27T05:19:52.524901</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919144</t>
+          <t>2026-04-27T05:19:52.524904</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919147</t>
+          <t>2026-04-27T05:19:52.524907</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919150</t>
+          <t>2026-04-27T05:19:52.524910</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919152</t>
+          <t>2026-04-27T05:19:52.524912</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919155</t>
+          <t>2026-04-27T05:19:52.524917</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919158</t>
+          <t>2026-04-27T05:19:52.524920</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919161</t>
+          <t>2026-04-27T05:19:52.524922</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919164</t>
+          <t>2026-04-27T05:19:52.524925</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919167</t>
+          <t>2026-04-27T05:19:52.524928</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919170</t>
+          <t>2026-04-27T05:19:52.524931</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919173</t>
+          <t>2026-04-27T05:19:52.524933</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919176</t>
+          <t>2026-04-27T05:19:52.524936</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919179</t>
+          <t>2026-04-27T05:19:52.524939</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919181</t>
+          <t>2026-04-27T05:19:52.524942</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919185</t>
+          <t>2026-04-27T05:19:52.524946</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919188</t>
+          <t>2026-04-27T05:19:52.524949</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919191</t>
+          <t>2026-04-27T05:19:52.524952</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919193</t>
+          <t>2026-04-27T05:19:52.524956</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919198</t>
+          <t>2026-04-27T05:19:52.524960</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919202</t>
+          <t>2026-04-27T05:19:52.524963</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919207</t>
+          <t>2026-04-27T05:19:52.524965</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919210</t>
+          <t>2026-04-27T05:19:52.524968</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919212</t>
+          <t>2026-04-27T05:19:52.524971</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919215</t>
+          <t>2026-04-27T05:19:52.524974</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919218</t>
+          <t>2026-04-27T05:19:52.524977</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919221</t>
+          <t>2026-04-27T05:19:52.524979</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:11.919224</t>
+          <t>2026-04-27T05:19:52.524982</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524818</t>
+          <t>2026-04-28T05:27:39.544451</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524831</t>
+          <t>2026-04-28T05:27:39.544466</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1261.00</t>
+          <t>1262.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524835</t>
+          <t>2026-04-28T05:27:39.544470</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1261.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524838</t>
+          <t>2026-04-28T05:27:39.544473</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524841</t>
+          <t>2026-04-28T05:27:39.544476</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524844</t>
+          <t>2026-04-28T05:27:39.544479</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1276</v>
+        <v>1265</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524846</t>
+          <t>2026-04-28T05:27:39.544482</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1269</v>
+        <v>1260</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524856</t>
+          <t>2026-04-28T05:27:39.544493</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1274</v>
+        <v>1263</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524859</t>
+          <t>2026-04-28T05:27:39.544496</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524862</t>
+          <t>2026-04-28T05:27:39.544499</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524865</t>
+          <t>2026-04-28T05:27:39.544502</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524867</t>
+          <t>2026-04-28T05:27:39.544505</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524870</t>
+          <t>2026-04-28T05:27:39.544508</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1289</v>
+        <v>1271</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524873</t>
+          <t>2026-04-28T05:27:39.544511</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524876</t>
+          <t>2026-04-28T05:27:39.544514</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524879</t>
+          <t>2026-04-28T05:27:39.544517</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524881</t>
+          <t>2026-04-28T05:27:39.544521</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524886</t>
+          <t>2026-04-28T05:27:39.544530</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524889</t>
+          <t>2026-04-28T05:27:39.544533</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524892</t>
+          <t>2026-04-28T05:27:39.544536</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524895</t>
+          <t>2026-04-28T05:27:39.544539</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524898</t>
+          <t>2026-04-28T05:27:39.544542</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524901</t>
+          <t>2026-04-28T05:27:39.544545</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524904</t>
+          <t>2026-04-28T05:27:39.544548</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524907</t>
+          <t>2026-04-28T05:27:39.544551</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524910</t>
+          <t>2026-04-28T05:27:39.544554</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524912</t>
+          <t>2026-04-28T05:27:39.544557</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524917</t>
+          <t>2026-04-28T05:27:39.544561</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524920</t>
+          <t>2026-04-28T05:27:39.544564</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524922</t>
+          <t>2026-04-28T05:27:39.544567</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524925</t>
+          <t>2026-04-28T05:27:39.544570</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524928</t>
+          <t>2026-04-28T05:27:39.544573</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524931</t>
+          <t>2026-04-28T05:27:39.544576</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524933</t>
+          <t>2026-04-28T05:27:39.544579</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524936</t>
+          <t>2026-04-28T05:27:39.544582</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524939</t>
+          <t>2026-04-28T05:27:39.544585</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524942</t>
+          <t>2026-04-28T05:27:39.544588</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524946</t>
+          <t>2026-04-28T05:27:39.544592</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524949</t>
+          <t>2026-04-28T05:27:39.544595</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524952</t>
+          <t>2026-04-28T05:27:39.544598</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524956</t>
+          <t>2026-04-28T05:27:39.544601</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524960</t>
+          <t>2026-04-28T05:27:39.544604</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524963</t>
+          <t>2026-04-28T05:27:39.544607</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524965</t>
+          <t>2026-04-28T05:27:39.544610</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524968</t>
+          <t>2026-04-28T05:27:39.544613</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524971</t>
+          <t>2026-04-28T05:27:39.544616</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524974</t>
+          <t>2026-04-28T05:27:39.544619</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524977</t>
+          <t>2026-04-28T05:27:39.544622</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524979</t>
+          <t>2026-04-28T05:27:39.544625</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:52.524982</t>
+          <t>2026-04-28T05:27:39.544628</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1263</v>
+        <v>1234</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544451</t>
+          <t>2026-04-29T05:23:09.301142</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1265</v>
+        <v>1236</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544466</t>
+          <t>2026-04-29T05:23:09.301156</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1262.00</t>
+          <t>1232.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1262</v>
+        <v>1232</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544470</t>
+          <t>2026-04-29T05:23:09.301160</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1261.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544473</t>
+          <t>2026-04-29T05:23:09.301164</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544476</t>
+          <t>2026-04-29T05:23:09.301167</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1262.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544479</t>
+          <t>2026-04-29T05:23:09.301170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544482</t>
+          <t>2026-04-29T05:23:09.301173</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544493</t>
+          <t>2026-04-29T05:23:09.301188</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1261.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544496</t>
+          <t>2026-04-29T05:23:09.301191</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1276</v>
+        <v>1265</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544499</t>
+          <t>2026-04-29T05:23:09.301194</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1274</v>
+        <v>1260</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544502</t>
+          <t>2026-04-29T05:23:09.301197</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544505</t>
+          <t>2026-04-29T05:23:09.301200</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544508</t>
+          <t>2026-04-29T05:23:09.301203</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544511</t>
+          <t>2026-04-29T05:23:09.301206</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544514</t>
+          <t>2026-04-29T05:23:09.301209</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544517</t>
+          <t>2026-04-29T05:23:09.301211</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1289</v>
+        <v>1271</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544521</t>
+          <t>2026-04-29T05:23:09.301214</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1285</v>
+        <v>1274</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544530</t>
+          <t>2026-04-29T05:23:09.301219</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544533</t>
+          <t>2026-04-29T05:23:09.301222</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544536</t>
+          <t>2026-04-29T05:23:09.301225</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544539</t>
+          <t>2026-04-29T05:23:09.301228</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544542</t>
+          <t>2026-04-29T05:23:09.301232</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544545</t>
+          <t>2026-04-29T05:23:09.301234</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544548</t>
+          <t>2026-04-29T05:23:09.301237</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1291</v>
+        <v>1285</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544551</t>
+          <t>2026-04-29T05:23:09.301240</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544554</t>
+          <t>2026-04-29T05:23:09.301243</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1296</v>
+        <v>1277</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544557</t>
+          <t>2026-04-29T05:23:09.301246</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544561</t>
+          <t>2026-04-29T05:23:09.301250</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544564</t>
+          <t>2026-04-29T05:23:09.301253</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544567</t>
+          <t>2026-04-29T05:23:09.301256</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1272</v>
+        <v>1300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544570</t>
+          <t>2026-04-29T05:23:09.301259</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1277</v>
+        <v>1296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544573</t>
+          <t>2026-04-29T05:23:09.301262</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544576</t>
+          <t>2026-04-29T05:23:09.301265</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544579</t>
+          <t>2026-04-29T05:23:09.301267</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544582</t>
+          <t>2026-04-29T05:23:09.301270</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544585</t>
+          <t>2026-04-29T05:23:09.301273</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544588</t>
+          <t>2026-04-29T05:23:09.301276</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544592</t>
+          <t>2026-04-29T05:23:09.301279</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544595</t>
+          <t>2026-04-29T05:23:09.301282</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544598</t>
+          <t>2026-04-29T05:23:09.301285</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544601</t>
+          <t>2026-04-29T05:23:09.301288</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544604</t>
+          <t>2026-04-29T05:23:09.301291</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544607</t>
+          <t>2026-04-29T05:23:09.301294</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544610</t>
+          <t>2026-04-29T05:23:09.301297</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544613</t>
+          <t>2026-04-29T05:23:09.301300</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1255</v>
+        <v>1295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544616</t>
+          <t>2026-04-29T05:23:09.301303</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1257</v>
+        <v>1292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544619</t>
+          <t>2026-04-29T05:23:09.301305</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1259</v>
+        <v>1293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544622</t>
+          <t>2026-04-29T05:23:09.301308</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544625</t>
+          <t>2026-04-29T05:23:09.301311</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:39.544628</t>
+          <t>2026-04-29T05:23:09.301314</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1234.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301142</t>
+          <t>2026-04-30T05:27:19.000489</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1236.00</t>
+          <t>1235.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301156</t>
+          <t>2026-04-30T05:27:19.000503</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1232.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301160</t>
+          <t>2026-04-30T05:27:19.000507</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1232.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1265</v>
+        <v>1232</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301164</t>
+          <t>2026-04-30T05:27:19.000511</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1263</v>
+        <v>1234</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301167</t>
+          <t>2026-04-30T05:27:19.000514</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1262.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1262</v>
+        <v>1236</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301170</t>
+          <t>2026-04-30T05:27:19.000518</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301173</t>
+          <t>2026-04-30T05:27:19.000522</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301188</t>
+          <t>2026-04-30T05:27:19.000532</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1261.00</t>
+          <t>1262.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301191</t>
+          <t>2026-04-30T05:27:19.000536</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301194</t>
+          <t>2026-04-30T05:27:19.000539</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301197</t>
+          <t>2026-04-30T05:27:19.000543</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1261.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301200</t>
+          <t>2026-04-30T05:27:19.000547</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1274</v>
+        <v>1265</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301203</t>
+          <t>2026-04-30T05:27:19.000550</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1276</v>
+        <v>1263</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301206</t>
+          <t>2026-04-30T05:27:19.000553</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1269</v>
+        <v>1260</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301209</t>
+          <t>2026-04-30T05:27:19.000557</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301211</t>
+          <t>2026-04-30T05:27:19.000560</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301214</t>
+          <t>2026-04-30T05:27:19.000564</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301219</t>
+          <t>2026-04-30T05:27:19.000569</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1289</v>
+        <v>1276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301222</t>
+          <t>2026-04-30T05:27:19.000573</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301225</t>
+          <t>2026-04-30T05:27:19.000576</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1285</v>
+        <v>1271</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301228</t>
+          <t>2026-04-30T05:27:19.000580</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301232</t>
+          <t>2026-04-30T05:27:19.000584</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301234</t>
+          <t>2026-04-30T05:27:19.000588</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301237</t>
+          <t>2026-04-30T05:27:19.000591</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301240</t>
+          <t>2026-04-30T05:27:19.000594</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301243</t>
+          <t>2026-04-30T05:27:19.000598</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301246</t>
+          <t>2026-04-30T05:27:19.000602</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1294</v>
+        <v>1277</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301250</t>
+          <t>2026-04-30T05:27:19.000607</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1296</v>
+        <v>1283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301253</t>
+          <t>2026-04-30T05:27:19.000610</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1291</v>
+        <v>1285</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301256</t>
+          <t>2026-04-30T05:27:19.000614</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301259</t>
+          <t>2026-04-30T05:27:19.000617</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301262</t>
+          <t>2026-04-30T05:27:19.000620</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301265</t>
+          <t>2026-04-30T05:27:19.000624</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301267</t>
+          <t>2026-04-30T05:27:19.000627</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1270</v>
+        <v>1300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301270</t>
+          <t>2026-04-30T05:27:19.000631</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1277</v>
+        <v>1294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301273</t>
+          <t>2026-04-30T05:27:19.000634</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301276</t>
+          <t>2026-04-30T05:27:19.000637</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301279</t>
+          <t>2026-04-30T05:27:19.000642</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301282</t>
+          <t>2026-04-30T05:27:19.000645</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301285</t>
+          <t>2026-04-30T05:27:19.000648</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301288</t>
+          <t>2026-04-30T05:27:19.000651</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301291</t>
+          <t>2026-04-30T05:27:19.000654</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301294</t>
+          <t>2026-04-30T05:27:19.000656</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301297</t>
+          <t>2026-04-30T05:27:19.000659</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301300</t>
+          <t>2026-04-30T05:27:19.000662</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301303</t>
+          <t>2026-04-30T05:27:19.000665</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301305</t>
+          <t>2026-04-30T05:27:19.000667</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301308</t>
+          <t>2026-04-30T05:27:19.000670</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1255</v>
+        <v>1295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301311</t>
+          <t>2026-04-30T05:27:19.000673</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1257</v>
+        <v>1293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:09.301314</t>
+          <t>2026-04-30T05:27:19.000676</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1236.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000489</t>
+          <t>2026-05-01T05:38:33.655178</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1235.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000503</t>
+          <t>2026-05-01T05:38:33.655194</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1234.00</t>
+          <t>1235.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000507</t>
+          <t>2026-05-01T05:38:33.655198</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000511</t>
+          <t>2026-05-01T05:38:33.655201</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000514</t>
+          <t>2026-05-01T05:38:33.655204</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000518</t>
+          <t>2026-05-01T05:38:33.655207</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000522</t>
+          <t>2026-05-01T05:38:33.655209</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1262.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000532</t>
+          <t>2026-05-01T05:38:33.655221</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1262.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000536</t>
+          <t>2026-05-01T05:38:33.655224</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000539</t>
+          <t>2026-05-01T05:38:33.655227</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000543</t>
+          <t>2026-05-01T05:38:33.655230</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000547</t>
+          <t>2026-05-01T05:38:33.655233</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000550</t>
+          <t>2026-05-01T05:38:33.655236</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000553</t>
+          <t>2026-05-01T05:38:33.655238</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000557</t>
+          <t>2026-05-01T05:38:33.655241</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000560</t>
+          <t>2026-05-01T05:38:33.655244</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000564</t>
+          <t>2026-05-01T05:38:33.655247</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000569</t>
+          <t>2026-05-01T05:38:33.655253</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000573</t>
+          <t>2026-05-01T05:38:33.655256</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000576</t>
+          <t>2026-05-01T05:38:33.655258</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000580</t>
+          <t>2026-05-01T05:38:33.655262</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000584</t>
+          <t>2026-05-01T05:38:33.655265</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000588</t>
+          <t>2026-05-01T05:38:33.655268</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000591</t>
+          <t>2026-05-01T05:38:33.655270</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000594</t>
+          <t>2026-05-01T05:38:33.655273</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000598</t>
+          <t>2026-05-01T05:38:33.655276</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000602</t>
+          <t>2026-05-01T05:38:33.655279</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000607</t>
+          <t>2026-05-01T05:38:33.655284</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000610</t>
+          <t>2026-05-01T05:38:33.655287</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000614</t>
+          <t>2026-05-01T05:38:33.655290</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000617</t>
+          <t>2026-05-01T05:38:33.655292</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000620</t>
+          <t>2026-05-01T05:38:33.655295</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000624</t>
+          <t>2026-05-01T05:38:33.655298</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000627</t>
+          <t>2026-05-01T05:38:33.655301</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000631</t>
+          <t>2026-05-01T05:38:33.655305</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000634</t>
+          <t>2026-05-01T05:38:33.655308</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000637</t>
+          <t>2026-05-01T05:38:33.655311</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1277</v>
+        <v>1270</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000642</t>
+          <t>2026-05-01T05:38:33.655315</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000645</t>
+          <t>2026-05-01T05:38:33.655318</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000648</t>
+          <t>2026-05-01T05:38:33.655321</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000651</t>
+          <t>2026-05-01T05:38:33.655324</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000654</t>
+          <t>2026-05-01T05:38:33.655327</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000656</t>
+          <t>2026-05-01T05:38:33.655329</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000659</t>
+          <t>2026-05-01T05:38:33.655332</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000662</t>
+          <t>2026-05-01T05:38:33.655335</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000665</t>
+          <t>2026-05-01T05:38:33.655338</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000667</t>
+          <t>2026-05-01T05:38:33.655341</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000670</t>
+          <t>2026-05-01T05:38:33.655344</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000673</t>
+          <t>2026-05-01T05:38:33.655348</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:19.000676</t>
+          <t>2026-05-01T05:38:33.655351</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1234.00</t>
+          <t>1235.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655178</t>
+          <t>2026-05-02T04:55:48.163532</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1236.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655194</t>
+          <t>2026-05-02T04:55:48.163547</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1235.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655198</t>
+          <t>2026-05-02T04:55:48.163551</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1232.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655201</t>
+          <t>2026-05-02T04:55:48.163555</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1234.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655204</t>
+          <t>2026-05-02T04:55:48.163558</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1236.00</t>
+          <t>1232.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655207</t>
+          <t>2026-05-02T04:55:48.163561</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655209</t>
+          <t>2026-05-02T04:55:48.163563</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1262.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655221</t>
+          <t>2026-05-02T04:55:48.163566</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1262.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655224</t>
+          <t>2026-05-02T04:55:48.163569</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655227</t>
+          <t>2026-05-02T04:55:48.163572</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1261.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655230</t>
+          <t>2026-05-02T04:55:48.163575</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1261.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655233</t>
+          <t>2026-05-02T04:55:48.163578</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655236</t>
+          <t>2026-05-02T04:55:48.163581</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655238</t>
+          <t>2026-05-02T04:55:48.163584</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655241</t>
+          <t>2026-05-02T04:55:48.163587</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655244</t>
+          <t>2026-05-02T04:55:48.163590</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655247</t>
+          <t>2026-05-02T04:55:48.163592</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655253</t>
+          <t>2026-05-02T04:55:48.163595</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655256</t>
+          <t>2026-05-02T04:55:48.163598</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655258</t>
+          <t>2026-05-02T04:55:48.163601</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655262</t>
+          <t>2026-05-02T04:55:48.163605</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655265</t>
+          <t>2026-05-02T04:55:48.163608</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655268</t>
+          <t>2026-05-02T04:55:48.163610</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655270</t>
+          <t>2026-05-02T04:55:48.163613</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655273</t>
+          <t>2026-05-02T04:55:48.163616</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655276</t>
+          <t>2026-05-02T04:55:48.163619</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655279</t>
+          <t>2026-05-02T04:55:48.163622</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655284</t>
+          <t>2026-05-02T04:55:48.163625</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655287</t>
+          <t>2026-05-02T04:55:48.163628</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655290</t>
+          <t>2026-05-02T04:55:48.163630</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655292</t>
+          <t>2026-05-02T04:55:48.163633</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655295</t>
+          <t>2026-05-02T04:55:48.163637</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655298</t>
+          <t>2026-05-02T04:55:48.163641</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655301</t>
+          <t>2026-05-02T04:55:48.163645</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655305</t>
+          <t>2026-05-02T04:55:48.163648</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655308</t>
+          <t>2026-05-02T04:55:48.163650</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655311</t>
+          <t>2026-05-02T04:55:48.163653</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655315</t>
+          <t>2026-05-02T04:55:48.163656</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655318</t>
+          <t>2026-05-02T04:55:48.163660</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655321</t>
+          <t>2026-05-02T04:55:48.163662</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655324</t>
+          <t>2026-05-02T04:55:48.163665</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655327</t>
+          <t>2026-05-02T04:55:48.163668</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655329</t>
+          <t>2026-05-02T04:55:48.163671</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655332</t>
+          <t>2026-05-02T04:55:48.163674</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655335</t>
+          <t>2026-05-02T04:55:48.163677</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655338</t>
+          <t>2026-05-02T04:55:48.163680</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655341</t>
+          <t>2026-05-02T04:55:48.163683</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655344</t>
+          <t>2026-05-02T04:55:48.163686</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655348</t>
+          <t>2026-05-02T04:55:48.163689</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:33.655351</t>
+          <t>2026-05-02T04:55:48.163691</t>
         </is>
       </c>
     </row>

--- a/gold_bar_latest.xlsx
+++ b/gold_bar_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1235.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163532</t>
+          <t>2026-05-03T05:27:17.942274</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1234.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163547</t>
+          <t>2026-05-03T05:27:17.942297</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1236.00</t>
+          <t>1235.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163551</t>
+          <t>2026-05-03T05:27:17.942305</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1234.00</t>
+          <t>1232.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163555</t>
+          <t>2026-05-03T05:27:17.942312</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1236.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163558</t>
+          <t>2026-05-03T05:27:17.942318</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1232.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163561</t>
+          <t>2026-05-03T05:27:17.942324</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1262.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163563</t>
+          <t>2026-05-03T05:27:17.942330</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163566</t>
+          <t>2026-05-03T05:27:17.942358</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1262.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163569</t>
+          <t>2026-05-03T05:27:17.942362</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163572</t>
+          <t>2026-05-03T05:27:17.942365</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1261.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163575</t>
+          <t>2026-05-03T05:27:17.942368</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1261.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163578</t>
+          <t>2026-05-03T05:27:17.942371</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163581</t>
+          <t>2026-05-03T05:27:17.942374</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163584</t>
+          <t>2026-05-03T05:27:17.942377</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163587</t>
+          <t>2026-05-03T05:27:17.942380</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163590</t>
+          <t>2026-05-03T05:27:17.942383</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163592</t>
+          <t>2026-05-03T05:27:17.942386</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163595</t>
+          <t>2026-05-03T05:27:17.942389</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163598</t>
+          <t>2026-05-03T05:27:17.942392</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163601</t>
+          <t>2026-05-03T05:27:17.942395</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163605</t>
+          <t>2026-05-03T05:27:17.942399</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163608</t>
+          <t>2026-05-03T05:27:17.942402</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163610</t>
+          <t>2026-05-03T05:27:17.942404</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163613</t>
+          <t>2026-05-03T05:27:17.942407</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163616</t>
+          <t>2026-05-03T05:27:17.942410</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:48.163619</t>
+          <t>2026-05-03T05:27:17.942413</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          